--- a/research/traditional_assets/database/data/portugal/portugal_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_telecom_services.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -599,40 +599,40 @@
         <v>-0.0204</v>
       </c>
       <c r="G2">
-        <v>0.3273472469395459</v>
+        <v>0.3259720649301623</v>
       </c>
       <c r="H2">
-        <v>0.3273472469395459</v>
+        <v>0.3259720649301623</v>
       </c>
       <c r="I2">
-        <v>0.149760017257186</v>
+        <v>0.148643693037804</v>
       </c>
       <c r="J2">
-        <v>0.1366542220708337</v>
+        <v>0.1421396413143358</v>
       </c>
       <c r="K2">
-        <v>285.3</v>
+        <v>285.109</v>
       </c>
       <c r="L2">
-        <v>0.1538585989322116</v>
+        <v>0.1537555951032735</v>
       </c>
       <c r="M2">
         <v>117.65</v>
       </c>
       <c r="N2">
-        <v>0.06674041297935104</v>
+        <v>0.0652777007157521</v>
       </c>
       <c r="O2">
-        <v>0.412372940764108</v>
+        <v>0.412649197324532</v>
       </c>
       <c r="P2">
         <v>112.9</v>
       </c>
       <c r="Q2">
-        <v>0.06404583616972997</v>
+        <v>0.06264217943738556</v>
       </c>
       <c r="R2">
-        <v>0.3957237995092885</v>
+        <v>0.3959889024899249</v>
       </c>
       <c r="S2">
         <v>4.75</v>
@@ -641,73 +641,73 @@
         <v>0.04037399065023374</v>
       </c>
       <c r="U2">
-        <v>34.7</v>
+        <v>51.8</v>
       </c>
       <c r="V2">
-        <v>0.01968459269344225</v>
+        <v>0.02874105309881818</v>
       </c>
       <c r="W2">
-        <v>0.2868778280542987</v>
+        <v>0.1421501151067715</v>
       </c>
       <c r="X2">
-        <v>0.1027224721581503</v>
+        <v>0.09005860988640407</v>
       </c>
       <c r="Y2">
-        <v>0.1841553558961483</v>
+        <v>0.0520915052203674</v>
       </c>
       <c r="Z2">
-        <v>0.8498556304138595</v>
+        <v>0.8313513101528156</v>
       </c>
       <c r="AA2">
-        <v>0.1161363600467239</v>
+        <v>0.03675653583516059</v>
       </c>
       <c r="AB2">
-        <v>0.07951308812672432</v>
+        <v>0.07844983781681902</v>
       </c>
       <c r="AC2">
-        <v>0.03662327191999962</v>
+        <v>-0.04169330198165843</v>
       </c>
       <c r="AD2">
-        <v>1787.3</v>
+        <v>1787.329</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1787.3</v>
+        <v>1787.329</v>
       </c>
       <c r="AG2">
-        <v>1752.6</v>
+        <v>1735.529</v>
       </c>
       <c r="AH2">
-        <v>0.5034506070251542</v>
+        <v>0.4979146870052588</v>
       </c>
       <c r="AI2">
-        <v>0.6130758412513292</v>
+        <v>0.5981431859200188</v>
       </c>
       <c r="AJ2">
-        <v>0.4985492404847244</v>
+        <v>0.4905632804751163</v>
       </c>
       <c r="AK2">
-        <v>0.608414913559675</v>
+        <v>0.5910539997391301</v>
       </c>
       <c r="AL2">
         <v>95.40000000000001</v>
       </c>
       <c r="AM2">
-        <v>85.30000000000001</v>
+        <v>84.935</v>
       </c>
       <c r="AN2">
-        <v>2.756477483035164</v>
+        <v>2.765264949330858</v>
       </c>
       <c r="AO2">
-        <v>2.910901467505241</v>
+        <v>2.889203354297694</v>
       </c>
       <c r="AP2">
-        <v>2.702961135101789</v>
+        <v>2.685122611588149</v>
       </c>
       <c r="AQ2">
-        <v>3.255568581477139</v>
+        <v>3.245187496320716</v>
       </c>
     </row>
     <row r="3">
@@ -787,10 +787,10 @@
         <v>0.2868778280542987</v>
       </c>
       <c r="X3">
-        <v>0.1027224721581503</v>
+        <v>0.1027032013272417</v>
       </c>
       <c r="Y3">
-        <v>0.1841553558961483</v>
+        <v>0.1841746267270569</v>
       </c>
       <c r="Z3">
         <v>0.8498556304138595</v>
@@ -799,10 +799,10 @@
         <v>0.1161363600467239</v>
       </c>
       <c r="AB3">
-        <v>0.07951308812672432</v>
+        <v>0.07950351920733453</v>
       </c>
       <c r="AC3">
-        <v>0.03662327191999962</v>
+        <v>0.03663284083938941</v>
       </c>
       <c r="AD3">
         <v>1787.3</v>
@@ -845,6 +845,113 @@
       </c>
       <c r="AQ3">
         <v>3.255568581477139</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pharol, SGPS S.A. (ENXTLS:PHR)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Telecom. Services</t>
+        </is>
+      </c>
+      <c r="K4">
+        <v>-0.191</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>17.1</v>
+      </c>
+      <c r="V4">
+        <v>0.4329113924050633</v>
+      </c>
+      <c r="W4">
+        <v>-0.002577597840755736</v>
+      </c>
+      <c r="X4">
+        <v>0.07741401844556642</v>
+      </c>
+      <c r="Y4">
+        <v>-0.07999161628632215</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>-0.04262328837640277</v>
+      </c>
+      <c r="AB4">
+        <v>0.0773961564263035</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1200194448027063</v>
+      </c>
+      <c r="AD4">
+        <v>0.029</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.029</v>
+      </c>
+      <c r="AG4">
+        <v>-17.071</v>
+      </c>
+      <c r="AH4">
+        <v>0.0007336385944496446</v>
+      </c>
+      <c r="AI4">
+        <v>0.0003981930275027805</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.7611128449774847</v>
+      </c>
+      <c r="AK4">
+        <v>-0.3063216637657235</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>-0.365</v>
+      </c>
+      <c r="AN4">
+        <v>-0.01414634146341464</v>
+      </c>
+      <c r="AP4">
+        <v>8.327317073170732</v>
+      </c>
+      <c r="AQ4">
+        <v>5.671232876712328</v>
       </c>
     </row>
   </sheetData>
@@ -1139,7 +1246,7 @@
         <v>0.954926624737946</v>
       </c>
       <c r="F2">
-        <v>14.023577782473</v>
+        <v>14.3393569022883</v>
       </c>
       <c r="G2">
         <v>2.75647748303516</v>
@@ -1157,13 +1264,13 @@
         <v>1762.8</v>
       </c>
       <c r="L2">
-        <v>3343.42779872791</v>
+        <v>3346.52614424949</v>
       </c>
       <c r="M2">
         <v>3515.4</v>
       </c>
       <c r="N2">
-        <v>3592.73579872791</v>
+        <v>3595.83414424949</v>
       </c>
       <c r="O2">
         <v>1787.3</v>
@@ -1172,16 +1279,16 @@
         <v>284.008</v>
       </c>
       <c r="Q2">
-        <v>0.07951308812672429</v>
+        <v>0.07950351920733451</v>
       </c>
       <c r="R2">
-        <v>0.0772292340784468</v>
+        <v>0.07713023364834989</v>
       </c>
       <c r="S2">
         <v>0.0566218543268039</v>
       </c>
       <c r="T2">
-        <v>0.0502228543268039</v>
+        <v>0.0491168543268039</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1301,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.10272247215815</v>
+        <v>0.102703201327242</v>
       </c>
       <c r="X2">
-        <v>0.0795776149264158</v>
+        <v>0.07956617967631049</v>
       </c>
       <c r="Y2">
         <v>0.959469722745937</v>
@@ -1236,7 +1343,7 @@
         <v>1762.8</v>
       </c>
       <c r="AK2">
-        <v>0.05932701242019611</v>
+        <v>0.05930692754367342</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1531,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.0774063931370042</v>
+        <v>0.07739569294365908</v>
       </c>
       <c r="C2">
-        <v>3621.315316475573</v>
+        <v>3621.35497792876</v>
       </c>
       <c r="D2">
-        <v>3586.615316475573</v>
+        <v>3586.65497792876</v>
       </c>
       <c r="E2">
         <v>-1787.3</v>
@@ -1475,19 +1582,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.0774063931370042</v>
+        <v>0.07739569294365908</v>
       </c>
       <c r="T2">
         <v>0.532748774085323</v>
       </c>
       <c r="U2">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V2">
         <v>0.21</v>
       </c>
       <c r="W2">
-        <v>0.05022285432680387</v>
+        <v>0.04911685432680387</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1613,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07738424825468454</v>
+        <v>0.07736251053174545</v>
       </c>
       <c r="C3">
-        <v>3586.578236096196</v>
+        <v>3586.998810040751</v>
       </c>
       <c r="D3">
-        <v>3587.379236096197</v>
+        <v>3587.799810040751</v>
       </c>
       <c r="E3">
         <v>-1751.799</v>
@@ -1539,37 +1646,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M3">
-        <v>2.256913356273246</v>
+        <v>2.207211956273246</v>
       </c>
       <c r="N3">
-        <v>250.9430866437267</v>
+        <v>250.9927880437267</v>
       </c>
       <c r="O3">
-        <v>52.6980481951826</v>
+        <v>52.7084854891826</v>
       </c>
       <c r="P3">
-        <v>198.2450384485441</v>
+        <v>198.2843025545441</v>
       </c>
       <c r="Q3">
-        <v>755.545038448544</v>
+        <v>755.584302554544</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07765860576910757</v>
+        <v>0.07764782019038122</v>
       </c>
       <c r="T3">
         <v>0.5370000016765089</v>
       </c>
       <c r="U3">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V3">
         <v>0.21</v>
       </c>
       <c r="W3">
-        <v>0.05022285432680387</v>
+        <v>0.04911685432680387</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1684,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>112.1886222597838</v>
+        <v>114.7148552183063</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1695,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07736210337236489</v>
+        <v>0.0773293281198318</v>
       </c>
       <c r="C4">
-        <v>3551.841481203362</v>
+        <v>3552.643373228942</v>
       </c>
       <c r="D4">
-        <v>3588.143481203363</v>
+        <v>3588.945373228942</v>
       </c>
       <c r="E4">
         <v>-1716.298</v>
@@ -1621,37 +1728,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M4">
-        <v>4.513826712546491</v>
+        <v>4.414423912546491</v>
       </c>
       <c r="N4">
-        <v>248.6861732874534</v>
+        <v>248.7855760874534</v>
       </c>
       <c r="O4">
-        <v>52.22409639036522</v>
+        <v>52.24497097836522</v>
       </c>
       <c r="P4">
-        <v>196.4620768970882</v>
+        <v>196.5406051090882</v>
       </c>
       <c r="Q4">
-        <v>753.7620768970881</v>
+        <v>753.8406051090882</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07791596559778449</v>
+        <v>0.07790509289111808</v>
       </c>
       <c r="T4">
         <v>0.5413379890144537</v>
       </c>
       <c r="U4">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V4">
         <v>0.21</v>
       </c>
       <c r="W4">
-        <v>0.05022285432680387</v>
+        <v>0.04911685432680387</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1766,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>56.09431112989189</v>
+        <v>57.35742760915314</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1777,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.0773399584900452</v>
+        <v>0.07729614570791815</v>
       </c>
       <c r="C5">
-        <v>3517.105052005139</v>
+        <v>3518.28866819384</v>
       </c>
       <c r="D5">
-        <v>3588.908052005139</v>
+        <v>3590.09166819384</v>
       </c>
       <c r="E5">
         <v>-1680.797</v>
@@ -1703,37 +1810,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M5">
-        <v>6.770740068819737</v>
+        <v>6.621635868819737</v>
       </c>
       <c r="N5">
-        <v>246.4292599311802</v>
+        <v>246.5783641311802</v>
       </c>
       <c r="O5">
-        <v>51.75014458554784</v>
+        <v>51.78145646754784</v>
       </c>
       <c r="P5">
-        <v>194.6791153456323</v>
+        <v>194.7969076636323</v>
       </c>
       <c r="Q5">
-        <v>751.9791153456323</v>
+        <v>752.0969076636322</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07817863181468153</v>
+        <v>0.07816767018362272</v>
       </c>
       <c r="T5">
         <v>0.5457654193902942</v>
       </c>
       <c r="U5">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V5">
         <v>0.21</v>
       </c>
       <c r="W5">
-        <v>0.05022285432680387</v>
+        <v>0.04911685432680387</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1848,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>37.39620741992792</v>
+        <v>38.23828507276875</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1859,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07731781360772551</v>
+        <v>0.0772629632960045</v>
       </c>
       <c r="C6">
-        <v>3482.368948709769</v>
+        <v>3483.93469563685</v>
       </c>
       <c r="D6">
-        <v>3589.672948709769</v>
+        <v>3591.23869563685</v>
       </c>
       <c r="E6">
         <v>-1645.296</v>
@@ -1785,37 +1892,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M6">
-        <v>9.027653425092982</v>
+        <v>8.828847825092982</v>
       </c>
       <c r="N6">
-        <v>244.172346574907</v>
+        <v>244.3711521749069</v>
       </c>
       <c r="O6">
-        <v>51.27619278073046</v>
+        <v>51.31794195673046</v>
       </c>
       <c r="P6">
-        <v>192.8961537941765</v>
+        <v>193.0532102181765</v>
       </c>
       <c r="Q6">
-        <v>750.1961537941764</v>
+        <v>750.3532102181764</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07844677024443059</v>
+        <v>0.07843571783638786</v>
       </c>
       <c r="T6">
         <v>0.5502850878989648</v>
       </c>
       <c r="U6">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V6">
         <v>0.21</v>
       </c>
       <c r="W6">
-        <v>0.05022285432680387</v>
+        <v>0.04911685432680387</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1930,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.04715556494594</v>
+        <v>28.67871380457657</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1941,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07729566872540584</v>
+        <v>0.07722978088409087</v>
       </c>
       <c r="C7">
-        <v>3447.633171525672</v>
+        <v>3449.581456260271</v>
       </c>
       <c r="D7">
-        <v>3590.438171525672</v>
+        <v>3592.386456260272</v>
       </c>
       <c r="E7">
         <v>-1609.795</v>
@@ -1867,37 +1974,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M7">
-        <v>11.28456678136623</v>
+        <v>11.03605978136623</v>
       </c>
       <c r="N7">
-        <v>241.9154332186337</v>
+        <v>242.1639402186337</v>
       </c>
       <c r="O7">
-        <v>50.80224097591307</v>
+        <v>50.85442744591307</v>
       </c>
       <c r="P7">
-        <v>191.1131922427206</v>
+        <v>191.3095127727206</v>
       </c>
       <c r="Q7">
-        <v>748.4131922427206</v>
+        <v>748.6095127727206</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07872055369375333</v>
+        <v>0.07870940859763229</v>
       </c>
       <c r="T7">
         <v>0.5548999073236075</v>
       </c>
       <c r="U7">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V7">
         <v>0.21</v>
       </c>
       <c r="W7">
-        <v>0.05022285432680387</v>
+        <v>0.04911685432680387</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +2012,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.43772445195675</v>
+        <v>22.94297104366126</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +2023,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07727352384308618</v>
+        <v>0.07719659847217722</v>
       </c>
       <c r="C8">
-        <v>3412.897720661449</v>
+        <v>3415.228950767304</v>
       </c>
       <c r="D8">
-        <v>3591.203720661449</v>
+        <v>3593.534950767305</v>
       </c>
       <c r="E8">
         <v>-1574.294</v>
@@ -1949,37 +2056,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M8">
-        <v>13.54148013763947</v>
+        <v>13.24327173763947</v>
       </c>
       <c r="N8">
-        <v>239.6585198623605</v>
+        <v>239.9567282623605</v>
       </c>
       <c r="O8">
-        <v>50.3282891710957</v>
+        <v>50.39091293509569</v>
       </c>
       <c r="P8">
-        <v>189.3302306912648</v>
+        <v>189.5658153272648</v>
       </c>
       <c r="Q8">
-        <v>746.6302306912647</v>
+        <v>746.8658153272647</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07900016232284889</v>
+        <v>0.07898892256656274</v>
       </c>
       <c r="T8">
         <v>0.5596129143955828</v>
       </c>
       <c r="U8">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V8">
         <v>0.21</v>
       </c>
       <c r="W8">
-        <v>0.05022285432680387</v>
+        <v>0.04911685432680387</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +2094,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.69810370996396</v>
+        <v>19.11914253638438</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +2105,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07725137896076652</v>
+        <v>0.07716341606026356</v>
       </c>
       <c r="C9">
-        <v>3378.162596325877</v>
+        <v>3380.877179862045</v>
       </c>
       <c r="D9">
-        <v>3591.969596325877</v>
+        <v>3594.684179862045</v>
       </c>
       <c r="E9">
         <v>-1538.793</v>
@@ -2031,37 +2138,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M9">
-        <v>15.79839349391272</v>
+        <v>15.45048369391272</v>
       </c>
       <c r="N9">
-        <v>237.4016065060872</v>
+        <v>237.7495163060872</v>
       </c>
       <c r="O9">
-        <v>49.85433736627831</v>
+        <v>49.92739842427831</v>
       </c>
       <c r="P9">
-        <v>187.5472691398089</v>
+        <v>187.8221178818089</v>
       </c>
       <c r="Q9">
-        <v>744.8472691398089</v>
+        <v>745.1221178818089</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.0792857840407422</v>
+        <v>0.0792744475885885</v>
       </c>
       <c r="T9">
         <v>0.5644272764583534</v>
       </c>
       <c r="U9">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V9">
         <v>0.21</v>
       </c>
       <c r="W9">
-        <v>0.05022285432680387</v>
+        <v>0.04911685432680387</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2176,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.02694603711197</v>
+        <v>16.38783645975803</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2187,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07722923407844684</v>
+        <v>0.07713023364834992</v>
       </c>
       <c r="C10">
-        <v>3343.427798727911</v>
+        <v>3346.526144249493</v>
       </c>
       <c r="D10">
-        <v>3592.735798727911</v>
+        <v>3595.834144249493</v>
       </c>
       <c r="E10">
         <v>-1503.292</v>
@@ -2113,37 +2220,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M10">
-        <v>18.05530685018596</v>
+        <v>17.65769565018596</v>
       </c>
       <c r="N10">
-        <v>235.144693149814</v>
+        <v>235.542304349814</v>
       </c>
       <c r="O10">
-        <v>49.38038556146093</v>
+        <v>49.46388391346093</v>
       </c>
       <c r="P10">
-        <v>185.764307588353</v>
+        <v>186.078420436353</v>
       </c>
       <c r="Q10">
-        <v>743.064307588353</v>
+        <v>743.3784204363531</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.0795776149264158</v>
+        <v>0.07956617967631045</v>
       </c>
       <c r="T10">
         <v>0.5693462985659669</v>
       </c>
       <c r="U10">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V10">
         <v>0.21</v>
       </c>
       <c r="W10">
-        <v>0.05022285432680387</v>
+        <v>0.04911685432680387</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2258,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.02357778247297</v>
+        <v>14.33935690228829</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2269,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07728529919612719</v>
+        <v>0.07720370123643627</v>
       </c>
       <c r="C11">
-        <v>3305.98760577393</v>
+        <v>3308.480051363006</v>
       </c>
       <c r="D11">
-        <v>3590.79660577393</v>
+        <v>3593.289051363006</v>
       </c>
       <c r="E11">
         <v>-1467.791</v>
@@ -2195,37 +2302,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M11">
-        <v>20.66368010645921</v>
+        <v>20.34417110645921</v>
       </c>
       <c r="N11">
-        <v>232.5363198935407</v>
+        <v>232.8558288935407</v>
       </c>
       <c r="O11">
-        <v>48.83262717764355</v>
+        <v>48.89972406764355</v>
       </c>
       <c r="P11">
-        <v>183.7036927158972</v>
+        <v>183.9561048258972</v>
       </c>
       <c r="Q11">
-        <v>741.0036927158972</v>
+        <v>741.2561048258972</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.0798758596777086</v>
+        <v>0.07986432345826805</v>
       </c>
       <c r="T11">
         <v>0.5743734310495718</v>
       </c>
       <c r="U11">
-        <v>0.06467323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V11">
         <v>0.21</v>
       </c>
       <c r="W11">
-        <v>0.05109185432680387</v>
+        <v>0.05030185432680388</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2340,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.25338365167842</v>
+        <v>12.44582532633191</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2351,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07727184431380751</v>
+        <v>0.07718236882452263</v>
       </c>
       <c r="C12">
-        <v>3270.951795349539</v>
+        <v>3273.71768585173</v>
       </c>
       <c r="D12">
-        <v>3591.261795349539</v>
+        <v>3594.02768585173</v>
       </c>
       <c r="E12">
         <v>-1432.29</v>
@@ -2277,37 +2384,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M12">
-        <v>22.95964456273246</v>
+        <v>22.60463456273246</v>
       </c>
       <c r="N12">
-        <v>230.2403554372675</v>
+        <v>230.5953654372675</v>
       </c>
       <c r="O12">
-        <v>48.35047464182617</v>
+        <v>48.42502674182617</v>
       </c>
       <c r="P12">
-        <v>181.8898807954413</v>
+        <v>182.1703386954413</v>
       </c>
       <c r="Q12">
-        <v>739.1898807954412</v>
+        <v>739.4703386954412</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08018073209014125</v>
+        <v>0.0801690926576025</v>
       </c>
       <c r="T12">
         <v>0.579512277588368</v>
       </c>
       <c r="U12">
-        <v>0.06467323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V12">
         <v>0.21</v>
       </c>
       <c r="W12">
-        <v>0.05109185432680387</v>
+        <v>0.05030185432680388</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2422,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.02804528651058</v>
+        <v>11.20124279369872</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2433,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07725838943148784</v>
+        <v>0.07716103641260899</v>
       </c>
       <c r="C13">
-        <v>3235.91610547187</v>
+        <v>3238.955624069472</v>
       </c>
       <c r="D13">
-        <v>3591.72710547187</v>
+        <v>3594.766624069473</v>
       </c>
       <c r="E13">
         <v>-1396.789</v>
@@ -2359,37 +2466,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M13">
-        <v>25.2556090190057</v>
+        <v>24.8650980190057</v>
       </c>
       <c r="N13">
-        <v>227.9443909809942</v>
+        <v>228.3349019809942</v>
       </c>
       <c r="O13">
-        <v>47.86832210600878</v>
+        <v>47.95032941600878</v>
       </c>
       <c r="P13">
-        <v>180.0760688749855</v>
+        <v>180.3845725649854</v>
       </c>
       <c r="Q13">
-        <v>737.3760688749854</v>
+        <v>737.6845725649854</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08049245556802181</v>
+        <v>0.08048071060298939</v>
       </c>
       <c r="T13">
         <v>0.5847666038246652</v>
       </c>
       <c r="U13">
-        <v>0.06467323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V13">
         <v>0.21</v>
       </c>
       <c r="W13">
-        <v>0.05109185432680387</v>
+        <v>0.05030185432680388</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2504,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.02549571500962</v>
+        <v>10.18294799427156</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2515,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07745349454916815</v>
+        <v>0.07730086400069534</v>
       </c>
       <c r="C14">
-        <v>3193.679566848742</v>
+        <v>3198.616628899476</v>
       </c>
       <c r="D14">
-        <v>3584.991566848742</v>
+        <v>3589.928628899476</v>
       </c>
       <c r="E14">
         <v>-1361.288</v>
@@ -2441,37 +2548,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M14">
-        <v>28.48879987527895</v>
+        <v>27.84978187527895</v>
       </c>
       <c r="N14">
-        <v>224.711200124721</v>
+        <v>225.350218124721</v>
       </c>
       <c r="O14">
-        <v>47.18935202619141</v>
+        <v>47.3235458061914</v>
       </c>
       <c r="P14">
-        <v>177.5218480985296</v>
+        <v>178.0266723185296</v>
       </c>
       <c r="Q14">
-        <v>734.8218480985295</v>
+        <v>735.3266723185295</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08081126367039966</v>
+        <v>0.08079941077440782</v>
       </c>
       <c r="T14">
         <v>0.5901403465663327</v>
       </c>
       <c r="U14">
-        <v>0.06687323332506818</v>
+        <v>0.06537323332506818</v>
       </c>
       <c r="V14">
         <v>0.21</v>
       </c>
       <c r="W14">
-        <v>0.05282985432680387</v>
+        <v>0.05164485432680387</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2586,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.887703276673065</v>
+        <v>9.091633145778951</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2597,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07745741966684851</v>
+        <v>0.07729296158878171</v>
       </c>
       <c r="C15">
-        <v>3158.043320741584</v>
+        <v>3163.388702914172</v>
       </c>
       <c r="D15">
-        <v>3584.856320741585</v>
+        <v>3590.201702914172</v>
       </c>
       <c r="E15">
         <v>-1325.787</v>
@@ -2523,37 +2630,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M15">
-        <v>30.86286653155219</v>
+        <v>30.17059703155219</v>
       </c>
       <c r="N15">
-        <v>222.3371334684477</v>
+        <v>223.0294029684478</v>
       </c>
       <c r="O15">
-        <v>46.69079802837403</v>
+        <v>46.83617462337403</v>
       </c>
       <c r="P15">
-        <v>175.6463354400737</v>
+        <v>176.1932283450737</v>
       </c>
       <c r="Q15">
-        <v>732.9463354400737</v>
+        <v>733.4932283450737</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08113740069467126</v>
+        <v>0.08112543738654851</v>
       </c>
       <c r="T15">
         <v>0.5956376236239008</v>
       </c>
       <c r="U15">
-        <v>0.06687323332506818</v>
+        <v>0.06537323332506818</v>
       </c>
       <c r="V15">
         <v>0.21</v>
       </c>
       <c r="W15">
-        <v>0.05282985432680387</v>
+        <v>0.05164485432680387</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2668,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.204033793852062</v>
+        <v>8.392276749949801</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2679,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07762724478452883</v>
+        <v>0.07728505917686805</v>
       </c>
       <c r="C16">
-        <v>3116.700485109196</v>
+        <v>3128.160818475704</v>
       </c>
       <c r="D16">
-        <v>3579.014485109196</v>
+        <v>3590.474818475705</v>
       </c>
       <c r="E16">
         <v>-1290.286</v>
@@ -2605,45 +2712,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M16">
-        <v>33.98245418782544</v>
+        <v>32.49141218782544</v>
       </c>
       <c r="N16">
-        <v>219.2175458121745</v>
+        <v>220.7085878121745</v>
       </c>
       <c r="O16">
-        <v>46.03568462055664</v>
+        <v>46.34880344055664</v>
       </c>
       <c r="P16">
-        <v>173.1818611916178</v>
+        <v>174.3597843716178</v>
       </c>
       <c r="Q16">
-        <v>730.4818611916178</v>
+        <v>731.6597843716178</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08147112230090266</v>
+        <v>0.08145904601292502</v>
       </c>
       <c r="T16">
         <v>0.6012627443339703</v>
       </c>
       <c r="U16">
-        <v>0.06837323332506819</v>
+        <v>0.06537323332506818</v>
       </c>
       <c r="V16">
         <v>0.21</v>
       </c>
       <c r="W16">
-        <v>0.05401485432680387</v>
+        <v>0.05164485432680387</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.450903887062736</v>
+        <v>7.792828410667672</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2761,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07764301990220915</v>
+        <v>0.0773719567649544</v>
       </c>
       <c r="C17">
-        <v>3080.65780113956</v>
+        <v>3089.658829514847</v>
       </c>
       <c r="D17">
-        <v>3578.47280113956</v>
+        <v>3587.473829514847</v>
       </c>
       <c r="E17">
         <v>-1254.785</v>
@@ -2687,37 +2794,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M17">
-        <v>36.40977234409868</v>
+        <v>35.23823934409869</v>
       </c>
       <c r="N17">
-        <v>216.7902276559012</v>
+        <v>217.9617606559012</v>
       </c>
       <c r="O17">
-        <v>45.52594780773926</v>
+        <v>45.77196973773925</v>
       </c>
       <c r="P17">
-        <v>171.264279848162</v>
+        <v>172.189790918162</v>
       </c>
       <c r="Q17">
-        <v>728.564279848162</v>
+        <v>729.4897909181619</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08181269618022186</v>
+        <v>0.0818005042540398</v>
       </c>
       <c r="T17">
         <v>0.6070202208254533</v>
       </c>
       <c r="U17">
-        <v>0.06837323332506819</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V17">
         <v>0.21</v>
       </c>
       <c r="W17">
-        <v>0.05401485432680387</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2832,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.954176961258554</v>
+        <v>7.185376020848302</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2843,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07765879501988948</v>
+        <v>0.07737037435304076</v>
       </c>
       <c r="C18">
-        <v>3044.615281112887</v>
+        <v>3054.212432914867</v>
       </c>
       <c r="D18">
-        <v>3577.931281112887</v>
+        <v>3587.528432914867</v>
       </c>
       <c r="E18">
         <v>-1219.284</v>
@@ -2769,37 +2876,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M18">
-        <v>38.83709050037193</v>
+        <v>37.58745530037193</v>
       </c>
       <c r="N18">
-        <v>214.362909499628</v>
+        <v>215.612544699628</v>
       </c>
       <c r="O18">
-        <v>45.01621099492188</v>
+        <v>45.27863438692188</v>
       </c>
       <c r="P18">
-        <v>169.3466985047061</v>
+        <v>170.3339103127061</v>
       </c>
       <c r="Q18">
-        <v>726.6466985047061</v>
+        <v>727.6339103127061</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08216240277095341</v>
+        <v>0.08215009245327635</v>
       </c>
       <c r="T18">
         <v>0.6129147800905429</v>
       </c>
       <c r="U18">
-        <v>0.06837323332506819</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V18">
         <v>0.21</v>
       </c>
       <c r="W18">
-        <v>0.05401485432680387</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2914,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.519540901179895</v>
+        <v>6.736290019545285</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2925,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.0776745701375698</v>
+        <v>0.07736879194112711</v>
       </c>
       <c r="C19">
-        <v>3008.572924954761</v>
+        <v>3018.766037977102</v>
       </c>
       <c r="D19">
-        <v>3577.389924954762</v>
+        <v>3587.583037977103</v>
       </c>
       <c r="E19">
         <v>-1183.783</v>
@@ -2851,37 +2958,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M19">
-        <v>41.26440865664518</v>
+        <v>39.93667125664518</v>
       </c>
       <c r="N19">
-        <v>211.9355913433548</v>
+        <v>213.2633287433547</v>
       </c>
       <c r="O19">
-        <v>44.5064741821045</v>
+        <v>44.7852990361045</v>
       </c>
       <c r="P19">
-        <v>167.4291171612502</v>
+        <v>168.4780297072502</v>
       </c>
       <c r="Q19">
-        <v>724.7291171612502</v>
+        <v>725.7780297072502</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08252053602652187</v>
+        <v>0.08250810446454272</v>
       </c>
       <c r="T19">
         <v>0.6189513769282855</v>
       </c>
       <c r="U19">
-        <v>0.06837323332506819</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V19">
         <v>0.21</v>
       </c>
       <c r="W19">
-        <v>0.05401485432680387</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2996,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.136038495228135</v>
+        <v>6.340037665454384</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +3007,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07788942525525014</v>
+        <v>0.07750940952921348</v>
       </c>
       <c r="C20">
-        <v>2965.714998548383</v>
+        <v>2978.419158558423</v>
       </c>
       <c r="D20">
-        <v>3570.032998548383</v>
+        <v>3582.737158558423</v>
       </c>
       <c r="E20">
         <v>-1148.282</v>
@@ -2933,37 +3040,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M20">
-        <v>44.58635201291842</v>
+        <v>42.92490521291842</v>
       </c>
       <c r="N20">
-        <v>208.6136479870815</v>
+        <v>210.2750947870815</v>
       </c>
       <c r="O20">
-        <v>43.80886607728712</v>
+        <v>44.15776990528712</v>
       </c>
       <c r="P20">
-        <v>164.8047819097944</v>
+        <v>166.1173248817944</v>
       </c>
       <c r="Q20">
-        <v>722.1047819097944</v>
+        <v>723.4173248817943</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08288740423954323</v>
+        <v>0.08287484847608387</v>
       </c>
       <c r="T20">
         <v>0.6251352078352411</v>
       </c>
       <c r="U20">
-        <v>0.06977323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V20">
         <v>0.21</v>
       </c>
       <c r="W20">
-        <v>0.05512085432680387</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +3078,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.678867827684982</v>
+        <v>5.898673479744771</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +3089,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07791626037293048</v>
+        <v>0.07751572711729984</v>
       </c>
       <c r="C21">
-        <v>2929.29725338445</v>
+        <v>2942.700752873417</v>
       </c>
       <c r="D21">
-        <v>3569.116253384451</v>
+        <v>3582.519752873417</v>
       </c>
       <c r="E21">
         <v>-1112.781</v>
@@ -3015,37 +3122,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M21">
-        <v>47.06337156919167</v>
+        <v>45.30962216919167</v>
       </c>
       <c r="N21">
-        <v>206.1366284308083</v>
+        <v>207.8903778308083</v>
       </c>
       <c r="O21">
-        <v>43.28869197046973</v>
+        <v>43.65697934446973</v>
       </c>
       <c r="P21">
-        <v>162.8479364603385</v>
+        <v>164.2333984863385</v>
       </c>
       <c r="Q21">
-        <v>720.1479364603385</v>
+        <v>721.5333984863385</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08326333092696017</v>
+        <v>0.0832506478953174</v>
       </c>
       <c r="T21">
         <v>0.6314717259250847</v>
       </c>
       <c r="U21">
-        <v>0.06977323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V21">
         <v>0.21</v>
       </c>
       <c r="W21">
-        <v>0.05512085432680387</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3160,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.379980047280508</v>
+        <v>5.588216980810834</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3171,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07794309549061081</v>
+        <v>0.07752204470538619</v>
       </c>
       <c r="C22">
-        <v>2892.879978919776</v>
+        <v>2906.982373571794</v>
       </c>
       <c r="D22">
-        <v>3568.199978919777</v>
+        <v>3582.302373571794</v>
       </c>
       <c r="E22">
         <v>-1077.28</v>
@@ -3097,37 +3204,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M22">
-        <v>49.54039112546491</v>
+        <v>47.69433912546491</v>
       </c>
       <c r="N22">
-        <v>203.659608874535</v>
+        <v>205.505660874535</v>
       </c>
       <c r="O22">
-        <v>42.76851786365236</v>
+        <v>43.15618878365235</v>
       </c>
       <c r="P22">
-        <v>160.8910910108827</v>
+        <v>162.3494720908827</v>
       </c>
       <c r="Q22">
-        <v>718.1910910108826</v>
+        <v>719.6494720908827</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08364865578156254</v>
+        <v>0.08363584230003177</v>
       </c>
       <c r="T22">
         <v>0.6379666569671743</v>
       </c>
       <c r="U22">
-        <v>0.06977323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V22">
         <v>0.21</v>
       </c>
       <c r="W22">
-        <v>0.05512085432680387</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3242,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.110981044916483</v>
+        <v>5.308806131770293</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3253,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07796993060829113</v>
+        <v>0.07752836229347254</v>
       </c>
       <c r="C23">
-        <v>2856.463174791934</v>
+        <v>2871.264020648753</v>
       </c>
       <c r="D23">
-        <v>3567.284174791934</v>
+        <v>3582.085020648753</v>
       </c>
       <c r="E23">
         <v>-1041.779</v>
@@ -3179,37 +3286,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M23">
-        <v>52.01741068173816</v>
+        <v>50.07905608173816</v>
       </c>
       <c r="N23">
-        <v>201.1825893182618</v>
+        <v>203.1209439182618</v>
       </c>
       <c r="O23">
-        <v>42.24834375683497</v>
+        <v>42.65539822283498</v>
       </c>
       <c r="P23">
-        <v>158.9342455614268</v>
+        <v>160.4655456954268</v>
       </c>
       <c r="Q23">
-        <v>716.2342455614267</v>
+        <v>717.7655456954268</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08404373569577508</v>
+        <v>0.08403078846182749</v>
       </c>
       <c r="T23">
         <v>0.6446260166432407</v>
       </c>
       <c r="U23">
-        <v>0.06977323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V23">
         <v>0.21</v>
       </c>
       <c r="W23">
-        <v>0.05512085432680387</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3324,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.867600995158556</v>
+        <v>5.056005839781232</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3335,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07799676572597146</v>
+        <v>0.07753467988155888</v>
       </c>
       <c r="C24">
-        <v>2820.04684063887</v>
+        <v>2835.545694099491</v>
       </c>
       <c r="D24">
-        <v>3566.36884063887</v>
+        <v>3581.867694099491</v>
       </c>
       <c r="E24">
         <v>-1006.278</v>
@@ -3261,37 +3368,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M24">
-        <v>54.4944302380114</v>
+        <v>52.4637730380114</v>
       </c>
       <c r="N24">
-        <v>198.7055697619885</v>
+        <v>200.7362269619885</v>
       </c>
       <c r="O24">
-        <v>41.72816965001759</v>
+        <v>42.15460766201759</v>
       </c>
       <c r="P24">
-        <v>156.977400111971</v>
+        <v>158.581619299971</v>
       </c>
       <c r="Q24">
-        <v>714.2774001119709</v>
+        <v>715.8816192999709</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08444894586419821</v>
+        <v>0.08443586144828466</v>
       </c>
       <c r="T24">
         <v>0.6514561291315141</v>
       </c>
       <c r="U24">
-        <v>0.06977323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V24">
         <v>0.21</v>
       </c>
       <c r="W24">
-        <v>0.05512085432680387</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3406,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.646346404469531</v>
+        <v>4.826187392518449</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3417,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.0784960208436518</v>
+        <v>0.07754099746964524</v>
       </c>
       <c r="C25">
-        <v>2767.601723266666</v>
+        <v>2799.827393919209</v>
       </c>
       <c r="D25">
-        <v>3549.424723266666</v>
+        <v>3581.65039391921</v>
       </c>
       <c r="E25">
         <v>-970.7769999999999</v>
@@ -3343,45 +3450,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M25">
-        <v>59.09440959428464</v>
+        <v>54.84848999428466</v>
       </c>
       <c r="N25">
-        <v>194.1055904057153</v>
+        <v>198.3515100057153</v>
       </c>
       <c r="O25">
-        <v>40.76217398520021</v>
+        <v>41.65381710120021</v>
       </c>
       <c r="P25">
-        <v>153.3434164205151</v>
+        <v>156.6976929045151</v>
       </c>
       <c r="Q25">
-        <v>710.643416420515</v>
+        <v>713.997692904515</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08486468097206092</v>
+        <v>0.08485145581101344</v>
       </c>
       <c r="T25">
         <v>0.6584636471389634</v>
       </c>
       <c r="U25">
-        <v>0.07237323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V25">
         <v>0.21</v>
       </c>
       <c r="W25">
-        <v>0.05717485432680386</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.284669256167479</v>
+        <v>4.616353158061124</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3499,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07854339596133213</v>
+        <v>0.07802131505773159</v>
       </c>
       <c r="C26">
-        <v>2730.501228996935</v>
+        <v>2747.882207767366</v>
       </c>
       <c r="D26">
-        <v>3547.825228996935</v>
+        <v>3565.206207767366</v>
       </c>
       <c r="E26">
         <v>-935.276</v>
@@ -3425,37 +3532,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M26">
-        <v>61.66373175055789</v>
+        <v>59.36326695055789</v>
       </c>
       <c r="N26">
-        <v>191.5362682494421</v>
+        <v>193.836733049442</v>
       </c>
       <c r="O26">
-        <v>40.22261633238283</v>
+        <v>40.70571394038283</v>
       </c>
       <c r="P26">
-        <v>151.3136519170592</v>
+        <v>153.1310191090592</v>
       </c>
       <c r="Q26">
-        <v>708.6136519170592</v>
+        <v>710.4310191090592</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08529135647749894</v>
+        <v>0.08527798686749824</v>
       </c>
       <c r="T26">
         <v>0.6656555735150298</v>
       </c>
       <c r="U26">
-        <v>0.07237323332506818</v>
+        <v>0.06967323332506818</v>
       </c>
       <c r="V26">
         <v>0.21</v>
       </c>
       <c r="W26">
-        <v>0.05717485432680386</v>
+        <v>0.05504185432680386</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3570,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.106141370493835</v>
+        <v>4.265263908249585</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3581,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07912402107901245</v>
+        <v>0.07804738264581795</v>
       </c>
       <c r="C27">
-        <v>2675.513431536177</v>
+        <v>2711.493074771136</v>
       </c>
       <c r="D27">
-        <v>3528.338431536177</v>
+        <v>3564.318074771136</v>
       </c>
       <c r="E27">
         <v>-899.775</v>
@@ -3507,45 +3614,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M27">
-        <v>66.62937140683114</v>
+        <v>61.83673640683114</v>
       </c>
       <c r="N27">
-        <v>186.5706285931688</v>
+        <v>191.3632635931688</v>
       </c>
       <c r="O27">
-        <v>39.17983200456545</v>
+        <v>40.18628535456545</v>
       </c>
       <c r="P27">
-        <v>147.3907965886034</v>
+        <v>151.1769782386033</v>
       </c>
       <c r="Q27">
-        <v>704.6907965886033</v>
+        <v>708.4769782386034</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08572940999641532</v>
+        <v>0.08571589208548931</v>
       </c>
       <c r="T27">
         <v>0.6730392845944579</v>
       </c>
       <c r="U27">
-        <v>0.07507323332506818</v>
+        <v>0.06967323332506818</v>
       </c>
       <c r="V27">
         <v>0.21</v>
       </c>
       <c r="W27">
-        <v>0.05930785432680387</v>
+        <v>0.05504185432680386</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.800125900242858</v>
+        <v>4.094653351919601</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3663,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07919272619669278</v>
+        <v>0.0787923502339043</v>
       </c>
       <c r="C28">
-        <v>2637.720721932852</v>
+        <v>2650.796430606559</v>
       </c>
       <c r="D28">
-        <v>3526.046721932852</v>
+        <v>3539.122430606559</v>
       </c>
       <c r="E28">
         <v>-864.274</v>
@@ -3589,37 +3696,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M28">
-        <v>69.29454626310438</v>
+        <v>67.54079686310439</v>
       </c>
       <c r="N28">
-        <v>183.9054537368955</v>
+        <v>185.6592031368955</v>
       </c>
       <c r="O28">
-        <v>38.62014528474806</v>
+        <v>38.98843265874806</v>
       </c>
       <c r="P28">
-        <v>145.2853084521475</v>
+        <v>146.6707704781475</v>
       </c>
       <c r="Q28">
-        <v>702.5853084521475</v>
+        <v>703.9707704781474</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08617930279962673</v>
+        <v>0.0861656325796423</v>
       </c>
       <c r="T28">
         <v>0.6806225554327896</v>
       </c>
       <c r="U28">
-        <v>0.07507323332506818</v>
+        <v>0.07317323332506818</v>
       </c>
       <c r="V28">
         <v>0.21</v>
       </c>
       <c r="W28">
-        <v>0.05930785432680387</v>
+        <v>0.05780685432680387</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3734,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.653967211771979</v>
+        <v>3.748845316604724</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3745,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07926143131437312</v>
+        <v>0.07884606782199066</v>
       </c>
       <c r="C29">
-        <v>2599.930987397825</v>
+        <v>2613.492402834231</v>
       </c>
       <c r="D29">
-        <v>3523.757987397826</v>
+        <v>3537.319402834231</v>
       </c>
       <c r="E29">
         <v>-828.7729999999999</v>
@@ -3671,37 +3778,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M29">
-        <v>71.95972111937763</v>
+        <v>70.13851981937763</v>
       </c>
       <c r="N29">
-        <v>181.2402788806223</v>
+        <v>183.0614801806223</v>
       </c>
       <c r="O29">
-        <v>38.06045856493068</v>
+        <v>38.44291083793068</v>
       </c>
       <c r="P29">
-        <v>143.1798203156916</v>
+        <v>144.6185693426916</v>
       </c>
       <c r="Q29">
-        <v>700.4798203156915</v>
+        <v>701.9185693426916</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08664152143306311</v>
+        <v>0.08662769473116935</v>
       </c>
       <c r="T29">
         <v>0.6884135871160071</v>
       </c>
       <c r="U29">
-        <v>0.07507323332506818</v>
+        <v>0.07317323332506818</v>
       </c>
       <c r="V29">
         <v>0.21</v>
       </c>
       <c r="W29">
-        <v>0.05930785432680387</v>
+        <v>0.05780685432680387</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3816,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.518635092817461</v>
+        <v>3.609999193767512</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3827,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08036977643205344</v>
+        <v>0.07951914541007701</v>
       </c>
       <c r="C30">
-        <v>2527.914638797658</v>
+        <v>2555.554327562993</v>
       </c>
       <c r="D30">
-        <v>3487.242638797658</v>
+        <v>3514.882327562993</v>
       </c>
       <c r="E30">
         <v>-793.2719999999999</v>
@@ -3753,37 +3860,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M30">
-        <v>79.29682757565089</v>
+        <v>75.51952117565088</v>
       </c>
       <c r="N30">
-        <v>173.903172424349</v>
+        <v>177.6804788243491</v>
       </c>
       <c r="O30">
-        <v>36.5196662091133</v>
+        <v>37.3129005531133</v>
       </c>
       <c r="P30">
-        <v>137.3835062152357</v>
+        <v>140.3675782712357</v>
       </c>
       <c r="Q30">
-        <v>694.6835062152356</v>
+        <v>697.6675782712357</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08711657947298383</v>
+        <v>0.08710259194246102</v>
       </c>
       <c r="T30">
         <v>0.6964210363459805</v>
       </c>
       <c r="U30">
-        <v>0.07977323332506819</v>
+        <v>0.07597323332506818</v>
       </c>
       <c r="V30">
         <v>0.21</v>
       </c>
       <c r="W30">
-        <v>0.06302085432680388</v>
+        <v>0.06001885432680387</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3898,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.193065949056305</v>
+        <v>3.352775495107841</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3909,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08047561154973376</v>
+        <v>0.07959498299816337</v>
       </c>
       <c r="C31">
-        <v>2488.966356904225</v>
+        <v>2517.54310706958</v>
       </c>
       <c r="D31">
-        <v>3483.795356904225</v>
+        <v>3512.372107069581</v>
       </c>
       <c r="E31">
         <v>-757.771</v>
@@ -3835,37 +3942,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M31">
-        <v>82.12885713192414</v>
+        <v>78.21664693192412</v>
       </c>
       <c r="N31">
-        <v>171.0711428680758</v>
+        <v>174.9833530680758</v>
       </c>
       <c r="O31">
-        <v>35.92494000229592</v>
+        <v>36.74650414429592</v>
       </c>
       <c r="P31">
-        <v>135.1462028657799</v>
+        <v>138.2368489237799</v>
       </c>
       <c r="Q31">
-        <v>692.4462028657798</v>
+        <v>695.5368489237799</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08760501942952204</v>
+        <v>0.08759086653998627</v>
       </c>
       <c r="T31">
         <v>0.7046540475260941</v>
       </c>
       <c r="U31">
-        <v>0.07977323332506819</v>
+        <v>0.07597323332506818</v>
       </c>
       <c r="V31">
         <v>0.21</v>
       </c>
       <c r="W31">
-        <v>0.06302085432680388</v>
+        <v>0.06001885432680387</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3980,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.082960226675054</v>
+        <v>3.237162547000674</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3991,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.0827855466674141</v>
+        <v>0.07967082058624972</v>
       </c>
       <c r="C32">
-        <v>2379.887572776208</v>
+        <v>2479.535469461409</v>
       </c>
       <c r="D32">
-        <v>3410.217572776208</v>
+        <v>3509.865469461409</v>
       </c>
       <c r="E32">
         <v>-722.27</v>
@@ -3917,45 +4024,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M32">
-        <v>94.86566568819737</v>
+        <v>80.91377268819737</v>
       </c>
       <c r="N32">
-        <v>158.3343343118026</v>
+        <v>172.2862273118026</v>
       </c>
       <c r="O32">
-        <v>33.25021020547854</v>
+        <v>36.18010773547854</v>
       </c>
       <c r="P32">
-        <v>125.084124106324</v>
+        <v>136.106119576324</v>
       </c>
       <c r="Q32">
-        <v>682.384124106324</v>
+        <v>693.406119576324</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08810741481338991</v>
+        <v>0.08809309184029795</v>
       </c>
       <c r="T32">
         <v>0.713122287597068</v>
       </c>
       <c r="U32">
-        <v>0.08907323332506818</v>
+        <v>0.07597323332506818</v>
       </c>
       <c r="V32">
         <v>0.21</v>
       </c>
       <c r="W32">
-        <v>0.07036785432680387</v>
+        <v>0.06001885432680387</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.669037297774442</v>
+        <v>3.129257128767318</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +4073,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08296485178509444</v>
+        <v>0.07974665817433607</v>
       </c>
       <c r="C33">
-        <v>2338.804986302534</v>
+        <v>2441.531407073071</v>
       </c>
       <c r="D33">
-        <v>3404.635986302534</v>
+        <v>3507.362407073071</v>
       </c>
       <c r="E33">
         <v>-686.769</v>
@@ -3999,45 +4106,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M33">
-        <v>98.02785454447061</v>
+        <v>83.61089844447061</v>
       </c>
       <c r="N33">
-        <v>155.1721454555293</v>
+        <v>169.5891015555293</v>
       </c>
       <c r="O33">
-        <v>32.58615054566116</v>
+        <v>35.61371132666116</v>
       </c>
       <c r="P33">
-        <v>122.5859949098682</v>
+        <v>133.9753902288682</v>
       </c>
       <c r="Q33">
-        <v>679.8859949098681</v>
+        <v>691.2753902288681</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08862437238229745</v>
+        <v>0.08860987439569114</v>
       </c>
       <c r="T33">
         <v>0.7218359839019833</v>
       </c>
       <c r="U33">
-        <v>0.08907323332506818</v>
+        <v>0.07597323332506818</v>
       </c>
       <c r="V33">
         <v>0.21</v>
       </c>
       <c r="W33">
-        <v>0.07036785432680387</v>
+        <v>0.06001885432680387</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.582939320426879</v>
+        <v>3.028313350419986</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4155,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08314415690277475</v>
+        <v>0.08179433576242244</v>
       </c>
       <c r="C34">
-        <v>2297.740641011148</v>
+        <v>2339.769743319551</v>
       </c>
       <c r="D34">
-        <v>3399.072641011148</v>
+        <v>3441.101743319551</v>
       </c>
       <c r="E34">
         <v>-651.268</v>
@@ -4081,37 +4188,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M34">
-        <v>101.1900434007438</v>
+        <v>95.16907380074387</v>
       </c>
       <c r="N34">
-        <v>152.0099565992561</v>
+        <v>158.030926199256</v>
       </c>
       <c r="O34">
-        <v>31.92209088584378</v>
+        <v>33.18649450184377</v>
       </c>
       <c r="P34">
-        <v>120.0878657134123</v>
+        <v>124.8444316974123</v>
       </c>
       <c r="Q34">
-        <v>677.3878657134123</v>
+        <v>682.1444316974122</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08915653458558459</v>
+        <v>0.08914185643800765</v>
       </c>
       <c r="T34">
         <v>0.7308059653923371</v>
       </c>
       <c r="U34">
-        <v>0.08907323332506818</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V34">
         <v>0.21</v>
       </c>
       <c r="W34">
-        <v>0.07036785432680387</v>
+        <v>0.06618085432680387</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4226,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.50222246666354</v>
+        <v>2.660528151509874</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4237,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08454875202045509</v>
+        <v>0.08193179335050879</v>
       </c>
       <c r="C35">
-        <v>2219.280026278648</v>
+        <v>2299.910320308845</v>
       </c>
       <c r="D35">
-        <v>3356.113026278648</v>
+        <v>3436.743320308845</v>
       </c>
       <c r="E35">
         <v>-615.7669999999998</v>
@@ -4163,45 +4270,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M35">
-        <v>109.8584373570171</v>
+        <v>98.14310735701713</v>
       </c>
       <c r="N35">
-        <v>143.3415626429828</v>
+        <v>155.0568926429828</v>
       </c>
       <c r="O35">
-        <v>30.10172815502639</v>
+        <v>32.56194745502638</v>
       </c>
       <c r="P35">
-        <v>113.2398344879564</v>
+        <v>122.4949451879564</v>
       </c>
       <c r="Q35">
-        <v>670.5398344879563</v>
+        <v>679.7949451879564</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08970458222777584</v>
+        <v>0.08968971854128882</v>
       </c>
       <c r="T35">
         <v>0.7400437075241941</v>
       </c>
       <c r="U35">
-        <v>0.09377323332506818</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V35">
         <v>0.21</v>
       </c>
       <c r="W35">
-        <v>0.07408085432680386</v>
+        <v>0.06618085432680387</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.304784285044511</v>
+        <v>2.579906086312605</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4319,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08476518713813541</v>
+        <v>0.08206925093859514</v>
       </c>
       <c r="C36">
-        <v>2177.255714732647</v>
+        <v>2260.061923895588</v>
       </c>
       <c r="D36">
-        <v>3349.589714732647</v>
+        <v>3432.395923895589</v>
       </c>
       <c r="E36">
         <v>-580.2659999999998</v>
@@ -4245,45 +4352,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M36">
-        <v>113.1874809132904</v>
+        <v>101.1171409132904</v>
       </c>
       <c r="N36">
-        <v>140.0125190867096</v>
+        <v>152.0828590867096</v>
       </c>
       <c r="O36">
-        <v>29.40262900820901</v>
+        <v>31.93740040820901</v>
       </c>
       <c r="P36">
-        <v>110.6098900785006</v>
+        <v>120.1454586785005</v>
       </c>
       <c r="Q36">
-        <v>667.9098900785006</v>
+        <v>677.4454586785005</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09026923737427592</v>
+        <v>0.09025418252648762</v>
       </c>
       <c r="T36">
         <v>0.7495613812358045</v>
       </c>
       <c r="U36">
-        <v>0.09377323332506818</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V36">
         <v>0.21</v>
       </c>
       <c r="W36">
-        <v>0.07408085432680386</v>
+        <v>0.06618085432680387</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.236996511954967</v>
+        <v>2.504026495538705</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4401,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08498162225581575</v>
+        <v>0.0832850585266815</v>
       </c>
       <c r="C37">
-        <v>2135.256712848025</v>
+        <v>2186.581929564155</v>
       </c>
       <c r="D37">
-        <v>3343.091712848026</v>
+        <v>3394.416929564155</v>
       </c>
       <c r="E37">
         <v>-544.7649999999999</v>
@@ -4327,37 +4434,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M37">
-        <v>116.5165244695636</v>
+        <v>108.9370609695636</v>
       </c>
       <c r="N37">
-        <v>136.6834755304363</v>
+        <v>144.2629390304363</v>
       </c>
       <c r="O37">
-        <v>28.70352986139163</v>
+        <v>30.29521719639163</v>
       </c>
       <c r="P37">
-        <v>107.9799456690447</v>
+        <v>113.9677218340447</v>
       </c>
       <c r="Q37">
-        <v>665.2799456690447</v>
+        <v>671.2677218340447</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09085126652528369</v>
+        <v>0.09083601463430792</v>
       </c>
       <c r="T37">
         <v>0.7593719064462334</v>
       </c>
       <c r="U37">
-        <v>0.09377323332506818</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V37">
         <v>0.21</v>
       </c>
       <c r="W37">
-        <v>0.07408085432680386</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4472,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.173082325899111</v>
+        <v>2.324277869684244</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4483,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08519805737349607</v>
+        <v>0.08345332611476786</v>
       </c>
       <c r="C38">
-        <v>2093.282873612332</v>
+        <v>2145.890750652767</v>
       </c>
       <c r="D38">
-        <v>3336.618873612332</v>
+        <v>3389.226750652766</v>
       </c>
       <c r="E38">
         <v>-509.2640000000001</v>
@@ -4409,37 +4516,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M38">
-        <v>119.8455680258368</v>
+        <v>112.0495484258368</v>
       </c>
       <c r="N38">
-        <v>133.3544319741631</v>
+        <v>141.1504515741631</v>
       </c>
       <c r="O38">
-        <v>28.00443071457425</v>
+        <v>29.64159483057425</v>
       </c>
       <c r="P38">
-        <v>105.3500012595889</v>
+        <v>111.5088567435889</v>
       </c>
       <c r="Q38">
-        <v>662.6500012595889</v>
+        <v>668.8088567435888</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09145148408726045</v>
+        <v>0.0914360289954976</v>
       </c>
       <c r="T38">
         <v>0.7694890105694884</v>
       </c>
       <c r="U38">
-        <v>0.09377323332506818</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V38">
         <v>0.21</v>
       </c>
       <c r="W38">
-        <v>0.07408085432680386</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4554,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.112718927957469</v>
+        <v>2.259714595526349</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4565,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08541449249117641</v>
+        <v>0.0836215937028542</v>
       </c>
       <c r="C39">
-        <v>2051.334051149488</v>
+        <v>2105.215419429815</v>
       </c>
       <c r="D39">
-        <v>3330.171051149488</v>
+        <v>3384.052419429815</v>
       </c>
       <c r="E39">
         <v>-473.7629999999999</v>
@@ -4491,37 +4598,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M39">
-        <v>123.1746115821101</v>
+        <v>115.1620358821101</v>
       </c>
       <c r="N39">
-        <v>130.0253884178898</v>
+        <v>138.0379641178898</v>
       </c>
       <c r="O39">
-        <v>27.30533156775687</v>
+        <v>28.98797246475686</v>
       </c>
       <c r="P39">
-        <v>102.720056850133</v>
+        <v>109.049991653133</v>
       </c>
       <c r="Q39">
-        <v>660.020056850133</v>
+        <v>666.349991653133</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09207075617501426</v>
+        <v>0.09205509143164567</v>
       </c>
       <c r="T39">
         <v>0.779927292601418</v>
       </c>
       <c r="U39">
-        <v>0.09377323332506818</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V39">
         <v>0.21</v>
       </c>
       <c r="W39">
-        <v>0.07408085432680386</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4636,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.055618416391051</v>
+        <v>2.198641228079691</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4647,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08563092760885674</v>
+        <v>0.08378986129094057</v>
       </c>
       <c r="C40">
-        <v>2009.410100708827</v>
+        <v>2064.555863421965</v>
       </c>
       <c r="D40">
-        <v>3323.748100708827</v>
+        <v>3378.893863421965</v>
       </c>
       <c r="E40">
         <v>-438.2619999999999</v>
@@ -4573,37 +4680,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M40">
-        <v>126.5036551383833</v>
+        <v>118.2745233383833</v>
       </c>
       <c r="N40">
-        <v>126.6963448616166</v>
+        <v>134.9254766616166</v>
       </c>
       <c r="O40">
-        <v>26.60623242093949</v>
+        <v>28.33435009893948</v>
       </c>
       <c r="P40">
-        <v>100.0901124406771</v>
+        <v>106.5911265626771</v>
       </c>
       <c r="Q40">
-        <v>657.3901124406771</v>
+        <v>663.8911265626771</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09271000478172786</v>
+        <v>0.09269412362379854</v>
       </c>
       <c r="T40">
         <v>0.7907022934085713</v>
       </c>
       <c r="U40">
-        <v>0.09377323332506818</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V40">
         <v>0.21</v>
       </c>
       <c r="W40">
-        <v>0.07408085432680386</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4718,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.001523194907076</v>
+        <v>2.140782248393383</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4729,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.09086939272653707</v>
+        <v>0.08395812887902691</v>
       </c>
       <c r="C41">
-        <v>1825.671652121509</v>
+        <v>2023.912010597116</v>
       </c>
       <c r="D41">
-        <v>3175.510652121509</v>
+        <v>3373.751010597116</v>
       </c>
       <c r="E41">
         <v>-402.761</v>
@@ -4655,45 +4762,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M41">
-        <v>152.4006843946566</v>
+        <v>121.3870107946566</v>
       </c>
       <c r="N41">
-        <v>100.7993156053433</v>
+        <v>131.8129892053433</v>
       </c>
       <c r="O41">
-        <v>21.1678562771221</v>
+        <v>27.6807277331221</v>
       </c>
       <c r="P41">
-        <v>79.63145932822124</v>
+        <v>104.1322614722212</v>
       </c>
       <c r="Q41">
-        <v>636.9314593282212</v>
+        <v>661.4322614722212</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09337021235915338</v>
+        <v>0.09335410769110394</v>
       </c>
       <c r="T41">
         <v>0.8018305729307131</v>
       </c>
       <c r="U41">
-        <v>0.1100732333250682</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V41">
         <v>0.21</v>
       </c>
       <c r="W41">
-        <v>0.08695785432680388</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.661409861810814</v>
+        <v>2.085890395870476</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4811,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.0912145978442174</v>
+        <v>0.08412639646711327</v>
       </c>
       <c r="C42">
-        <v>1780.865102209806</v>
+        <v>1983.283789361044</v>
       </c>
       <c r="D42">
-        <v>3166.205102209806</v>
+        <v>3368.623789361044</v>
       </c>
       <c r="E42">
         <v>-367.26</v>
@@ -4737,45 +4844,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M42">
-        <v>156.3083942509298</v>
+        <v>124.4994982509298</v>
       </c>
       <c r="N42">
-        <v>96.8916057490701</v>
+        <v>128.7005017490701</v>
       </c>
       <c r="O42">
-        <v>20.34723720730472</v>
+        <v>27.02710536730472</v>
       </c>
       <c r="P42">
-        <v>76.54436854176538</v>
+        <v>101.6733963817654</v>
       </c>
       <c r="Q42">
-        <v>633.8443685417653</v>
+        <v>658.9733963817653</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.09405242685582643</v>
+        <v>0.09403609122731954</v>
       </c>
       <c r="T42">
         <v>0.8133297951035932</v>
       </c>
       <c r="U42">
-        <v>0.1100732333250682</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V42">
         <v>0.21</v>
       </c>
       <c r="W42">
-        <v>0.08695785432680388</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.619874615265544</v>
+        <v>2.033743135973714</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4893,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09155980296189774</v>
+        <v>0.08889404405519963</v>
       </c>
       <c r="C43">
-        <v>1736.112931109102</v>
+        <v>1808.718384754376</v>
       </c>
       <c r="D43">
-        <v>3156.953931109103</v>
+        <v>3229.559384754376</v>
       </c>
       <c r="E43">
         <v>-331.7589999999998</v>
@@ -4819,37 +4926,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M43">
-        <v>160.2161041072031</v>
+        <v>148.2806679072031</v>
       </c>
       <c r="N43">
-        <v>92.98389589279685</v>
+        <v>104.9193320927969</v>
       </c>
       <c r="O43">
-        <v>19.52661813748734</v>
+        <v>22.03305973948734</v>
       </c>
       <c r="P43">
-        <v>73.45727775530952</v>
+        <v>82.88627235330951</v>
       </c>
       <c r="Q43">
-        <v>630.7572777553095</v>
+        <v>640.1862723533095</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.09475776726764093</v>
+        <v>0.09474119284950855</v>
       </c>
       <c r="T43">
         <v>0.8252188214179265</v>
       </c>
       <c r="U43">
-        <v>0.1100732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V43">
         <v>0.21</v>
       </c>
       <c r="W43">
-        <v>0.08695785432680388</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4964,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.580365478307848</v>
+        <v>1.707572562044685</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4975,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09190500807957806</v>
+        <v>0.08917449164328597</v>
       </c>
       <c r="C44">
-        <v>1691.414663548155</v>
+        <v>1765.393886906166</v>
       </c>
       <c r="D44">
-        <v>3147.756663548155</v>
+        <v>3221.735886906166</v>
       </c>
       <c r="E44">
         <v>-296.258</v>
@@ -4901,37 +5008,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M44">
-        <v>164.1238139634763</v>
+        <v>151.8972695634763</v>
       </c>
       <c r="N44">
-        <v>89.07618603652361</v>
+        <v>101.3027304365236</v>
       </c>
       <c r="O44">
-        <v>18.70599906766996</v>
+        <v>21.27357339166996</v>
       </c>
       <c r="P44">
-        <v>70.37018696885366</v>
+        <v>80.02915704485366</v>
       </c>
       <c r="Q44">
-        <v>627.6701869688536</v>
+        <v>637.3291570448537</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.09548742976262144</v>
+        <v>0.09547060832073853</v>
       </c>
       <c r="T44">
         <v>0.8375178141568921</v>
       </c>
       <c r="U44">
-        <v>0.1100732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V44">
         <v>0.21</v>
       </c>
       <c r="W44">
-        <v>0.08695785432680388</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +5046,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.542737728824328</v>
+        <v>1.666916072472193</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +5057,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.0922502131972584</v>
+        <v>0.08945493923137235</v>
       </c>
       <c r="C45">
-        <v>1646.769829778128</v>
+        <v>1722.107201773227</v>
       </c>
       <c r="D45">
-        <v>3138.612829778128</v>
+        <v>3213.950201773227</v>
       </c>
       <c r="E45">
         <v>-260.7570000000001</v>
@@ -4983,37 +5090,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M45">
-        <v>168.0315238197496</v>
+        <v>155.5138712197495</v>
       </c>
       <c r="N45">
-        <v>85.16847618025037</v>
+        <v>97.68612878025039</v>
       </c>
       <c r="O45">
-        <v>17.88537999785258</v>
+        <v>20.51408704385258</v>
       </c>
       <c r="P45">
-        <v>67.28309618239778</v>
+        <v>77.1720417363978</v>
       </c>
       <c r="Q45">
-        <v>624.5830961823978</v>
+        <v>634.4720417363977</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.09624269445040828</v>
+        <v>0.09622561731727486</v>
       </c>
       <c r="T45">
         <v>0.8502483505007338</v>
       </c>
       <c r="U45">
-        <v>0.1100732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V45">
         <v>0.21</v>
       </c>
       <c r="W45">
-        <v>0.08695785432680388</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5128,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.506860107223762</v>
+        <v>1.6281505824147</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5139,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1167872299203759</v>
+        <v>0.0897353868194587</v>
       </c>
       <c r="C46">
-        <v>1074.125238478384</v>
+        <v>1678.858055880474</v>
       </c>
       <c r="D46">
-        <v>2601.469238478384</v>
+        <v>3206.202055880474</v>
       </c>
       <c r="E46">
         <v>-225.2560000000001</v>
@@ -5065,45 +5172,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M46">
-        <v>274.0969112760228</v>
+        <v>159.1304728760228</v>
       </c>
       <c r="N46">
-        <v>-20.89691127602288</v>
+        <v>94.06952712397714</v>
       </c>
       <c r="O46">
-        <v>-4.388351367964804</v>
+        <v>19.7546006960352</v>
       </c>
       <c r="P46">
-        <v>-16.50855990805807</v>
+        <v>74.31492642794194</v>
       </c>
       <c r="Q46">
-        <v>540.7914400919419</v>
+        <v>631.6149264279419</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.09742252414635381</v>
+        <v>0.09700759092083033</v>
       </c>
       <c r="T46">
-        <v>0.8701352392520015</v>
+        <v>0.8634335488568556</v>
       </c>
       <c r="U46">
-        <v>0.1754732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V46">
-        <v>0.1939897817617302</v>
+        <v>0.21</v>
       </c>
       <c r="W46">
-        <v>0.141433219087313</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.9237608655320485</v>
+        <v>1.591147160087094</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5221,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1180839622536266</v>
+        <v>0.09001583440754506</v>
       </c>
       <c r="C47">
-        <v>1015.306327554016</v>
+        <v>1635.646178383638</v>
       </c>
       <c r="D47">
-        <v>2578.151327554016</v>
+        <v>3198.491178383639</v>
       </c>
       <c r="E47">
         <v>-189.7549999999999</v>
@@ -5147,45 +5254,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M47">
-        <v>280.3263865322961</v>
+        <v>162.7470745322961</v>
       </c>
       <c r="N47">
-        <v>-27.12638653229618</v>
+        <v>90.45292546770386</v>
       </c>
       <c r="O47">
-        <v>-5.696541171782198</v>
+        <v>18.99511434821781</v>
       </c>
       <c r="P47">
-        <v>-21.42984536051398</v>
+        <v>71.45781111948605</v>
       </c>
       <c r="Q47">
-        <v>535.8701546394859</v>
+        <v>628.757811119486</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.09836111549446934</v>
+        <v>0.09781799992815146</v>
       </c>
       <c r="T47">
-        <v>0.8859558799656744</v>
+        <v>0.8770982089713818</v>
       </c>
       <c r="U47">
-        <v>0.1754732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V47">
-        <v>0.1896788977225806</v>
+        <v>0.21</v>
       </c>
       <c r="W47">
-        <v>0.1421896638481521</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.9032328462980028</v>
+        <v>1.55578833430738</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5303,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1193806945868773</v>
+        <v>0.09029628199563142</v>
       </c>
       <c r="C48">
-        <v>956.9017168672879</v>
+        <v>1592.471301037713</v>
       </c>
       <c r="D48">
-        <v>2555.247716867288</v>
+        <v>3190.817301037713</v>
       </c>
       <c r="E48">
         <v>-154.2539999999999</v>
@@ -5229,45 +5336,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M48">
-        <v>286.5558617885694</v>
+        <v>166.3636761885693</v>
       </c>
       <c r="N48">
-        <v>-33.35586178856943</v>
+        <v>86.83632381143062</v>
       </c>
       <c r="O48">
-        <v>-7.004730975599579</v>
+        <v>18.23562800040043</v>
       </c>
       <c r="P48">
-        <v>-26.35113081296985</v>
+        <v>68.60069581103019</v>
       </c>
       <c r="Q48">
-        <v>530.9488691870301</v>
+        <v>625.9006958110301</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.09933446948510766</v>
+        <v>0.09865842408389189</v>
       </c>
       <c r="T48">
-        <v>0.902362470335409</v>
+        <v>0.891268967608668</v>
       </c>
       <c r="U48">
-        <v>0.1754732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V48">
-        <v>0.1855554434242636</v>
+        <v>0.21</v>
       </c>
       <c r="W48">
-        <v>0.1429132197063459</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.8835973496393505</v>
+        <v>1.521966848778959</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5385,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.120677426920128</v>
+        <v>0.1124861013157825</v>
       </c>
       <c r="C49">
-        <v>898.900462045734</v>
+        <v>1047.888379719555</v>
       </c>
       <c r="D49">
-        <v>2532.747462045734</v>
+        <v>2681.735379719555</v>
       </c>
       <c r="E49">
         <v>-118.7529999999999</v>
@@ -5311,37 +5418,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M49">
-        <v>292.7853370448425</v>
+        <v>264.7537474448425</v>
       </c>
       <c r="N49">
-        <v>-39.58533704484262</v>
+        <v>-11.5537474448426</v>
       </c>
       <c r="O49">
-        <v>-8.312920779416949</v>
+        <v>-2.426286963416946</v>
       </c>
       <c r="P49">
-        <v>-31.27241626542567</v>
+        <v>-9.127460481425654</v>
       </c>
       <c r="Q49">
-        <v>526.0275837345743</v>
+        <v>548.1725395185744</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1003445538150153</v>
+        <v>0.09978733569360888</v>
       </c>
       <c r="T49">
-        <v>0.9193881773228696</v>
+        <v>0.9103040391673096</v>
       </c>
       <c r="U49">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V49">
-        <v>0.1816074552663006</v>
+        <v>0.2008356841524125</v>
       </c>
       <c r="W49">
-        <v>0.1436059859535528</v>
+        <v>0.1268059859535527</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5456,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8647974060300028</v>
+        <v>0.9563604007257739</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5467,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1219741592533786</v>
+        <v>0.1136148336490332</v>
       </c>
       <c r="C50">
-        <v>841.2920008351887</v>
+        <v>990.7985796711421</v>
       </c>
       <c r="D50">
-        <v>2510.640000835189</v>
+        <v>2660.146579671142</v>
       </c>
       <c r="E50">
         <v>-83.25199999999995</v>
@@ -5393,37 +5500,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M50">
-        <v>299.0148123011158</v>
+        <v>270.3868059011158</v>
       </c>
       <c r="N50">
-        <v>-45.81481230111586</v>
+        <v>-17.18680590111586</v>
       </c>
       <c r="O50">
-        <v>-9.621110583234332</v>
+        <v>-3.609229239234331</v>
       </c>
       <c r="P50">
-        <v>-36.19370171788153</v>
+        <v>-13.57757666188153</v>
       </c>
       <c r="Q50">
-        <v>521.1062982821185</v>
+        <v>543.7224233381185</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1013934875422272</v>
+        <v>0.1008255536877167</v>
       </c>
       <c r="T50">
-        <v>0.9370687191944632</v>
+        <v>0.9278098860743732</v>
       </c>
       <c r="U50">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V50">
-        <v>0.1778239666149193</v>
+        <v>0.1966516073992372</v>
       </c>
       <c r="W50">
-        <v>0.1442698869404593</v>
+        <v>0.1274698869404593</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5538,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8467807934043777</v>
+        <v>0.9364362257106535</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5549,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1232708915866293</v>
+        <v>0.1147435659822839</v>
       </c>
       <c r="C51">
-        <v>784.0661365672154</v>
+        <v>934.053596785996</v>
       </c>
       <c r="D51">
-        <v>2488.915136567216</v>
+        <v>2638.902596785996</v>
       </c>
       <c r="E51">
         <v>-47.75099999999998</v>
@@ -5475,37 +5582,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M51">
-        <v>305.244287557389</v>
+        <v>276.0198643573891</v>
       </c>
       <c r="N51">
-        <v>-52.04428755738911</v>
+        <v>-22.81986435738912</v>
       </c>
       <c r="O51">
-        <v>-10.92930038705171</v>
+        <v>-4.792171515051716</v>
       </c>
       <c r="P51">
-        <v>-41.1149871703374</v>
+        <v>-18.02769284233741</v>
       </c>
       <c r="Q51">
-        <v>516.1850128296626</v>
+        <v>539.2723071576626</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1024835559254081</v>
+        <v>0.1019044861129661</v>
       </c>
       <c r="T51">
-        <v>0.9554426156492565</v>
+        <v>0.9460022367817138</v>
       </c>
       <c r="U51">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V51">
-        <v>0.1741949060717577</v>
+        <v>0.1926383092890487</v>
       </c>
       <c r="W51">
-        <v>0.1449066899279003</v>
+        <v>0.1281066899279003</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5620,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8294995527226557</v>
+        <v>0.9173252823288034</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5631,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.12456762391988</v>
+        <v>0.1158722983155345</v>
       </c>
       <c r="C52">
-        <v>727.2130224775162</v>
+        <v>877.645235365196</v>
       </c>
       <c r="D52">
-        <v>2467.563022477516</v>
+        <v>2617.995235365196</v>
       </c>
       <c r="E52">
         <v>-12.25</v>
@@ -5557,37 +5664,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M52">
-        <v>311.4737628136623</v>
+        <v>281.6529228136623</v>
       </c>
       <c r="N52">
-        <v>-58.27376281366236</v>
+        <v>-28.45292281366233</v>
       </c>
       <c r="O52">
-        <v>-12.23749019086909</v>
+        <v>-5.975113790869088</v>
       </c>
       <c r="P52">
-        <v>-46.03627262279326</v>
+        <v>-22.47780902279324</v>
       </c>
       <c r="Q52">
-        <v>511.2637273772067</v>
+        <v>534.8221909772067</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1036172270439163</v>
+        <v>0.1030265758352254</v>
       </c>
       <c r="T52">
-        <v>0.9745514679622418</v>
+        <v>0.964922281517348</v>
       </c>
       <c r="U52">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V52">
-        <v>0.1707110079503225</v>
+        <v>0.1887855431032678</v>
       </c>
       <c r="W52">
-        <v>0.1455180207958437</v>
+        <v>0.1287180207958437</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5702,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8129095616682027</v>
+        <v>0.8989787766822275</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5713,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1531048922744659</v>
+        <v>0.1170010306487852</v>
       </c>
       <c r="C53">
-        <v>299.8314262286567</v>
+        <v>821.5655573980616</v>
       </c>
       <c r="D53">
-        <v>2075.682426228657</v>
+        <v>2597.416557398062</v>
       </c>
       <c r="E53">
         <v>23.25099999999998</v>
@@ -5639,45 +5746,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M53">
-        <v>412.2140002699355</v>
+        <v>287.2859812699355</v>
       </c>
       <c r="N53">
-        <v>-159.0140002699356</v>
+        <v>-34.08598126993559</v>
       </c>
       <c r="O53">
-        <v>-33.39294005668647</v>
+        <v>-7.158056066686473</v>
       </c>
       <c r="P53">
-        <v>-125.6210602132491</v>
+        <v>-26.92792520324911</v>
       </c>
       <c r="Q53">
-        <v>431.6789397867508</v>
+        <v>530.3720747967509</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1060594888638639</v>
+        <v>0.1041944651379851</v>
       </c>
       <c r="T53">
-        <v>1.015717569545949</v>
+        <v>0.9846145729768859</v>
       </c>
       <c r="U53">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V53">
-        <v>0.12899125203215</v>
+        <v>0.1850838657875174</v>
       </c>
       <c r="W53">
-        <v>0.1983053779042599</v>
+        <v>0.1293053779042598</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.6142440572959522</v>
+        <v>0.8813517418453209</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5795,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1549236246077165</v>
+        <v>0.1181297629820359</v>
       </c>
       <c r="C54">
-        <v>243.5320601333817</v>
+        <v>765.8068725133915</v>
       </c>
       <c r="D54">
-        <v>2054.884060133382</v>
+        <v>2577.158872513392</v>
       </c>
       <c r="E54">
         <v>58.75199999999995</v>
@@ -5721,45 +5828,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M54">
-        <v>420.2966277262088</v>
+        <v>292.9190397262088</v>
       </c>
       <c r="N54">
-        <v>-167.0966277262089</v>
+        <v>-39.71903972620885</v>
       </c>
       <c r="O54">
-        <v>-35.09029182250386</v>
+        <v>-8.340998342503857</v>
       </c>
       <c r="P54">
-        <v>-132.006335903705</v>
+        <v>-31.37804138370499</v>
       </c>
       <c r="Q54">
-        <v>425.2936640962949</v>
+        <v>525.921958616295</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1073148948818611</v>
+        <v>0.1054110164950265</v>
       </c>
       <c r="T54">
-        <v>1.036878352244823</v>
+        <v>1.005127376580571</v>
       </c>
       <c r="U54">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V54">
-        <v>0.1265106510315317</v>
+        <v>0.181524560676219</v>
       </c>
       <c r="W54">
-        <v>0.19887014435466</v>
+        <v>0.12987014435466</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.6024316715787223</v>
+        <v>0.8644026698867571</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5877,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1567423569409672</v>
+        <v>0.1192584953152866</v>
       </c>
       <c r="C55">
-        <v>187.6453589514379</v>
+        <v>710.3617283972842</v>
       </c>
       <c r="D55">
-        <v>2034.498358951438</v>
+        <v>2557.214728397284</v>
       </c>
       <c r="E55">
         <v>94.25300000000016</v>
@@ -5803,45 +5910,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M55">
-        <v>428.379255182482</v>
+        <v>298.552098182482</v>
       </c>
       <c r="N55">
-        <v>-175.1792551824821</v>
+        <v>-45.35209818248211</v>
       </c>
       <c r="O55">
-        <v>-36.78764358832124</v>
+        <v>-9.523940618321243</v>
       </c>
       <c r="P55">
-        <v>-138.3916115941609</v>
+        <v>-35.82815756416087</v>
       </c>
       <c r="Q55">
-        <v>418.9083884058391</v>
+        <v>521.4718424358391</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.108623722432539</v>
+        <v>0.1066793359949207</v>
       </c>
       <c r="T55">
-        <v>1.058939593781947</v>
+        <v>1.026513065443988</v>
       </c>
       <c r="U55">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V55">
-        <v>0.1241236576158424</v>
+        <v>0.1780995689653469</v>
       </c>
       <c r="W55">
-        <v>0.1994135988635356</v>
+        <v>0.1304135988635357</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.5910650362659162</v>
+        <v>0.848093185549271</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5959,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1585610892742179</v>
+        <v>0.1203872276485373</v>
       </c>
       <c r="C56">
-        <v>132.1591616658316</v>
+        <v>655.2229016524766</v>
       </c>
       <c r="D56">
-        <v>2014.513161665832</v>
+        <v>2537.576901652477</v>
       </c>
       <c r="E56">
         <v>129.7540000000001</v>
@@ -5885,45 +5992,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M56">
-        <v>436.4618826387553</v>
+        <v>304.1851566387553</v>
       </c>
       <c r="N56">
-        <v>-183.2618826387554</v>
+        <v>-50.98515663875537</v>
       </c>
       <c r="O56">
-        <v>-38.48499535413863</v>
+        <v>-10.70688289413863</v>
       </c>
       <c r="P56">
-        <v>-144.7768872846167</v>
+        <v>-40.27827374461674</v>
       </c>
       <c r="Q56">
-        <v>412.5231127153832</v>
+        <v>517.0217262553832</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1099894555288985</v>
+        <v>0.1080027998208972</v>
       </c>
       <c r="T56">
-        <v>1.081960019733728</v>
+        <v>1.048828566866683</v>
       </c>
       <c r="U56">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V56">
-        <v>0.1218250713636972</v>
+        <v>0.174801428799322</v>
       </c>
       <c r="W56">
-        <v>0.1999369254276381</v>
+        <v>0.1309369254276381</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.580119387446177</v>
+        <v>0.8323877561872475</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +6041,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1603798216074686</v>
+        <v>0.1215159599817879</v>
       </c>
       <c r="C57">
-        <v>77.06178044967805</v>
+        <v>600.3833890756375</v>
       </c>
       <c r="D57">
-        <v>1994.916780449678</v>
+        <v>2518.238389075638</v>
       </c>
       <c r="E57">
         <v>165.2550000000001</v>
@@ -5967,45 +6074,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M57">
-        <v>444.5445100950286</v>
+        <v>309.8182150950285</v>
       </c>
       <c r="N57">
-        <v>-191.3445100950286</v>
+        <v>-56.61821509502857</v>
       </c>
       <c r="O57">
-        <v>-40.18234711995601</v>
+        <v>-11.889825169956</v>
       </c>
       <c r="P57">
-        <v>-151.1621629750726</v>
+        <v>-44.72838992507258</v>
       </c>
       <c r="Q57">
-        <v>406.1378370249273</v>
+        <v>512.5716100749273</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1114158878739852</v>
+        <v>0.1093850842613616</v>
       </c>
       <c r="T57">
-        <v>1.106003575727811</v>
+        <v>1.072135868352609</v>
       </c>
       <c r="U57">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V57">
-        <v>0.1196100700661754</v>
+        <v>0.1716232210029707</v>
       </c>
       <c r="W57">
-        <v>0.2004412219348641</v>
+        <v>0.1314412219348641</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.5695717622198828</v>
+        <v>0.8172534333474795</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6123,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1621985539407192</v>
+        <v>0.1226446923150386</v>
       </c>
       <c r="C58">
-        <v>22.34197787289736</v>
+        <v>545.8363993304906</v>
       </c>
       <c r="D58">
-        <v>1975.697977872897</v>
+        <v>2499.192399330491</v>
       </c>
       <c r="E58">
         <v>200.7560000000001</v>
@@ -6049,45 +6156,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M58">
-        <v>452.6271375513018</v>
+        <v>315.4512735513018</v>
       </c>
       <c r="N58">
-        <v>-199.4271375513019</v>
+        <v>-62.25127355130184</v>
       </c>
       <c r="O58">
-        <v>-41.87969888577339</v>
+        <v>-13.07276744577339</v>
       </c>
       <c r="P58">
-        <v>-157.5474386655285</v>
+        <v>-49.17850610552845</v>
       </c>
       <c r="Q58">
-        <v>399.7525613344715</v>
+        <v>508.1214938944715</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1129071580529394</v>
+        <v>0.1108301998127562</v>
       </c>
       <c r="T58">
-        <v>1.131140020630716</v>
+        <v>1.09650259263335</v>
       </c>
       <c r="U58">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V58">
-        <v>0.1174741759578508</v>
+        <v>0.1685585206279176</v>
       </c>
       <c r="W58">
-        <v>0.2009275078525463</v>
+        <v>0.1319275078525463</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.5594008378945279</v>
+        <v>0.802659622037703</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6205,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1640172862739699</v>
+        <v>0.1553106890622852</v>
       </c>
       <c r="C59">
-        <v>-32.01105458612437</v>
+        <v>61.53896899954907</v>
       </c>
       <c r="D59">
-        <v>1956.845945413876</v>
+        <v>2050.395968999549</v>
       </c>
       <c r="E59">
         <v>236.2570000000003</v>
@@ -6131,37 +6238,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M59">
-        <v>460.7097650075751</v>
+        <v>430.3564100075751</v>
       </c>
       <c r="N59">
-        <v>-207.5097650075751</v>
+        <v>-177.1564100075751</v>
       </c>
       <c r="O59">
-        <v>-43.57705065159078</v>
+        <v>-37.20284610159077</v>
       </c>
       <c r="P59">
-        <v>-163.9327143559844</v>
+        <v>-139.9535639059843</v>
       </c>
       <c r="Q59">
-        <v>393.3672856440156</v>
+        <v>417.3464360940156</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1144677896355659</v>
+        <v>0.1141036100735082</v>
       </c>
       <c r="T59">
-        <v>1.157445602505849</v>
+        <v>1.151696992281545</v>
       </c>
       <c r="U59">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V59">
-        <v>0.11541322550245</v>
+        <v>0.1235534054182301</v>
       </c>
       <c r="W59">
-        <v>0.2013967311064502</v>
+        <v>0.1863967311064502</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6276,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5495867881069045</v>
+        <v>0.5883495496106197</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6287,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1658360186072206</v>
+        <v>0.1569794213955358</v>
       </c>
       <c r="C60">
-        <v>-86.00771681026004</v>
+        <v>7.39941048833407</v>
       </c>
       <c r="D60">
-        <v>1938.35028318974</v>
+        <v>2031.757410488334</v>
       </c>
       <c r="E60">
         <v>271.758</v>
@@ -6213,37 +6320,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M60">
-        <v>468.7923924638483</v>
+        <v>437.9065224638483</v>
       </c>
       <c r="N60">
-        <v>-215.5923924638483</v>
+        <v>-184.7065224638483</v>
       </c>
       <c r="O60">
-        <v>-45.27440241740815</v>
+        <v>-38.78836971740814</v>
       </c>
       <c r="P60">
-        <v>-170.3179900464402</v>
+        <v>-145.9181527464402</v>
       </c>
       <c r="Q60">
-        <v>386.9820099535598</v>
+        <v>411.3818472535598</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1161027370078412</v>
+        <v>0.1157298865038298</v>
       </c>
       <c r="T60">
-        <v>1.18500383113694</v>
+        <v>1.17911834924063</v>
       </c>
       <c r="U60">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V60">
-        <v>0.1134233423041318</v>
+        <v>0.1214231742903296</v>
       </c>
       <c r="W60">
-        <v>0.2018497742481505</v>
+        <v>0.1868497742481505</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6358,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5401111538291994</v>
+        <v>0.5782055918587123</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6369,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1676547509404713</v>
+        <v>0.1586481537287865</v>
       </c>
       <c r="C61">
-        <v>-139.6580191746261</v>
+        <v>-46.40434322237525</v>
       </c>
       <c r="D61">
-        <v>1920.200980825374</v>
+        <v>2013.454656777625</v>
       </c>
       <c r="E61">
         <v>307.2589999999998</v>
@@ -6295,37 +6402,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M61">
-        <v>476.8750199201215</v>
+        <v>445.4566349201214</v>
       </c>
       <c r="N61">
-        <v>-223.6750199201215</v>
+        <v>-192.2566349201215</v>
       </c>
       <c r="O61">
-        <v>-46.97175418322552</v>
+        <v>-40.37389333322551</v>
       </c>
       <c r="P61">
-        <v>-176.703265736896</v>
+        <v>-151.882741586896</v>
       </c>
       <c r="Q61">
-        <v>380.5967342631039</v>
+        <v>405.417258413104</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1178174379104715</v>
+        <v>0.1174354934917281</v>
       </c>
       <c r="T61">
-        <v>1.213906363603695</v>
+        <v>1.20787733336845</v>
       </c>
       <c r="U61">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V61">
-        <v>0.1115009127735534</v>
+        <v>0.1193651543871037</v>
       </c>
       <c r="W61">
-        <v>0.2022874599952169</v>
+        <v>0.1872874599952169</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6440,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5309567274931113</v>
+        <v>0.5684054970814463</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6451,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.169473483273722</v>
+        <v>0.1603168860620372</v>
       </c>
       <c r="C62">
-        <v>-192.971600612758</v>
+        <v>-99.88128623821308</v>
       </c>
       <c r="D62">
-        <v>1902.388399387242</v>
+        <v>1995.478713761787</v>
       </c>
       <c r="E62">
         <v>342.76</v>
@@ -6377,37 +6484,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M62">
-        <v>484.9576473763947</v>
+        <v>453.0067473763947</v>
       </c>
       <c r="N62">
-        <v>-231.7576473763948</v>
+        <v>-199.8067473763948</v>
       </c>
       <c r="O62">
-        <v>-48.66910594904291</v>
+        <v>-41.95941694904291</v>
       </c>
       <c r="P62">
-        <v>-183.0885414273519</v>
+        <v>-157.8473304273519</v>
       </c>
       <c r="Q62">
-        <v>374.2114585726481</v>
+        <v>399.4526695726481</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1196178738582333</v>
+        <v>0.1192263808290213</v>
       </c>
       <c r="T62">
-        <v>1.244254022693787</v>
+        <v>1.238074266702661</v>
       </c>
       <c r="U62">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V62">
-        <v>0.1096425642273275</v>
+        <v>0.1173757351473186</v>
       </c>
       <c r="W62">
-        <v>0.2027105562173811</v>
+        <v>0.1877105562173811</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6522,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5221074487015593</v>
+        <v>0.5589320721300887</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6533,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1712922156069727</v>
+        <v>0.1619856183952879</v>
       </c>
       <c r="C63">
-        <v>-245.957745686492</v>
+        <v>-153.0400943127522</v>
       </c>
       <c r="D63">
-        <v>1884.903254313508</v>
+        <v>1977.820905687247</v>
       </c>
       <c r="E63">
         <v>378.2609999999997</v>
@@ -6459,37 +6566,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M63">
-        <v>493.0402748326679</v>
+        <v>460.5568598326679</v>
       </c>
       <c r="N63">
-        <v>-239.840274832668</v>
+        <v>-207.356859832668</v>
       </c>
       <c r="O63">
-        <v>-50.36645771486028</v>
+        <v>-43.54494056486027</v>
       </c>
       <c r="P63">
-        <v>-189.4738171178077</v>
+        <v>-163.8119192678077</v>
       </c>
       <c r="Q63">
-        <v>367.8261828821923</v>
+        <v>393.4880807321923</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1215106398545983</v>
+        <v>0.121109108542586</v>
       </c>
       <c r="T63">
-        <v>1.276157971993628</v>
+        <v>1.269819760720678</v>
       </c>
       <c r="U63">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V63">
-        <v>0.1078451451416336</v>
+        <v>0.1154515427678544</v>
       </c>
       <c r="W63">
-        <v>0.2031197804322612</v>
+        <v>0.1881197804322612</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6604,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5135483101982552</v>
+        <v>0.5497692512754973</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6615,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1731109479402234</v>
+        <v>0.1636543507285385</v>
       </c>
       <c r="C64">
-        <v>-298.6254007230762</v>
+        <v>-205.8891388092977</v>
       </c>
       <c r="D64">
-        <v>1867.736599276924</v>
+        <v>1960.472861190702</v>
       </c>
       <c r="E64">
         <v>413.7619999999999</v>
@@ -6541,37 +6648,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M64">
-        <v>501.1229022889412</v>
+        <v>468.1069722889412</v>
       </c>
       <c r="N64">
-        <v>-247.9229022889413</v>
+        <v>-214.9069722889413</v>
       </c>
       <c r="O64">
-        <v>-52.06380948067768</v>
+        <v>-45.13046418067767</v>
       </c>
       <c r="P64">
-        <v>-195.8590928082637</v>
+        <v>-169.7765081082636</v>
       </c>
       <c r="Q64">
-        <v>361.4409071917363</v>
+        <v>387.5234918917363</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1235030251139298</v>
+        <v>0.1230909271884435</v>
       </c>
       <c r="T64">
-        <v>1.309741076519776</v>
+        <v>1.303236070213327</v>
       </c>
       <c r="U64">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V64">
-        <v>0.1061057073167685</v>
+        <v>0.1135894211103083</v>
       </c>
       <c r="W64">
-        <v>0.2035158038660162</v>
+        <v>0.1885158038660162</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6686,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5052652729369929</v>
+        <v>0.5409020052871827</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6697,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1940717593866454</v>
+        <v>0.1653230830617892</v>
       </c>
       <c r="C65">
-        <v>-511.5469186460743</v>
+        <v>-258.4364999342909</v>
       </c>
       <c r="D65">
-        <v>1690.316081353926</v>
+        <v>1943.426500065709</v>
       </c>
       <c r="E65">
         <v>449.2630000000001</v>
@@ -6623,45 +6730,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M65">
-        <v>576.3024197452145</v>
+        <v>475.6570847452145</v>
       </c>
       <c r="N65">
-        <v>-323.1024197452145</v>
+        <v>-222.4570847452146</v>
       </c>
       <c r="O65">
-        <v>-67.85150814649505</v>
+        <v>-46.71598779649506</v>
       </c>
       <c r="P65">
-        <v>-255.2509115987195</v>
+        <v>-175.7410969487195</v>
       </c>
       <c r="Q65">
-        <v>302.0490884012805</v>
+        <v>381.5589030512805</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1262573747472018</v>
+        <v>0.1251798711665095</v>
       </c>
       <c r="T65">
-        <v>1.356167645479018</v>
+        <v>1.33845866670558</v>
       </c>
       <c r="U65">
-        <v>0.2576732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V65">
-        <v>0.09226405820664006</v>
+        <v>0.1117864144260177</v>
       </c>
       <c r="W65">
-        <v>0.2338992551272709</v>
+        <v>0.1888992551272709</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.4393526581268574</v>
+        <v>0.532316259171513</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6779,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1961904917198961</v>
+        <v>0.1669918153950399</v>
       </c>
       <c r="C66">
-        <v>-563.1237702954752</v>
+        <v>-310.689979286278</v>
       </c>
       <c r="D66">
-        <v>1674.240229704525</v>
+        <v>1926.674020713722</v>
       </c>
       <c r="E66">
         <v>484.7639999999999</v>
@@ -6705,45 +6812,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M66">
-        <v>585.4500772014877</v>
+        <v>483.2071972014877</v>
       </c>
       <c r="N66">
-        <v>-332.2500772014878</v>
+        <v>-230.0071972014878</v>
       </c>
       <c r="O66">
-        <v>-69.77251621231242</v>
+        <v>-48.30151141231243</v>
       </c>
       <c r="P66">
-        <v>-262.4775609891753</v>
+        <v>-181.7056857891753</v>
       </c>
       <c r="Q66">
-        <v>294.8224390108246</v>
+        <v>375.5943142108246</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.128492301823513</v>
+        <v>0.1273848675878015</v>
       </c>
       <c r="T66">
-        <v>1.393838968964546</v>
+        <v>1.375638074114068</v>
       </c>
       <c r="U66">
-        <v>0.2576732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V66">
-        <v>0.09082243229716132</v>
+        <v>0.1100397517006112</v>
       </c>
       <c r="W66">
-        <v>0.2342707235366115</v>
+        <v>0.1892707235366115</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.4324877728436254</v>
+        <v>0.5239988176219581</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6861,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1983092240531468</v>
+        <v>0.1686605477282906</v>
       </c>
       <c r="C67">
-        <v>-614.3977220058234</v>
+        <v>-362.6571117613873</v>
       </c>
       <c r="D67">
-        <v>1658.467277994177</v>
+        <v>1910.207888238613</v>
       </c>
       <c r="E67">
         <v>520.2650000000001</v>
@@ -6787,45 +6894,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M67">
-        <v>594.597734657761</v>
+        <v>490.757309657761</v>
       </c>
       <c r="N67">
-        <v>-341.397734657761</v>
+        <v>-237.557309657761</v>
       </c>
       <c r="O67">
-        <v>-71.69352427812981</v>
+        <v>-49.88703502812982</v>
       </c>
       <c r="P67">
-        <v>-269.7042103796312</v>
+        <v>-187.6702746296312</v>
       </c>
       <c r="Q67">
-        <v>287.5957896203687</v>
+        <v>369.6297253703688</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1308549390184705</v>
+        <v>0.1297158638045958</v>
       </c>
       <c r="T67">
-        <v>1.43366293950639</v>
+        <v>1.414942019088756</v>
       </c>
       <c r="U67">
-        <v>0.2576732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V67">
-        <v>0.08942516410797423</v>
+        <v>0.1083468324436787</v>
       </c>
       <c r="W67">
-        <v>0.2346307621487417</v>
+        <v>0.1896307621487416</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.4258341147998772</v>
+        <v>0.5159372973508511</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6943,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2004279563863974</v>
+        <v>0.1703292800615413</v>
       </c>
       <c r="C68">
-        <v>-665.377254704068</v>
+        <v>-414.3451768534844</v>
       </c>
       <c r="D68">
-        <v>1642.988745295932</v>
+        <v>1894.020823146516</v>
       </c>
       <c r="E68">
         <v>555.7660000000003</v>
@@ -6869,45 +6976,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M68">
-        <v>603.7453921140343</v>
+        <v>498.3074221140342</v>
       </c>
       <c r="N68">
-        <v>-350.5453921140344</v>
+        <v>-245.1074221140343</v>
       </c>
       <c r="O68">
-        <v>-73.61453234394722</v>
+        <v>-51.4725586439472</v>
       </c>
       <c r="P68">
-        <v>-276.9308597700872</v>
+        <v>-193.6348634700871</v>
       </c>
       <c r="Q68">
-        <v>280.3691402299128</v>
+        <v>363.6651365299128</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1333565548719549</v>
+        <v>0.1321839774459074</v>
       </c>
       <c r="T68">
-        <v>1.475829496550696</v>
+        <v>1.45655796082666</v>
       </c>
       <c r="U68">
-        <v>0.2576732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V68">
-        <v>0.08807023737906551</v>
+        <v>0.1067052137702896</v>
       </c>
       <c r="W68">
-        <v>0.2349798904998981</v>
+        <v>0.1899798904998981</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.4193820827574548</v>
+        <v>0.5081200655728079</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +7025,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2025466887196481</v>
+        <v>0.171998012394792</v>
       </c>
       <c r="C69">
-        <v>-716.0705356336348</v>
+        <v>-465.7612093846133</v>
       </c>
       <c r="D69">
-        <v>1627.796464366365</v>
+        <v>1878.105790615387</v>
       </c>
       <c r="E69">
         <v>591.2670000000001</v>
@@ -6951,45 +7058,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M69">
-        <v>612.8930495703075</v>
+        <v>505.8575345703075</v>
       </c>
       <c r="N69">
-        <v>-359.6930495703076</v>
+        <v>-252.6575345703075</v>
       </c>
       <c r="O69">
-        <v>-75.53554040976459</v>
+        <v>-53.05808225976457</v>
       </c>
       <c r="P69">
-        <v>-284.157509160543</v>
+        <v>-199.5994523105429</v>
       </c>
       <c r="Q69">
-        <v>273.142490839457</v>
+        <v>357.700547689457</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1360097838074687</v>
+        <v>0.1348016737321471</v>
       </c>
       <c r="T69">
-        <v>1.520551602506778</v>
+        <v>1.50069608085171</v>
       </c>
       <c r="U69">
-        <v>0.2576732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V69">
-        <v>0.08675575622415407</v>
+        <v>0.1051125986393898</v>
       </c>
       <c r="W69">
-        <v>0.235318597109229</v>
+        <v>0.190318597109229</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.413122648686448</v>
+        <v>0.5005361839970943</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7107,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2046654210528988</v>
+        <v>0.1977811909860263</v>
       </c>
       <c r="C70">
-        <v>-766.4854327242938</v>
+        <v>-717.0762987017288</v>
       </c>
       <c r="D70">
-        <v>1612.882567275706</v>
+        <v>1662.291701298271</v>
       </c>
       <c r="E70">
         <v>626.7680000000003</v>
@@ -7033,37 +7140,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M70">
-        <v>622.0407070265808</v>
+        <v>597.9000270265808</v>
       </c>
       <c r="N70">
-        <v>-368.8407070265808</v>
+        <v>-344.7000270265809</v>
       </c>
       <c r="O70">
-        <v>-77.45654847558197</v>
+        <v>-72.38700567558197</v>
       </c>
       <c r="P70">
-        <v>-291.3841585509989</v>
+        <v>-272.3130213509989</v>
       </c>
       <c r="Q70">
-        <v>265.9158414490011</v>
+        <v>284.9869786490011</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1388288395514521</v>
+        <v>0.1385656205924755</v>
       </c>
       <c r="T70">
-        <v>1.568068840085115</v>
+        <v>1.564161632284241</v>
       </c>
       <c r="U70">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V70">
-        <v>0.08547993627968123</v>
+        <v>0.08893125538801175</v>
       </c>
       <c r="W70">
-        <v>0.2356473417594619</v>
+        <v>0.2256473417594619</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7178,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4070473156175297</v>
+        <v>0.4234821685143417</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7189,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2067841533861495</v>
+        <v>0.1997999233192769</v>
       </c>
       <c r="C71">
-        <v>-816.6295281792536</v>
+        <v>-767.3997266468687</v>
       </c>
       <c r="D71">
-        <v>1598.239471820746</v>
+        <v>1647.469273353131</v>
       </c>
       <c r="E71">
         <v>662.269</v>
@@ -7115,37 +7222,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M71">
-        <v>631.188364482854</v>
+        <v>606.6926744828539</v>
       </c>
       <c r="N71">
-        <v>-377.9883644828541</v>
+        <v>-353.492674482854</v>
       </c>
       <c r="O71">
-        <v>-79.37755654139936</v>
+        <v>-74.23346164139933</v>
       </c>
       <c r="P71">
-        <v>-298.6108079414547</v>
+        <v>-279.2592128414547</v>
       </c>
       <c r="Q71">
-        <v>258.6891920585452</v>
+        <v>278.0407871585453</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1418297698595635</v>
+        <v>0.1415580599664263</v>
       </c>
       <c r="T71">
-        <v>1.618651705894312</v>
+        <v>1.61461845913212</v>
       </c>
       <c r="U71">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V71">
-        <v>0.08424109662345397</v>
+        <v>0.08764239661427246</v>
       </c>
       <c r="W71">
-        <v>0.2359665575792533</v>
+        <v>0.2259665575792533</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7260,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4011480791593046</v>
+        <v>0.4173447457822499</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7271,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2089028857194001</v>
+        <v>0.2018186556525276</v>
       </c>
       <c r="C72">
-        <v>-866.5101313287917</v>
+        <v>-817.461151706985</v>
       </c>
       <c r="D72">
-        <v>1583.859868671208</v>
+        <v>1632.908848293015</v>
       </c>
       <c r="E72">
         <v>697.7700000000002</v>
@@ -7197,37 +7304,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M72">
-        <v>640.3360219391272</v>
+        <v>615.4853219391273</v>
       </c>
       <c r="N72">
-        <v>-387.1360219391273</v>
+        <v>-362.2853219391274</v>
       </c>
       <c r="O72">
-        <v>-81.29856460721673</v>
+        <v>-76.07991760721674</v>
       </c>
       <c r="P72">
-        <v>-305.8374573319106</v>
+        <v>-286.2054043319106</v>
       </c>
       <c r="Q72">
-        <v>251.4625426680894</v>
+        <v>271.0945956680894</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1450307621882156</v>
+        <v>0.1447499952986405</v>
       </c>
       <c r="T72">
-        <v>1.672606762757455</v>
+        <v>1.668439074436524</v>
       </c>
       <c r="U72">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V72">
-        <v>0.08303765238597605</v>
+        <v>0.0863903623769257</v>
       </c>
       <c r="W72">
-        <v>0.2362766529470507</v>
+        <v>0.2262766529470507</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7342,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3954173923141717</v>
+        <v>0.4113826779853604</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7353,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2110216180526508</v>
+        <v>0.2038373879857783</v>
       </c>
       <c r="C73">
-        <v>-916.134290796188</v>
+        <v>-867.2674598120498</v>
       </c>
       <c r="D73">
-        <v>1569.736709203812</v>
+        <v>1618.60354018795</v>
       </c>
       <c r="E73">
         <v>733.271</v>
@@ -7279,37 +7386,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M73">
-        <v>649.4836793954005</v>
+        <v>624.2779693954004</v>
       </c>
       <c r="N73">
-        <v>-396.2836793954006</v>
+        <v>-371.0779693954005</v>
       </c>
       <c r="O73">
-        <v>-83.21957267303411</v>
+        <v>-77.9263735730341</v>
       </c>
       <c r="P73">
-        <v>-313.0641067223664</v>
+        <v>-293.1515958223664</v>
       </c>
       <c r="Q73">
-        <v>244.2358932776335</v>
+        <v>264.1484041776336</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1484525126084988</v>
+        <v>0.1481620641020419</v>
       </c>
       <c r="T73">
-        <v>1.730282858024954</v>
+        <v>1.725971456313645</v>
       </c>
       <c r="U73">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V73">
-        <v>0.08186810798617358</v>
+        <v>0.08517359670964507</v>
       </c>
       <c r="W73">
-        <v>0.236578013234065</v>
+        <v>0.226578013234065</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7424,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3898481332674932</v>
+        <v>0.4055885557602147</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7435,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2131403503859015</v>
+        <v>0.205856120319029</v>
       </c>
       <c r="C74">
-        <v>-965.5088060185217</v>
+        <v>-916.8252976873202</v>
       </c>
       <c r="D74">
-        <v>1555.863193981478</v>
+        <v>1604.546702312679</v>
       </c>
       <c r="E74">
         <v>768.7719999999997</v>
@@ -7361,37 +7468,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M74">
-        <v>658.6313368516736</v>
+        <v>633.0706168516737</v>
       </c>
       <c r="N74">
-        <v>-405.4313368516737</v>
+        <v>-379.8706168516737</v>
       </c>
       <c r="O74">
-        <v>-85.14058073885147</v>
+        <v>-79.77282953885148</v>
       </c>
       <c r="P74">
-        <v>-320.2907561128222</v>
+        <v>-300.0977873128222</v>
       </c>
       <c r="Q74">
-        <v>237.0092438871777</v>
+        <v>257.2022126871777</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1521186737730881</v>
+        <v>0.1518178521056862</v>
       </c>
       <c r="T74">
-        <v>1.792078674382988</v>
+        <v>1.787613294039132</v>
       </c>
       <c r="U74">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V74">
-        <v>0.08073105093081007</v>
+        <v>0.08399063008867777</v>
       </c>
       <c r="W74">
-        <v>0.2368710024019956</v>
+        <v>0.2268710024019956</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7506,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3844335758610004</v>
+        <v>0.3999553813746561</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7517,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2152590827191522</v>
+        <v>0.2078748526522797</v>
       </c>
       <c r="C75">
-        <v>-1014.640238161882</v>
+        <v>-966.1410831508258</v>
       </c>
       <c r="D75">
-        <v>1542.232761838118</v>
+        <v>1590.731916849174</v>
       </c>
       <c r="E75">
         <v>804.2729999999999</v>
@@ -7443,37 +7550,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M75">
-        <v>667.778994307947</v>
+        <v>641.8632643079469</v>
       </c>
       <c r="N75">
-        <v>-414.578994307947</v>
+        <v>-388.663264307947</v>
       </c>
       <c r="O75">
-        <v>-87.06158880466887</v>
+        <v>-81.61928550466887</v>
       </c>
       <c r="P75">
-        <v>-327.5174055032782</v>
+        <v>-307.0439788032781</v>
       </c>
       <c r="Q75">
-        <v>229.7825944967218</v>
+        <v>250.2560211967219</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1560564024313506</v>
+        <v>0.1557444392207116</v>
       </c>
       <c r="T75">
-        <v>1.858451958619395</v>
+        <v>1.85382119381836</v>
       </c>
       <c r="U75">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V75">
-        <v>0.07962514612353869</v>
+        <v>0.08284007351212055</v>
       </c>
       <c r="W75">
-        <v>0.237155964469435</v>
+        <v>0.227155964469435</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7588,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3791673624930414</v>
+        <v>0.3944765405339073</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7599,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2173778150524029</v>
+        <v>0.2098935849855303</v>
       </c>
       <c r="C76">
-        <v>-1063.534920467814</v>
+        <v>-1015.221014883451</v>
       </c>
       <c r="D76">
-        <v>1528.839079532186</v>
+        <v>1577.152985116549</v>
       </c>
       <c r="E76">
         <v>839.7740000000001</v>
@@ -7525,37 +7632,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M76">
-        <v>676.9266517642202</v>
+        <v>650.6559117642201</v>
       </c>
       <c r="N76">
-        <v>-423.7266517642203</v>
+        <v>-397.4559117642202</v>
       </c>
       <c r="O76">
-        <v>-88.98259687048625</v>
+        <v>-83.46574147048624</v>
       </c>
       <c r="P76">
-        <v>-334.744054893734</v>
+        <v>-313.990170293734</v>
       </c>
       <c r="Q76">
-        <v>222.5559451062659</v>
+        <v>243.309829706266</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1602970332940949</v>
+        <v>0.1599730714984313</v>
       </c>
       <c r="T76">
-        <v>1.929930880104756</v>
+        <v>1.92512200896522</v>
       </c>
       <c r="U76">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V76">
-        <v>0.07854913063538276</v>
+        <v>0.08172061305925406</v>
       </c>
       <c r="W76">
-        <v>0.237433224859376</v>
+        <v>0.2274332248593759</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7670,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3740434792161084</v>
+        <v>0.3891457764726384</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7681,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2194965473856536</v>
+        <v>0.211912317318781</v>
       </c>
       <c r="C77">
-        <v>-1112.198968065281</v>
+        <v>-1064.071081702849</v>
       </c>
       <c r="D77">
-        <v>1515.676031934719</v>
+        <v>1563.803918297151</v>
       </c>
       <c r="E77">
         <v>875.2749999999999</v>
@@ -7607,37 +7714,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M77">
-        <v>686.0743092204934</v>
+        <v>659.4485592204934</v>
       </c>
       <c r="N77">
-        <v>-432.8743092204935</v>
+        <v>-406.2485592204935</v>
       </c>
       <c r="O77">
-        <v>-90.90360493630364</v>
+        <v>-85.31219743630362</v>
       </c>
       <c r="P77">
-        <v>-341.9707042841899</v>
+        <v>-320.9363617841898</v>
       </c>
       <c r="Q77">
-        <v>215.3292957158101</v>
+        <v>236.3636382158101</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1648769146258587</v>
+        <v>0.1645399943583686</v>
       </c>
       <c r="T77">
-        <v>2.007128115308947</v>
+        <v>2.002126889323829</v>
       </c>
       <c r="U77">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V77">
-        <v>0.07750180889357765</v>
+        <v>0.08063100488513067</v>
       </c>
       <c r="W77">
-        <v>0.2377030916389185</v>
+        <v>0.2277030916389185</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7752,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3690562328265603</v>
+        <v>0.3839571661196699</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7763,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2216152797189042</v>
+        <v>0.2139310496520317</v>
       </c>
       <c r="C78">
-        <v>-1160.638287280076</v>
+        <v>-1112.697071370342</v>
       </c>
       <c r="D78">
-        <v>1502.737712719924</v>
+        <v>1550.678928629658</v>
       </c>
       <c r="E78">
         <v>910.7760000000001</v>
@@ -7689,37 +7796,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M78">
-        <v>695.2219666767667</v>
+        <v>668.2412066767666</v>
       </c>
       <c r="N78">
-        <v>-442.0219666767667</v>
+        <v>-415.0412066767667</v>
       </c>
       <c r="O78">
-        <v>-92.82461300212101</v>
+        <v>-87.158653402121</v>
       </c>
       <c r="P78">
-        <v>-349.1973536746457</v>
+        <v>-327.8825532746457</v>
       </c>
       <c r="Q78">
-        <v>208.1026463253542</v>
+        <v>229.4174467253542</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1698384527352695</v>
+        <v>0.1694874941233006</v>
       </c>
       <c r="T78">
-        <v>2.090758453446819</v>
+        <v>2.085548843045655</v>
       </c>
       <c r="U78">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V78">
-        <v>0.0764820482502411</v>
+        <v>0.07957007061032631</v>
       </c>
       <c r="W78">
-        <v>0.2379658566611047</v>
+        <v>0.2279658566611047</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7834,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3642002297630529</v>
+        <v>0.3789050981444111</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7845,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2237340120521549</v>
+        <v>0.2159497819852824</v>
       </c>
       <c r="C79">
-        <v>-1208.858584471458</v>
+        <v>-1161.104578958011</v>
       </c>
       <c r="D79">
-        <v>1490.018415528542</v>
+        <v>1537.772421041988</v>
       </c>
       <c r="E79">
         <v>946.2769999999998</v>
@@ -7771,37 +7878,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M79">
-        <v>704.3696241330399</v>
+        <v>677.0338541330399</v>
       </c>
       <c r="N79">
-        <v>-451.16962413304</v>
+        <v>-423.8338541330399</v>
       </c>
       <c r="O79">
-        <v>-94.74562106793839</v>
+        <v>-89.00510936793839</v>
       </c>
       <c r="P79">
-        <v>-356.4240030651016</v>
+        <v>-334.8287447651015</v>
       </c>
       <c r="Q79">
-        <v>200.8759969348984</v>
+        <v>222.4712552348984</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1752314289411507</v>
+        <v>0.1748652112590963</v>
       </c>
       <c r="T79">
-        <v>2.181660994901029</v>
+        <v>2.176224879699814</v>
       </c>
       <c r="U79">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V79">
-        <v>0.07548877489634187</v>
+        <v>0.07853669306993247</v>
       </c>
       <c r="W79">
-        <v>0.2382217966177795</v>
+        <v>0.2282217966177795</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7916,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.359470356649247</v>
+        <v>0.3739842527139642</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7927,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2258527443854056</v>
+        <v>0.2179685143185331</v>
       </c>
       <c r="C80">
-        <v>-1256.86537442379</v>
+        <v>-1209.299014801405</v>
       </c>
       <c r="D80">
-        <v>1477.51262557621</v>
+        <v>1525.078985198595</v>
       </c>
       <c r="E80">
         <v>981.778</v>
@@ -7853,37 +7960,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M80">
-        <v>713.5172815893131</v>
+        <v>685.8265015893131</v>
       </c>
       <c r="N80">
-        <v>-460.3172815893132</v>
+        <v>-432.6265015893132</v>
       </c>
       <c r="O80">
-        <v>-96.66662913375578</v>
+        <v>-90.85156533375577</v>
       </c>
       <c r="P80">
-        <v>-363.6506524555574</v>
+        <v>-341.7749362555574</v>
       </c>
       <c r="Q80">
-        <v>193.6493475444425</v>
+        <v>215.5250637444425</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1811146757112031</v>
+        <v>0.1807318117708734</v>
       </c>
       <c r="T80">
-        <v>2.280827403760167</v>
+        <v>2.275144192413442</v>
       </c>
       <c r="U80">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V80">
-        <v>0.07452097008997852</v>
+        <v>0.07752981238954872</v>
       </c>
       <c r="W80">
-        <v>0.2384711740114627</v>
+        <v>0.2284711740114627</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7998,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3548617623332311</v>
+        <v>0.3691895828073749</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +8009,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2279714767186563</v>
+        <v>0.2199872466517838</v>
       </c>
       <c r="C81">
-        <v>-1304.663988319109</v>
+        <v>-1257.285612061582</v>
       </c>
       <c r="D81">
-        <v>1465.215011680891</v>
+        <v>1512.593387938418</v>
       </c>
       <c r="E81">
         <v>1017.279</v>
@@ -7935,37 +8042,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M81">
-        <v>722.6649390455865</v>
+        <v>694.6191490455865</v>
       </c>
       <c r="N81">
-        <v>-469.4649390455866</v>
+        <v>-441.4191490455866</v>
       </c>
       <c r="O81">
-        <v>-98.58763719957318</v>
+        <v>-92.69802129957317</v>
       </c>
       <c r="P81">
-        <v>-370.8773018460134</v>
+        <v>-348.7211277460134</v>
       </c>
       <c r="Q81">
-        <v>186.4226981539866</v>
+        <v>208.5788722539866</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1875582316974508</v>
+        <v>0.187157136140915</v>
       </c>
       <c r="T81">
-        <v>2.38943823251065</v>
+        <v>2.383484392052178</v>
       </c>
       <c r="U81">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V81">
-        <v>0.07357766667111802</v>
+        <v>0.07654842235930126</v>
       </c>
       <c r="W81">
-        <v>0.2387142380534071</v>
+        <v>0.2287142380534071</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +8080,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3503698412910382</v>
+        <v>0.3645162969490536</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +8091,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.230090209051907</v>
+        <v>0.2220059789850345</v>
       </c>
       <c r="C82">
-        <v>-1352.259581314837</v>
+        <v>-1305.069433918732</v>
       </c>
       <c r="D82">
-        <v>1453.120418685163</v>
+        <v>1500.310566081268</v>
       </c>
       <c r="E82">
         <v>1052.78</v>
@@ -8017,37 +8124,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M82">
-        <v>731.8125965018596</v>
+        <v>703.4117965018596</v>
       </c>
       <c r="N82">
-        <v>-478.6125965018597</v>
+        <v>-450.2117965018597</v>
       </c>
       <c r="O82">
-        <v>-100.5086452653905</v>
+        <v>-94.54447726539053</v>
       </c>
       <c r="P82">
-        <v>-378.1039512364691</v>
+        <v>-355.6673192364692</v>
       </c>
       <c r="Q82">
-        <v>179.1960487635308</v>
+        <v>201.6326807635308</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1946461432823234</v>
+        <v>0.1942249929479607</v>
       </c>
       <c r="T82">
-        <v>2.508910144136184</v>
+        <v>2.502658611654786</v>
       </c>
       <c r="U82">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V82">
-        <v>0.07265794583772905</v>
+        <v>0.07559156707981</v>
       </c>
       <c r="W82">
-        <v>0.2389512254943029</v>
+        <v>0.2289512254943029</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8162,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3459902182749003</v>
+        <v>0.3599598432371905</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8173,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2322089413851577</v>
+        <v>0.2240247113182851</v>
       </c>
       <c r="C83">
-        <v>-1399.657139749267</v>
+        <v>-1352.655380418126</v>
       </c>
       <c r="D83">
-        <v>1441.223860250733</v>
+        <v>1488.225619581875</v>
       </c>
       <c r="E83">
         <v>1088.281</v>
@@ -8099,37 +8206,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M83">
-        <v>740.960253958133</v>
+        <v>712.204443958133</v>
       </c>
       <c r="N83">
-        <v>-487.760253958133</v>
+        <v>-459.004443958133</v>
       </c>
       <c r="O83">
-        <v>-102.4296533312079</v>
+        <v>-96.39093323120794</v>
       </c>
       <c r="P83">
-        <v>-385.3306006269251</v>
+        <v>-362.6135107269251</v>
       </c>
       <c r="Q83">
-        <v>171.9693993730749</v>
+        <v>194.6864892730749</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2024801508234983</v>
+        <v>0.2020368346820639</v>
       </c>
       <c r="T83">
-        <v>2.640958046459141</v>
+        <v>2.634377485952407</v>
       </c>
       <c r="U83">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V83">
-        <v>0.07176093416072005</v>
+        <v>0.07465833785660246</v>
       </c>
       <c r="W83">
-        <v>0.2391823613934481</v>
+        <v>0.2291823613934481</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8244,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3417187340986669</v>
+        <v>0.3555158945552498</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8255,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2343276737184083</v>
+        <v>0.2260434436515358</v>
       </c>
       <c r="C84">
-        <v>-1446.861487995973</v>
+        <v>-1400.048194987837</v>
       </c>
       <c r="D84">
-        <v>1429.520512004028</v>
+        <v>1476.333805012163</v>
       </c>
       <c r="E84">
         <v>1123.782</v>
@@ -8181,37 +8288,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M84">
-        <v>750.1079114144063</v>
+        <v>720.9970914144062</v>
       </c>
       <c r="N84">
-        <v>-496.9079114144064</v>
+        <v>-467.7970914144063</v>
       </c>
       <c r="O84">
-        <v>-104.3506613970253</v>
+        <v>-98.23738919702532</v>
       </c>
       <c r="P84">
-        <v>-392.5572500173811</v>
+        <v>-369.559702217381</v>
       </c>
       <c r="Q84">
-        <v>164.7427499826189</v>
+        <v>187.740297782619</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.211184603647026</v>
+        <v>0.2107166588310675</v>
       </c>
       <c r="T84">
-        <v>2.787677937929093</v>
+        <v>2.78073179072754</v>
       </c>
       <c r="U84">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V84">
-        <v>0.07088580081729662</v>
+        <v>0.07374787032176584</v>
       </c>
       <c r="W84">
-        <v>0.2394078598316386</v>
+        <v>0.2294078598316386</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8326,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3375514324633172</v>
+        <v>0.3511803348655517</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8337,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.236446406051659</v>
+        <v>0.2280621759847865</v>
       </c>
       <c r="C85">
-        <v>-1493.877294986953</v>
+        <v>-1447.252470646474</v>
       </c>
       <c r="D85">
-        <v>1418.005705013047</v>
+        <v>1464.630529353527</v>
       </c>
       <c r="E85">
         <v>1159.283</v>
@@ -8263,37 +8370,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M85">
-        <v>759.2555688706794</v>
+        <v>729.7897388706795</v>
       </c>
       <c r="N85">
-        <v>-506.0555688706795</v>
+        <v>-476.5897388706795</v>
       </c>
       <c r="O85">
-        <v>-106.2716694628427</v>
+        <v>-100.0838451628427</v>
       </c>
       <c r="P85">
-        <v>-399.7838994078368</v>
+        <v>-376.5058937078368</v>
       </c>
       <c r="Q85">
-        <v>157.5161005921631</v>
+        <v>180.7941062921631</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2209131097439099</v>
+        <v>0.2204176387623068</v>
       </c>
       <c r="T85">
-        <v>2.951658993101393</v>
+        <v>2.944304249005631</v>
       </c>
       <c r="U85">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V85">
-        <v>0.07003175502431715</v>
+        <v>0.07285934176367227</v>
       </c>
       <c r="W85">
-        <v>0.2396279245725233</v>
+        <v>0.2296279245725233</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8408,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3334845477348436</v>
+        <v>0.3469492464936775</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8419,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2385651383849097</v>
+        <v>0.2300809083180372</v>
       </c>
       <c r="C86">
-        <v>-1540.709080423025</v>
+        <v>-1494.272655917953</v>
       </c>
       <c r="D86">
-        <v>1406.674919576975</v>
+        <v>1453.111344082047</v>
       </c>
       <c r="E86">
         <v>1194.784</v>
@@ -8345,37 +8452,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M86">
-        <v>768.4032263269527</v>
+        <v>738.5823863269526</v>
       </c>
       <c r="N86">
-        <v>-515.2032263269527</v>
+        <v>-485.3823863269527</v>
       </c>
       <c r="O86">
-        <v>-108.1926775286601</v>
+        <v>-101.93030112866</v>
       </c>
       <c r="P86">
-        <v>-407.0105487982927</v>
+        <v>-383.4520851982926</v>
       </c>
       <c r="Q86">
-        <v>150.2894512017073</v>
+        <v>173.8479148017074</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2318576791029042</v>
+        <v>0.2313312411849509</v>
       </c>
       <c r="T86">
-        <v>3.136137680170228</v>
+        <v>3.128323264568482</v>
       </c>
       <c r="U86">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V86">
-        <v>0.06919804365498004</v>
+        <v>0.07199196864743811</v>
       </c>
       <c r="W86">
-        <v>0.2398427496767203</v>
+        <v>0.2298427496767203</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8490,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3295144935951431</v>
+        <v>0.3428188983211338</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8501,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2406838707181604</v>
+        <v>0.2320996406512879</v>
       </c>
       <c r="C87">
-        <v>-1587.36122068883</v>
+        <v>-1541.113060469355</v>
       </c>
       <c r="D87">
-        <v>1395.52377931117</v>
+        <v>1441.771939530645</v>
       </c>
       <c r="E87">
         <v>1230.285</v>
@@ -8427,37 +8534,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M87">
-        <v>777.5508837832259</v>
+        <v>747.3750337832259</v>
       </c>
       <c r="N87">
-        <v>-524.350883783226</v>
+        <v>-494.175033783226</v>
       </c>
       <c r="O87">
-        <v>-110.1136855944774</v>
+        <v>-103.7767570944775</v>
       </c>
       <c r="P87">
-        <v>-414.2371981887486</v>
+        <v>-390.3982766887485</v>
       </c>
       <c r="Q87">
-        <v>143.0628018112514</v>
+        <v>166.9017233112514</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2442615243764311</v>
+        <v>0.2436999905972809</v>
       </c>
       <c r="T87">
-        <v>3.34521352551491</v>
+        <v>3.336878148873047</v>
       </c>
       <c r="U87">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V87">
-        <v>0.06838394902374499</v>
+        <v>0.0711450043104094</v>
       </c>
       <c r="W87">
-        <v>0.2400525200725832</v>
+        <v>0.2300525200725832</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8572,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3256378524940238</v>
+        <v>0.3387857348114733</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8583,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.242802603051411</v>
+        <v>0.2341183729845385</v>
       </c>
       <c r="C88">
-        <v>-1633.837954488708</v>
+        <v>-1587.777860486838</v>
       </c>
       <c r="D88">
-        <v>1384.548045511292</v>
+        <v>1430.608139513162</v>
       </c>
       <c r="E88">
         <v>1265.786</v>
@@ -8509,37 +8616,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M88">
-        <v>786.6985412394991</v>
+        <v>756.1676812394991</v>
       </c>
       <c r="N88">
-        <v>-533.4985412394992</v>
+        <v>-502.9676812394991</v>
       </c>
       <c r="O88">
-        <v>-112.0346936602948</v>
+        <v>-105.6232130602948</v>
       </c>
       <c r="P88">
-        <v>-421.4638475792044</v>
+        <v>-397.3444681792043</v>
       </c>
       <c r="Q88">
-        <v>135.8361524207955</v>
+        <v>159.9555318207956</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2584373475461762</v>
+        <v>0.2578357042113724</v>
       </c>
       <c r="T88">
-        <v>3.584157348765975</v>
+        <v>3.575226588078265</v>
       </c>
       <c r="U88">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V88">
-        <v>0.06758878682579446</v>
+        <v>0.07031773681842791</v>
       </c>
       <c r="W88">
-        <v>0.240257412087147</v>
+        <v>0.230257412087147</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8654,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3218513658371165</v>
+        <v>0.3348463658020376</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8665,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2449213353846618</v>
+        <v>0.2361371053177892</v>
       </c>
       <c r="C89">
-        <v>-1680.1433882187</v>
+        <v>-1634.271103803721</v>
       </c>
       <c r="D89">
-        <v>1373.7436117813</v>
+        <v>1419.615896196279</v>
       </c>
       <c r="E89">
         <v>1301.287</v>
@@ -8591,37 +8698,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M89">
-        <v>795.8461986957724</v>
+        <v>764.9603286957723</v>
       </c>
       <c r="N89">
-        <v>-542.6461986957725</v>
+        <v>-511.7603286957724</v>
       </c>
       <c r="O89">
-        <v>-113.9557017261122</v>
+        <v>-107.4696690261122</v>
       </c>
       <c r="P89">
-        <v>-428.6904969696602</v>
+        <v>-404.2906596696602</v>
       </c>
       <c r="Q89">
-        <v>128.6095030303397</v>
+        <v>153.0093403303398</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2747940665881898</v>
+        <v>0.2741461429968626</v>
       </c>
       <c r="T89">
-        <v>3.859861760209512</v>
+        <v>3.850244017930439</v>
       </c>
       <c r="U89">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V89">
-        <v>0.06681190421860142</v>
+        <v>0.06950948696994023</v>
       </c>
       <c r="W89">
-        <v>0.2404575939404564</v>
+        <v>0.2304575939404564</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8736,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3181519248504829</v>
+        <v>0.3309975569997154</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8747,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2470400677179124</v>
+        <v>0.2381558376510399</v>
       </c>
       <c r="C90">
-        <v>-1726.281501088962</v>
+        <v>-1680.596714793953</v>
       </c>
       <c r="D90">
-        <v>1363.106498911038</v>
+        <v>1408.791285206047</v>
       </c>
       <c r="E90">
         <v>1336.788</v>
@@ -8673,37 +8780,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M90">
-        <v>804.9938561520456</v>
+        <v>773.7529761520456</v>
       </c>
       <c r="N90">
-        <v>-551.7938561520457</v>
+        <v>-520.5529761520456</v>
       </c>
       <c r="O90">
-        <v>-115.8767097919296</v>
+        <v>-109.3161249919296</v>
       </c>
       <c r="P90">
-        <v>-435.9171463601161</v>
+        <v>-411.236851160116</v>
       </c>
       <c r="Q90">
-        <v>121.3828536398838</v>
+        <v>146.0631488398839</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2938769054705389</v>
+        <v>0.2931749882466012</v>
       </c>
       <c r="T90">
-        <v>4.181516906893639</v>
+        <v>4.17109768609131</v>
       </c>
       <c r="U90">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V90">
-        <v>0.06605267803429914</v>
+        <v>0.06871960643619091</v>
       </c>
       <c r="W90">
-        <v>0.2406532262061906</v>
+        <v>0.2306532262061906</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8818,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3145365620680911</v>
+        <v>0.3272362211247186</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8829,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2491588000511631</v>
+        <v>0.2401745699842905</v>
       </c>
       <c r="C91">
-        <v>-1772.256150010038</v>
+        <v>-1726.7584990434</v>
       </c>
       <c r="D91">
-        <v>1352.632849989961</v>
+        <v>1398.1305009566</v>
       </c>
       <c r="E91">
         <v>1372.289</v>
@@ -8755,37 +8862,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M91">
-        <v>814.1415136083189</v>
+        <v>782.5456236083188</v>
       </c>
       <c r="N91">
-        <v>-560.9415136083189</v>
+        <v>-529.3456236083189</v>
       </c>
       <c r="O91">
-        <v>-117.797717857747</v>
+        <v>-111.162580957747</v>
       </c>
       <c r="P91">
-        <v>-443.1437957505719</v>
+        <v>-418.1830426505719</v>
       </c>
       <c r="Q91">
-        <v>114.156204249428</v>
+        <v>139.116957349428</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3164293514224061</v>
+        <v>0.3156636235417468</v>
       </c>
       <c r="T91">
-        <v>4.561654807520333</v>
+        <v>4.550288384826883</v>
       </c>
       <c r="U91">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V91">
-        <v>0.06531051311256544</v>
+        <v>0.0679474760267955</v>
       </c>
       <c r="W91">
-        <v>0.2408444622412342</v>
+        <v>0.2308444622412342</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8900,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3110024433931687</v>
+        <v>0.3235594096514072</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8911,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2512775323844137</v>
+        <v>0.2421933023175413</v>
       </c>
       <c r="C92">
-        <v>-1818.071074255572</v>
+        <v>-1772.760147810629</v>
       </c>
       <c r="D92">
-        <v>1342.318925744428</v>
+        <v>1387.629852189371</v>
       </c>
       <c r="E92">
         <v>1407.79</v>
@@ -8837,37 +8944,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M92">
-        <v>823.2891710645922</v>
+        <v>791.3382710645922</v>
       </c>
       <c r="N92">
-        <v>-570.0891710645923</v>
+        <v>-538.1382710645922</v>
       </c>
       <c r="O92">
-        <v>-119.7187259235644</v>
+        <v>-113.0090369235644</v>
       </c>
       <c r="P92">
-        <v>-450.3704451410279</v>
+        <v>-425.1292341410278</v>
       </c>
       <c r="Q92">
-        <v>106.929554858972</v>
+        <v>132.1707658589721</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3434922865646467</v>
+        <v>0.3426499858959214</v>
       </c>
       <c r="T92">
-        <v>5.017820288272366</v>
+        <v>5.005317223309572</v>
       </c>
       <c r="U92">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V92">
-        <v>0.06458484074464804</v>
+        <v>0.06719250407094221</v>
       </c>
       <c r="W92">
-        <v>0.2410314485866101</v>
+        <v>0.2310314485866101</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8982,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3075468606888002</v>
+        <v>0.3199643050997248</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8993,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2533962647176645</v>
+        <v>0.2442120346507919</v>
       </c>
       <c r="C93">
-        <v>-1863.72989991332</v>
+        <v>-1818.605242288179</v>
       </c>
       <c r="D93">
-        <v>1332.16110008668</v>
+        <v>1377.285757711821</v>
       </c>
       <c r="E93">
         <v>1443.291</v>
@@ -8919,37 +9026,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M93">
-        <v>832.4368285208653</v>
+        <v>800.1309185208653</v>
       </c>
       <c r="N93">
-        <v>-579.2368285208654</v>
+        <v>-546.9309185208654</v>
       </c>
       <c r="O93">
-        <v>-121.6397339893817</v>
+        <v>-114.8554928893817</v>
       </c>
       <c r="P93">
-        <v>-457.5970945314837</v>
+        <v>-432.0754256314837</v>
       </c>
       <c r="Q93">
-        <v>99.70290546851629</v>
+        <v>125.2245743685163</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.376569207294052</v>
+        <v>0.375633317662135</v>
       </c>
       <c r="T93">
-        <v>5.575355875858186</v>
+        <v>5.561463581455081</v>
       </c>
       <c r="U93">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V93">
-        <v>0.06387511721998158</v>
+        <v>0.06645412490532747</v>
       </c>
       <c r="W93">
-        <v>0.2412143253419778</v>
+        <v>0.2312143253419778</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +9064,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3041672248570552</v>
+        <v>0.3164482138348927</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +9075,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2555149970509152</v>
+        <v>0.2462307669840426</v>
       </c>
       <c r="C94">
-        <v>-1909.236144135585</v>
+        <v>-1864.297257674641</v>
       </c>
       <c r="D94">
-        <v>1322.155855864415</v>
+        <v>1367.094742325359</v>
       </c>
       <c r="E94">
         <v>1478.792</v>
@@ -9001,37 +9108,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M94">
-        <v>841.5844859771387</v>
+        <v>808.9235659771387</v>
       </c>
       <c r="N94">
-        <v>-588.3844859771388</v>
+        <v>-555.7235659771387</v>
       </c>
       <c r="O94">
-        <v>-123.5607420551991</v>
+        <v>-116.7019488551991</v>
       </c>
       <c r="P94">
-        <v>-464.8237439219396</v>
+        <v>-439.0216171219396</v>
       </c>
       <c r="Q94">
-        <v>92.47625607806032</v>
+        <v>118.2783828780604</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4179153582058086</v>
+        <v>0.416862482369902</v>
       </c>
       <c r="T94">
-        <v>6.272275360340461</v>
+        <v>6.256646529136969</v>
       </c>
       <c r="U94">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V94">
-        <v>0.06318082246759046</v>
+        <v>0.06573179746070434</v>
       </c>
       <c r="W94">
-        <v>0.241393226515707</v>
+        <v>0.231393226515707</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9146,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3008610593694785</v>
+        <v>0.3130085593366874</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9157,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2576337293841658</v>
+        <v>0.2482494993172933</v>
       </c>
       <c r="C95">
-        <v>-1954.593219199539</v>
+        <v>-1909.839567067286</v>
       </c>
       <c r="D95">
-        <v>1312.299780800462</v>
+        <v>1357.053432932714</v>
       </c>
       <c r="E95">
         <v>1514.293</v>
@@ -9083,37 +9190,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M95">
-        <v>850.7321434334119</v>
+        <v>817.7162134334119</v>
       </c>
       <c r="N95">
-        <v>-597.532143433412</v>
+        <v>-564.516213433412</v>
       </c>
       <c r="O95">
-        <v>-125.4817501210165</v>
+        <v>-118.5484048210165</v>
       </c>
       <c r="P95">
-        <v>-472.0503933123955</v>
+        <v>-445.9678086123955</v>
       </c>
       <c r="Q95">
-        <v>85.24960668760446</v>
+        <v>111.3321913876045</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4710746950923527</v>
+        <v>0.4698714084227452</v>
       </c>
       <c r="T95">
-        <v>7.168314697531956</v>
+        <v>7.150453176156536</v>
       </c>
       <c r="U95">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V95">
-        <v>0.06250145878514327</v>
+        <v>0.0650250039396215</v>
       </c>
       <c r="W95">
-        <v>0.2415682803523669</v>
+        <v>0.2315682803523668</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9228,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2976259942149679</v>
+        <v>0.3096428759029596</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9239,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2597524617174165</v>
+        <v>0.250268231650544</v>
       </c>
       <c r="C96">
-        <v>-1999.804436387281</v>
+        <v>-1955.235445184396</v>
       </c>
       <c r="D96">
-        <v>1302.589563612719</v>
+        <v>1347.158554815604</v>
       </c>
       <c r="E96">
         <v>1549.794</v>
@@ -9165,37 +9272,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M96">
-        <v>859.8798008896852</v>
+        <v>826.5088608896851</v>
       </c>
       <c r="N96">
-        <v>-606.6798008896852</v>
+        <v>-573.3088608896852</v>
       </c>
       <c r="O96">
-        <v>-127.4027581868339</v>
+        <v>-120.3948607868339</v>
       </c>
       <c r="P96">
-        <v>-479.2770427028513</v>
+        <v>-452.9140001028513</v>
       </c>
       <c r="Q96">
-        <v>78.02295729714865</v>
+        <v>104.3859998971486</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5419538109410783</v>
+        <v>0.5405499764932028</v>
       </c>
       <c r="T96">
-        <v>8.363033813787284</v>
+        <v>8.342195372182628</v>
       </c>
       <c r="U96">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V96">
-        <v>0.0618365496491311</v>
+        <v>0.06433324857856169</v>
       </c>
       <c r="W96">
-        <v>0.2417396096393105</v>
+        <v>0.2317396096393105</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9310,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2944597602339577</v>
+        <v>0.3063488027550557</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9321,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2618711940506672</v>
+        <v>0.2522869639837947</v>
       </c>
       <c r="C97">
-        <v>-2044.873009694908</v>
+        <v>-2000.488071925927</v>
       </c>
       <c r="D97">
-        <v>1293.021990305093</v>
+        <v>1337.406928074074</v>
       </c>
       <c r="E97">
         <v>1585.295</v>
@@ -9247,37 +9354,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M97">
-        <v>869.0274583459584</v>
+        <v>835.3015083459584</v>
       </c>
       <c r="N97">
-        <v>-615.8274583459585</v>
+        <v>-582.1015083459585</v>
       </c>
       <c r="O97">
-        <v>-129.3237662526513</v>
+        <v>-122.2413167526513</v>
       </c>
       <c r="P97">
-        <v>-486.5036920933072</v>
+        <v>-459.8601915933071</v>
       </c>
       <c r="Q97">
-        <v>70.79630790669273</v>
+        <v>97.4398084066928</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6411845731292941</v>
+        <v>0.6394999717918437</v>
       </c>
       <c r="T97">
-        <v>10.03564057654475</v>
+        <v>10.01063444661916</v>
       </c>
       <c r="U97">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V97">
-        <v>0.06118563860019288</v>
+        <v>0.06365605648826105</v>
       </c>
       <c r="W97">
-        <v>0.2419073319938974</v>
+        <v>0.2319073319938974</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9392,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2913601838104423</v>
+        <v>0.3031240785155288</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9403,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2639899263839179</v>
+        <v>0.2543056963170453</v>
       </c>
       <c r="C98">
-        <v>-2089.802059379301</v>
+        <v>-2045.600535780629</v>
       </c>
       <c r="D98">
-        <v>1283.593940620699</v>
+        <v>1327.795464219371</v>
       </c>
       <c r="E98">
         <v>1620.796</v>
@@ -9329,37 +9436,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M98">
-        <v>878.1751158022316</v>
+        <v>844.0941558022316</v>
       </c>
       <c r="N98">
-        <v>-624.9751158022317</v>
+        <v>-590.8941558022317</v>
       </c>
       <c r="O98">
-        <v>-131.2447743184686</v>
+        <v>-124.0877727184687</v>
       </c>
       <c r="P98">
-        <v>-493.730341483763</v>
+        <v>-466.806383083763</v>
       </c>
       <c r="Q98">
-        <v>63.56965851623693</v>
+        <v>90.49361691623693</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.790030716411616</v>
+        <v>0.7879249647398028</v>
       </c>
       <c r="T98">
-        <v>12.5445507206809</v>
+        <v>12.51329305827392</v>
       </c>
       <c r="U98">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V98">
-        <v>0.06054828819810754</v>
+        <v>0.06299297256650833</v>
       </c>
       <c r="W98">
-        <v>0.2420715601327638</v>
+        <v>0.2320715601327637</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9474,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2883251818957502</v>
+        <v>0.2999665360309921</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9485,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2661086587171685</v>
+        <v>0.256324428650296</v>
       </c>
       <c r="C99">
-        <v>-2134.594615350888</v>
+        <v>-2090.575837087316</v>
       </c>
       <c r="D99">
-        <v>1274.302384649112</v>
+        <v>1318.321162912683</v>
       </c>
       <c r="E99">
         <v>1656.297</v>
@@ -9411,37 +9518,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M99">
-        <v>887.3227732585048</v>
+        <v>852.8868032585048</v>
       </c>
       <c r="N99">
-        <v>-634.1227732585048</v>
+        <v>-599.6868032585048</v>
       </c>
       <c r="O99">
-        <v>-133.165782384286</v>
+        <v>-125.934228684286</v>
       </c>
       <c r="P99">
-        <v>-500.9569908742188</v>
+        <v>-473.7525745742188</v>
       </c>
       <c r="Q99">
-        <v>56.34300912578112</v>
+        <v>83.54742542578117</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.038107621882155</v>
+        <v>1.035299952986404</v>
       </c>
       <c r="T99">
-        <v>16.72606762757454</v>
+        <v>16.68439074436523</v>
       </c>
       <c r="U99">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V99">
-        <v>0.05992407904142603</v>
+        <v>0.06234356047819382</v>
       </c>
       <c r="W99">
-        <v>0.242232402124437</v>
+        <v>0.232232402124437</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9556,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.285352757340124</v>
+        <v>0.2968740975152087</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9567,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2682273910504193</v>
+        <v>0.2583431609835467</v>
       </c>
       <c r="C100">
-        <v>-2179.253620420093</v>
+        <v>-2135.416891157487</v>
       </c>
       <c r="D100">
-        <v>1265.144379579907</v>
+        <v>1308.981108842513</v>
       </c>
       <c r="E100">
         <v>1691.798</v>
@@ -9493,37 +9600,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M100">
-        <v>896.4704307147781</v>
+        <v>861.6794507147781</v>
       </c>
       <c r="N100">
-        <v>-643.2704307147782</v>
+        <v>-608.4794507147782</v>
       </c>
       <c r="O100">
-        <v>-135.0867904501034</v>
+        <v>-127.7806846501034</v>
       </c>
       <c r="P100">
-        <v>-508.1836402646748</v>
+        <v>-480.6987660646748</v>
       </c>
       <c r="Q100">
-        <v>49.1163597353252</v>
+        <v>76.60123393532518</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.534261432823232</v>
+        <v>1.530049929479606</v>
       </c>
       <c r="T100">
-        <v>25.08910144136181</v>
+        <v>25.02658611654784</v>
       </c>
       <c r="U100">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V100">
-        <v>0.05931260884712576</v>
+        <v>0.06170740169780407</v>
       </c>
       <c r="W100">
-        <v>0.2423899616264843</v>
+        <v>0.2323899616264843</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9638,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2824409945101226</v>
+        <v>0.2938447699895432</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9649,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2703461233836699</v>
+        <v>0.2603618933167974</v>
       </c>
       <c r="C101">
-        <v>-2223.781933404806</v>
+        <v>-2180.126531266147</v>
       </c>
       <c r="D101">
-        <v>1256.117066595193</v>
+        <v>1299.772468733853</v>
       </c>
       <c r="E101">
         <v>1727.299</v>
@@ -9575,37 +9682,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M101">
-        <v>905.6180881710512</v>
+        <v>870.4720981710512</v>
       </c>
       <c r="N101">
-        <v>-652.4180881710513</v>
+        <v>-617.2720981710513</v>
       </c>
       <c r="O101">
-        <v>-137.0077985159208</v>
+        <v>-129.6271406159208</v>
       </c>
       <c r="P101">
-        <v>-515.4102896551306</v>
+        <v>-487.6449575551305</v>
       </c>
       <c r="Q101">
-        <v>41.8897103448694</v>
+        <v>69.65504244486942</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.022722865646464</v>
+        <v>3.014299858959211</v>
       </c>
       <c r="T101">
-        <v>50.17820288272362</v>
+        <v>50.05317223309567</v>
       </c>
       <c r="U101">
-        <v>0.2576732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V101">
-        <v>0.05871349158604369</v>
+        <v>0.06108409460994748</v>
       </c>
       <c r="W101">
-        <v>0.2425443381082881</v>
+        <v>0.2325443381082881</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9720,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2795880551716367</v>
+        <v>0.2908766409997499</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/portugal/portugal_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_telecom_services.xlsx
@@ -1391,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1528,22 +1528,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07739569294365908</v>
+        <v>0.07736251053174545</v>
       </c>
       <c r="C2">
-        <v>3621.35497792876</v>
+        <v>3586.998810040751</v>
       </c>
       <c r="D2">
-        <v>3586.65497792876</v>
+        <v>3587.799810040751</v>
       </c>
       <c r="E2">
-        <v>-1787.3</v>
+        <v>-1751.799</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>35.501</v>
       </c>
       <c r="G2">
         <v>34.7</v>
@@ -1564,28 +1564,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.207211956273246</v>
       </c>
       <c r="N2">
-        <v>253.1999999999999</v>
+        <v>250.9927880437267</v>
       </c>
       <c r="O2">
-        <v>53.17199999999998</v>
+        <v>52.7084854891826</v>
       </c>
       <c r="P2">
-        <v>200.028</v>
+        <v>198.2843025545441</v>
       </c>
       <c r="Q2">
-        <v>757.328</v>
+        <v>755.584302554544</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07739569294365908</v>
+        <v>0.07764782019038122</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5370000016765089</v>
       </c>
       <c r="U2">
         <v>0.06217323332506819</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>114.7148552183063</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1610,22 +1610,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07736251053174545</v>
+        <v>0.0773293281198318</v>
       </c>
       <c r="C3">
-        <v>3586.998810040751</v>
+        <v>3552.643373228942</v>
       </c>
       <c r="D3">
-        <v>3587.799810040751</v>
+        <v>3588.945373228942</v>
       </c>
       <c r="E3">
-        <v>-1751.799</v>
+        <v>-1716.298</v>
       </c>
       <c r="F3">
-        <v>35.501</v>
+        <v>71.002</v>
       </c>
       <c r="G3">
         <v>34.7</v>
@@ -1646,28 +1646,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M3">
-        <v>2.207211956273246</v>
+        <v>4.414423912546491</v>
       </c>
       <c r="N3">
-        <v>250.9927880437267</v>
+        <v>248.7855760874534</v>
       </c>
       <c r="O3">
-        <v>52.7084854891826</v>
+        <v>52.24497097836522</v>
       </c>
       <c r="P3">
-        <v>198.2843025545441</v>
+        <v>196.5406051090882</v>
       </c>
       <c r="Q3">
-        <v>755.584302554544</v>
+        <v>753.8406051090882</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07764782019038122</v>
+        <v>0.07790509289111808</v>
       </c>
       <c r="T3">
-        <v>0.5370000016765089</v>
+        <v>0.5413379890144537</v>
       </c>
       <c r="U3">
         <v>0.06217323332506819</v>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>114.7148552183063</v>
+        <v>57.35742760915314</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1692,22 +1692,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0773293281198318</v>
+        <v>0.07729614570791815</v>
       </c>
       <c r="C4">
-        <v>3552.643373228942</v>
+        <v>3518.28866819384</v>
       </c>
       <c r="D4">
-        <v>3588.945373228942</v>
+        <v>3590.09166819384</v>
       </c>
       <c r="E4">
-        <v>-1716.298</v>
+        <v>-1680.797</v>
       </c>
       <c r="F4">
-        <v>71.002</v>
+        <v>106.503</v>
       </c>
       <c r="G4">
         <v>34.7</v>
@@ -1728,28 +1728,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M4">
-        <v>4.414423912546491</v>
+        <v>6.621635868819737</v>
       </c>
       <c r="N4">
-        <v>248.7855760874534</v>
+        <v>246.5783641311802</v>
       </c>
       <c r="O4">
-        <v>52.24497097836522</v>
+        <v>51.78145646754784</v>
       </c>
       <c r="P4">
-        <v>196.5406051090882</v>
+        <v>194.7969076636323</v>
       </c>
       <c r="Q4">
-        <v>753.8406051090882</v>
+        <v>752.0969076636322</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07790509289111808</v>
+        <v>0.07816767018362272</v>
       </c>
       <c r="T4">
-        <v>0.5413379890144537</v>
+        <v>0.5457654193902942</v>
       </c>
       <c r="U4">
         <v>0.06217323332506819</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>57.35742760915314</v>
+        <v>38.23828507276875</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1774,22 +1774,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07729614570791815</v>
+        <v>0.0772629632960045</v>
       </c>
       <c r="C5">
-        <v>3518.28866819384</v>
+        <v>3483.93469563685</v>
       </c>
       <c r="D5">
-        <v>3590.09166819384</v>
+        <v>3591.23869563685</v>
       </c>
       <c r="E5">
-        <v>-1680.797</v>
+        <v>-1645.296</v>
       </c>
       <c r="F5">
-        <v>106.503</v>
+        <v>142.004</v>
       </c>
       <c r="G5">
         <v>34.7</v>
@@ -1810,28 +1810,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M5">
-        <v>6.621635868819737</v>
+        <v>8.828847825092982</v>
       </c>
       <c r="N5">
-        <v>246.5783641311802</v>
+        <v>244.3711521749069</v>
       </c>
       <c r="O5">
-        <v>51.78145646754784</v>
+        <v>51.31794195673046</v>
       </c>
       <c r="P5">
-        <v>194.7969076636323</v>
+        <v>193.0532102181765</v>
       </c>
       <c r="Q5">
-        <v>752.0969076636322</v>
+        <v>750.3532102181764</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07816767018362272</v>
+        <v>0.07843571783638786</v>
       </c>
       <c r="T5">
-        <v>0.5457654193902942</v>
+        <v>0.5502850878989648</v>
       </c>
       <c r="U5">
         <v>0.06217323332506819</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>38.23828507276875</v>
+        <v>28.67871380457657</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1856,22 +1856,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0772629632960045</v>
+        <v>0.07722978088409087</v>
       </c>
       <c r="C6">
-        <v>3483.93469563685</v>
+        <v>3449.581456260271</v>
       </c>
       <c r="D6">
-        <v>3591.23869563685</v>
+        <v>3592.386456260272</v>
       </c>
       <c r="E6">
-        <v>-1645.296</v>
+        <v>-1609.795</v>
       </c>
       <c r="F6">
-        <v>142.004</v>
+        <v>177.505</v>
       </c>
       <c r="G6">
         <v>34.7</v>
@@ -1892,28 +1892,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M6">
-        <v>8.828847825092982</v>
+        <v>11.03605978136623</v>
       </c>
       <c r="N6">
-        <v>244.3711521749069</v>
+        <v>242.1639402186337</v>
       </c>
       <c r="O6">
-        <v>51.31794195673046</v>
+        <v>50.85442744591307</v>
       </c>
       <c r="P6">
-        <v>193.0532102181765</v>
+        <v>191.3095127727206</v>
       </c>
       <c r="Q6">
-        <v>750.3532102181764</v>
+        <v>748.6095127727206</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07843571783638786</v>
+        <v>0.07870940859763229</v>
       </c>
       <c r="T6">
-        <v>0.5502850878989648</v>
+        <v>0.5548999073236075</v>
       </c>
       <c r="U6">
         <v>0.06217323332506819</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.67871380457657</v>
+        <v>22.94297104366126</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1938,22 +1938,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07722978088409087</v>
+        <v>0.07719659847217722</v>
       </c>
       <c r="C7">
-        <v>3449.581456260271</v>
+        <v>3415.228950767304</v>
       </c>
       <c r="D7">
-        <v>3592.386456260272</v>
+        <v>3593.534950767305</v>
       </c>
       <c r="E7">
-        <v>-1609.795</v>
+        <v>-1574.294</v>
       </c>
       <c r="F7">
-        <v>177.505</v>
+        <v>213.006</v>
       </c>
       <c r="G7">
         <v>34.7</v>
@@ -1974,28 +1974,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M7">
-        <v>11.03605978136623</v>
+        <v>13.24327173763947</v>
       </c>
       <c r="N7">
-        <v>242.1639402186337</v>
+        <v>239.9567282623605</v>
       </c>
       <c r="O7">
-        <v>50.85442744591307</v>
+        <v>50.39091293509569</v>
       </c>
       <c r="P7">
-        <v>191.3095127727206</v>
+        <v>189.5658153272648</v>
       </c>
       <c r="Q7">
-        <v>748.6095127727206</v>
+        <v>746.8658153272647</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07870940859763229</v>
+        <v>0.07898892256656274</v>
       </c>
       <c r="T7">
-        <v>0.5548999073236075</v>
+        <v>0.5596129143955828</v>
       </c>
       <c r="U7">
         <v>0.06217323332506819</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.94297104366126</v>
+        <v>19.11914253638438</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2020,22 +2020,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07719659847217722</v>
+        <v>0.07716341606026357</v>
       </c>
       <c r="C8">
-        <v>3415.228950767304</v>
+        <v>3380.877179862045</v>
       </c>
       <c r="D8">
-        <v>3593.534950767305</v>
+        <v>3594.684179862045</v>
       </c>
       <c r="E8">
-        <v>-1574.294</v>
+        <v>-1538.793</v>
       </c>
       <c r="F8">
-        <v>213.006</v>
+        <v>248.507</v>
       </c>
       <c r="G8">
         <v>34.7</v>
@@ -2056,28 +2056,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M8">
-        <v>13.24327173763947</v>
+        <v>15.45048369391272</v>
       </c>
       <c r="N8">
-        <v>239.9567282623605</v>
+        <v>237.7495163060872</v>
       </c>
       <c r="O8">
-        <v>50.39091293509569</v>
+        <v>49.92739842427831</v>
       </c>
       <c r="P8">
-        <v>189.5658153272648</v>
+        <v>187.8221178818089</v>
       </c>
       <c r="Q8">
-        <v>746.8658153272647</v>
+        <v>745.1221178818089</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07898892256656274</v>
+        <v>0.0792744475885885</v>
       </c>
       <c r="T8">
-        <v>0.5596129143955828</v>
+        <v>0.5644272764583534</v>
       </c>
       <c r="U8">
         <v>0.06217323332506819</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.11914253638438</v>
+        <v>16.38783645975804</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2102,22 +2102,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07716341606026356</v>
+        <v>0.07713023364834992</v>
       </c>
       <c r="C9">
-        <v>3380.877179862045</v>
+        <v>3346.526144249493</v>
       </c>
       <c r="D9">
-        <v>3594.684179862045</v>
+        <v>3595.834144249493</v>
       </c>
       <c r="E9">
-        <v>-1538.793</v>
+        <v>-1503.292</v>
       </c>
       <c r="F9">
-        <v>248.507</v>
+        <v>284.008</v>
       </c>
       <c r="G9">
         <v>34.7</v>
@@ -2138,28 +2138,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M9">
-        <v>15.45048369391272</v>
+        <v>17.65769565018596</v>
       </c>
       <c r="N9">
-        <v>237.7495163060872</v>
+        <v>235.542304349814</v>
       </c>
       <c r="O9">
-        <v>49.92739842427831</v>
+        <v>49.46388391346093</v>
       </c>
       <c r="P9">
-        <v>187.8221178818089</v>
+        <v>186.078420436353</v>
       </c>
       <c r="Q9">
-        <v>745.1221178818089</v>
+        <v>743.3784204363531</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0792744475885885</v>
+        <v>0.07956617967631045</v>
       </c>
       <c r="T9">
-        <v>0.5644272764583534</v>
+        <v>0.5693462985659669</v>
       </c>
       <c r="U9">
         <v>0.06217323332506819</v>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.38783645975803</v>
+        <v>14.33935690228829</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2184,22 +2184,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07713023364834992</v>
+        <v>0.07720370123643627</v>
       </c>
       <c r="C10">
-        <v>3346.526144249493</v>
+        <v>3308.480051363006</v>
       </c>
       <c r="D10">
-        <v>3595.834144249493</v>
+        <v>3593.289051363006</v>
       </c>
       <c r="E10">
-        <v>-1503.292</v>
+        <v>-1467.791</v>
       </c>
       <c r="F10">
-        <v>284.008</v>
+        <v>319.509</v>
       </c>
       <c r="G10">
         <v>34.7</v>
@@ -2220,45 +2220,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M10">
-        <v>17.65769565018596</v>
+        <v>20.34417110645921</v>
       </c>
       <c r="N10">
-        <v>235.542304349814</v>
+        <v>232.8558288935407</v>
       </c>
       <c r="O10">
-        <v>49.46388391346093</v>
+        <v>48.89972406764355</v>
       </c>
       <c r="P10">
-        <v>186.078420436353</v>
+        <v>183.9561048258972</v>
       </c>
       <c r="Q10">
-        <v>743.3784204363531</v>
+        <v>741.2561048258972</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07956617967631045</v>
+        <v>0.07986432345826805</v>
       </c>
       <c r="T10">
-        <v>0.5693462985659669</v>
+        <v>0.5743734310495718</v>
       </c>
       <c r="U10">
-        <v>0.06217323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V10">
         <v>0.21</v>
       </c>
       <c r="W10">
-        <v>0.04911685432680387</v>
+        <v>0.05030185432680388</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>14.33935690228829</v>
+        <v>12.44582532633191</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2266,22 +2266,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07720370123643627</v>
+        <v>0.07718236882452263</v>
       </c>
       <c r="C11">
-        <v>3308.480051363006</v>
+        <v>3273.71768585173</v>
       </c>
       <c r="D11">
-        <v>3593.289051363006</v>
+        <v>3594.02768585173</v>
       </c>
       <c r="E11">
-        <v>-1467.791</v>
+        <v>-1432.29</v>
       </c>
       <c r="F11">
-        <v>319.509</v>
+        <v>355.0099999999999</v>
       </c>
       <c r="G11">
         <v>34.7</v>
@@ -2302,28 +2302,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M11">
-        <v>20.34417110645921</v>
+        <v>22.60463456273245</v>
       </c>
       <c r="N11">
-        <v>232.8558288935407</v>
+        <v>230.5953654372675</v>
       </c>
       <c r="O11">
-        <v>48.89972406764355</v>
+        <v>48.42502674182617</v>
       </c>
       <c r="P11">
-        <v>183.9561048258972</v>
+        <v>182.1703386954413</v>
       </c>
       <c r="Q11">
-        <v>741.2561048258972</v>
+        <v>739.4703386954412</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07986432345826805</v>
+        <v>0.0801690926576025</v>
       </c>
       <c r="T11">
-        <v>0.5743734310495718</v>
+        <v>0.579512277588368</v>
       </c>
       <c r="U11">
         <v>0.06367323332506819</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.44582532633191</v>
+        <v>11.20124279369872</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2348,22 +2348,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07718236882452263</v>
+        <v>0.07716103641260899</v>
       </c>
       <c r="C12">
-        <v>3273.71768585173</v>
+        <v>3238.955624069472</v>
       </c>
       <c r="D12">
-        <v>3594.02768585173</v>
+        <v>3594.766624069473</v>
       </c>
       <c r="E12">
-        <v>-1432.29</v>
+        <v>-1396.789</v>
       </c>
       <c r="F12">
-        <v>355.01</v>
+        <v>390.511</v>
       </c>
       <c r="G12">
         <v>34.7</v>
@@ -2384,28 +2384,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M12">
-        <v>22.60463456273246</v>
+        <v>24.8650980190057</v>
       </c>
       <c r="N12">
-        <v>230.5953654372675</v>
+        <v>228.3349019809942</v>
       </c>
       <c r="O12">
-        <v>48.42502674182617</v>
+        <v>47.95032941600878</v>
       </c>
       <c r="P12">
-        <v>182.1703386954413</v>
+        <v>180.3845725649854</v>
       </c>
       <c r="Q12">
-        <v>739.4703386954412</v>
+        <v>737.6845725649854</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0801690926576025</v>
+        <v>0.08048071060298939</v>
       </c>
       <c r="T12">
-        <v>0.579512277588368</v>
+        <v>0.5847666038246652</v>
       </c>
       <c r="U12">
         <v>0.06367323332506819</v>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.20124279369872</v>
+        <v>10.18294799427156</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2430,22 +2430,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07716103641260899</v>
+        <v>0.07730086400069534</v>
       </c>
       <c r="C13">
-        <v>3238.955624069472</v>
+        <v>3198.616628899476</v>
       </c>
       <c r="D13">
-        <v>3594.766624069473</v>
+        <v>3589.928628899476</v>
       </c>
       <c r="E13">
-        <v>-1396.789</v>
+        <v>-1361.288</v>
       </c>
       <c r="F13">
-        <v>390.511</v>
+        <v>426.012</v>
       </c>
       <c r="G13">
         <v>34.7</v>
@@ -2466,45 +2466,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M13">
-        <v>24.8650980190057</v>
+        <v>27.84978187527895</v>
       </c>
       <c r="N13">
-        <v>228.3349019809942</v>
+        <v>225.350218124721</v>
       </c>
       <c r="O13">
-        <v>47.95032941600878</v>
+        <v>47.3235458061914</v>
       </c>
       <c r="P13">
-        <v>180.3845725649854</v>
+        <v>178.0266723185296</v>
       </c>
       <c r="Q13">
-        <v>737.6845725649854</v>
+        <v>735.3266723185295</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08048071060298939</v>
+        <v>0.08079941077440782</v>
       </c>
       <c r="T13">
-        <v>0.5847666038246652</v>
+        <v>0.5901403465663327</v>
       </c>
       <c r="U13">
-        <v>0.06367323332506819</v>
+        <v>0.06537323332506818</v>
       </c>
       <c r="V13">
         <v>0.21</v>
       </c>
       <c r="W13">
-        <v>0.05030185432680388</v>
+        <v>0.05164485432680387</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.18294799427156</v>
+        <v>9.091633145778951</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2512,22 +2512,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07730086400069534</v>
+        <v>0.07729296158878171</v>
       </c>
       <c r="C14">
-        <v>3198.616628899476</v>
+        <v>3163.388702914172</v>
       </c>
       <c r="D14">
-        <v>3589.928628899476</v>
+        <v>3590.201702914172</v>
       </c>
       <c r="E14">
-        <v>-1361.288</v>
+        <v>-1325.787</v>
       </c>
       <c r="F14">
-        <v>426.012</v>
+        <v>461.513</v>
       </c>
       <c r="G14">
         <v>34.7</v>
@@ -2548,28 +2548,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M14">
-        <v>27.84978187527895</v>
+        <v>30.17059703155219</v>
       </c>
       <c r="N14">
-        <v>225.350218124721</v>
+        <v>223.0294029684478</v>
       </c>
       <c r="O14">
-        <v>47.3235458061914</v>
+        <v>46.83617462337403</v>
       </c>
       <c r="P14">
-        <v>178.0266723185296</v>
+        <v>176.1932283450737</v>
       </c>
       <c r="Q14">
-        <v>735.3266723185295</v>
+        <v>733.4932283450737</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08079941077440782</v>
+        <v>0.08112543738654851</v>
       </c>
       <c r="T14">
-        <v>0.5901403465663327</v>
+        <v>0.5956376236239008</v>
       </c>
       <c r="U14">
         <v>0.06537323332506818</v>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.091633145778951</v>
+        <v>8.392276749949801</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2594,22 +2594,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07729296158878171</v>
+        <v>0.07728505917686805</v>
       </c>
       <c r="C15">
-        <v>3163.388702914172</v>
+        <v>3128.160818475704</v>
       </c>
       <c r="D15">
-        <v>3590.201702914172</v>
+        <v>3590.474818475705</v>
       </c>
       <c r="E15">
-        <v>-1325.787</v>
+        <v>-1290.286</v>
       </c>
       <c r="F15">
-        <v>461.513</v>
+        <v>497.014</v>
       </c>
       <c r="G15">
         <v>34.7</v>
@@ -2630,28 +2630,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M15">
-        <v>30.17059703155219</v>
+        <v>32.49141218782544</v>
       </c>
       <c r="N15">
-        <v>223.0294029684478</v>
+        <v>220.7085878121745</v>
       </c>
       <c r="O15">
-        <v>46.83617462337403</v>
+        <v>46.34880344055664</v>
       </c>
       <c r="P15">
-        <v>176.1932283450737</v>
+        <v>174.3597843716178</v>
       </c>
       <c r="Q15">
-        <v>733.4932283450737</v>
+        <v>731.6597843716178</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08112543738654851</v>
+        <v>0.08145904601292502</v>
       </c>
       <c r="T15">
-        <v>0.5956376236239008</v>
+        <v>0.6012627443339703</v>
       </c>
       <c r="U15">
         <v>0.06537323332506818</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.392276749949801</v>
+        <v>7.792828410667672</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2676,22 +2676,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07728505917686805</v>
+        <v>0.07737195676495441</v>
       </c>
       <c r="C16">
-        <v>3128.160818475704</v>
+        <v>3089.658829514847</v>
       </c>
       <c r="D16">
-        <v>3590.474818475705</v>
+        <v>3587.473829514847</v>
       </c>
       <c r="E16">
-        <v>-1290.286</v>
+        <v>-1254.785</v>
       </c>
       <c r="F16">
-        <v>497.014</v>
+        <v>532.5150000000001</v>
       </c>
       <c r="G16">
         <v>34.7</v>
@@ -2712,45 +2712,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M16">
-        <v>32.49141218782544</v>
+        <v>35.23823934409869</v>
       </c>
       <c r="N16">
-        <v>220.7085878121745</v>
+        <v>217.9617606559012</v>
       </c>
       <c r="O16">
-        <v>46.34880344055664</v>
+        <v>45.77196973773925</v>
       </c>
       <c r="P16">
-        <v>174.3597843716178</v>
+        <v>172.189790918162</v>
       </c>
       <c r="Q16">
-        <v>731.6597843716178</v>
+        <v>729.4897909181619</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08145904601292502</v>
+        <v>0.0818005042540398</v>
       </c>
       <c r="T16">
-        <v>0.6012627443339703</v>
+        <v>0.6070202208254533</v>
       </c>
       <c r="U16">
-        <v>0.06537323332506818</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V16">
         <v>0.21</v>
       </c>
       <c r="W16">
-        <v>0.05164485432680387</v>
+        <v>0.05227685432680387</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.792828410667672</v>
+        <v>7.185376020848302</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2758,22 +2758,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0773719567649544</v>
+        <v>0.07737037435304076</v>
       </c>
       <c r="C17">
-        <v>3089.658829514847</v>
+        <v>3054.212432914867</v>
       </c>
       <c r="D17">
-        <v>3587.473829514847</v>
+        <v>3587.528432914867</v>
       </c>
       <c r="E17">
-        <v>-1254.785</v>
+        <v>-1219.284</v>
       </c>
       <c r="F17">
-        <v>532.515</v>
+        <v>568.016</v>
       </c>
       <c r="G17">
         <v>34.7</v>
@@ -2794,28 +2794,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M17">
-        <v>35.23823934409869</v>
+        <v>37.58745530037193</v>
       </c>
       <c r="N17">
-        <v>217.9617606559012</v>
+        <v>215.612544699628</v>
       </c>
       <c r="O17">
-        <v>45.77196973773925</v>
+        <v>45.27863438692188</v>
       </c>
       <c r="P17">
-        <v>172.189790918162</v>
+        <v>170.3339103127061</v>
       </c>
       <c r="Q17">
-        <v>729.4897909181619</v>
+        <v>727.6339103127061</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0818005042540398</v>
+        <v>0.08215009245327635</v>
       </c>
       <c r="T17">
-        <v>0.6070202208254533</v>
+        <v>0.6129147800905429</v>
       </c>
       <c r="U17">
         <v>0.06617323332506819</v>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.185376020848302</v>
+        <v>6.736290019545285</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2840,22 +2840,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07737037435304076</v>
+        <v>0.07736879194112711</v>
       </c>
       <c r="C18">
-        <v>3054.212432914867</v>
+        <v>3018.766037977102</v>
       </c>
       <c r="D18">
-        <v>3587.528432914867</v>
+        <v>3587.583037977103</v>
       </c>
       <c r="E18">
-        <v>-1219.284</v>
+        <v>-1183.783</v>
       </c>
       <c r="F18">
-        <v>568.016</v>
+        <v>603.5170000000001</v>
       </c>
       <c r="G18">
         <v>34.7</v>
@@ -2876,28 +2876,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M18">
-        <v>37.58745530037193</v>
+        <v>39.93667125664518</v>
       </c>
       <c r="N18">
-        <v>215.612544699628</v>
+        <v>213.2633287433547</v>
       </c>
       <c r="O18">
-        <v>45.27863438692188</v>
+        <v>44.7852990361045</v>
       </c>
       <c r="P18">
-        <v>170.3339103127061</v>
+        <v>168.4780297072502</v>
       </c>
       <c r="Q18">
-        <v>727.6339103127061</v>
+        <v>725.7780297072502</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08215009245327635</v>
+        <v>0.08250810446454272</v>
       </c>
       <c r="T18">
-        <v>0.6129147800905429</v>
+        <v>0.6189513769282855</v>
       </c>
       <c r="U18">
         <v>0.06617323332506819</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.736290019545285</v>
+        <v>6.340037665454384</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2922,22 +2922,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07736879194112711</v>
+        <v>0.07750940952921347</v>
       </c>
       <c r="C19">
-        <v>3018.766037977102</v>
+        <v>2978.419158558423</v>
       </c>
       <c r="D19">
-        <v>3587.583037977103</v>
+        <v>3582.737158558423</v>
       </c>
       <c r="E19">
-        <v>-1183.783</v>
+        <v>-1148.282</v>
       </c>
       <c r="F19">
-        <v>603.5170000000001</v>
+        <v>639.018</v>
       </c>
       <c r="G19">
         <v>34.7</v>
@@ -2958,45 +2958,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M19">
-        <v>39.93667125664518</v>
+        <v>42.92490521291843</v>
       </c>
       <c r="N19">
-        <v>213.2633287433547</v>
+        <v>210.2750947870815</v>
       </c>
       <c r="O19">
-        <v>44.7852990361045</v>
+        <v>44.15776990528712</v>
       </c>
       <c r="P19">
-        <v>168.4780297072502</v>
+        <v>166.1173248817944</v>
       </c>
       <c r="Q19">
-        <v>725.7780297072502</v>
+        <v>723.4173248817943</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08250810446454272</v>
+        <v>0.08287484847608387</v>
       </c>
       <c r="T19">
-        <v>0.6189513769282855</v>
+        <v>0.6251352078352411</v>
       </c>
       <c r="U19">
-        <v>0.06617323332506819</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V19">
         <v>0.21</v>
       </c>
       <c r="W19">
-        <v>0.05227685432680387</v>
+        <v>0.05306685432680387</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.340037665454384</v>
+        <v>5.898673479744769</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3004,22 +3004,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07750940952921348</v>
+        <v>0.07751572711729984</v>
       </c>
       <c r="C20">
-        <v>2978.419158558423</v>
+        <v>2942.700752873417</v>
       </c>
       <c r="D20">
-        <v>3582.737158558423</v>
+        <v>3582.519752873417</v>
       </c>
       <c r="E20">
-        <v>-1148.282</v>
+        <v>-1112.781</v>
       </c>
       <c r="F20">
-        <v>639.0179999999999</v>
+        <v>674.519</v>
       </c>
       <c r="G20">
         <v>34.7</v>
@@ -3040,28 +3040,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M20">
-        <v>42.92490521291842</v>
+        <v>45.30962216919167</v>
       </c>
       <c r="N20">
-        <v>210.2750947870815</v>
+        <v>207.8903778308083</v>
       </c>
       <c r="O20">
-        <v>44.15776990528712</v>
+        <v>43.65697934446973</v>
       </c>
       <c r="P20">
-        <v>166.1173248817944</v>
+        <v>164.2333984863385</v>
       </c>
       <c r="Q20">
-        <v>723.4173248817943</v>
+        <v>721.5333984863385</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08287484847608387</v>
+        <v>0.0832506478953174</v>
       </c>
       <c r="T20">
-        <v>0.6251352078352411</v>
+        <v>0.6314717259250847</v>
       </c>
       <c r="U20">
         <v>0.06717323332506819</v>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.898673479744771</v>
+        <v>5.588216980810834</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3086,22 +3086,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07751572711729984</v>
+        <v>0.07752204470538619</v>
       </c>
       <c r="C21">
-        <v>2942.700752873417</v>
+        <v>2906.982373571794</v>
       </c>
       <c r="D21">
-        <v>3582.519752873417</v>
+        <v>3582.302373571794</v>
       </c>
       <c r="E21">
-        <v>-1112.781</v>
+        <v>-1077.28</v>
       </c>
       <c r="F21">
-        <v>674.519</v>
+        <v>710.02</v>
       </c>
       <c r="G21">
         <v>34.7</v>
@@ -3122,28 +3122,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M21">
-        <v>45.30962216919167</v>
+        <v>47.69433912546491</v>
       </c>
       <c r="N21">
-        <v>207.8903778308083</v>
+        <v>205.505660874535</v>
       </c>
       <c r="O21">
-        <v>43.65697934446973</v>
+        <v>43.15618878365235</v>
       </c>
       <c r="P21">
-        <v>164.2333984863385</v>
+        <v>162.3494720908827</v>
       </c>
       <c r="Q21">
-        <v>721.5333984863385</v>
+        <v>719.6494720908827</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0832506478953174</v>
+        <v>0.08363584230003177</v>
       </c>
       <c r="T21">
-        <v>0.6314717259250847</v>
+        <v>0.6379666569671743</v>
       </c>
       <c r="U21">
         <v>0.06717323332506819</v>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.588216980810834</v>
+        <v>5.308806131770293</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3168,22 +3168,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07752204470538619</v>
+        <v>0.07752836229347254</v>
       </c>
       <c r="C22">
-        <v>2906.982373571794</v>
+        <v>2871.264020648753</v>
       </c>
       <c r="D22">
-        <v>3582.302373571794</v>
+        <v>3582.085020648753</v>
       </c>
       <c r="E22">
-        <v>-1077.28</v>
+        <v>-1041.779</v>
       </c>
       <c r="F22">
-        <v>710.02</v>
+        <v>745.5210000000001</v>
       </c>
       <c r="G22">
         <v>34.7</v>
@@ -3204,28 +3204,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M22">
-        <v>47.69433912546491</v>
+        <v>50.07905608173817</v>
       </c>
       <c r="N22">
-        <v>205.505660874535</v>
+        <v>203.1209439182618</v>
       </c>
       <c r="O22">
-        <v>43.15618878365235</v>
+        <v>42.65539822283497</v>
       </c>
       <c r="P22">
-        <v>162.3494720908827</v>
+        <v>160.4655456954268</v>
       </c>
       <c r="Q22">
-        <v>719.6494720908827</v>
+        <v>717.7655456954267</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08363584230003177</v>
+        <v>0.08403078846182749</v>
       </c>
       <c r="T22">
-        <v>0.6379666569671743</v>
+        <v>0.6446260166432407</v>
       </c>
       <c r="U22">
         <v>0.06717323332506819</v>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.308806131770293</v>
+        <v>5.056005839781231</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3250,22 +3250,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07752836229347254</v>
+        <v>0.07753467988155888</v>
       </c>
       <c r="C23">
-        <v>2871.264020648753</v>
+        <v>2835.545694099491</v>
       </c>
       <c r="D23">
-        <v>3582.085020648753</v>
+        <v>3581.867694099491</v>
       </c>
       <c r="E23">
-        <v>-1041.779</v>
+        <v>-1006.278</v>
       </c>
       <c r="F23">
-        <v>745.521</v>
+        <v>781.0219999999999</v>
       </c>
       <c r="G23">
         <v>34.7</v>
@@ -3286,28 +3286,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M23">
-        <v>50.07905608173816</v>
+        <v>52.4637730380114</v>
       </c>
       <c r="N23">
-        <v>203.1209439182618</v>
+        <v>200.7362269619885</v>
       </c>
       <c r="O23">
-        <v>42.65539822283498</v>
+        <v>42.15460766201759</v>
       </c>
       <c r="P23">
-        <v>160.4655456954268</v>
+        <v>158.581619299971</v>
       </c>
       <c r="Q23">
-        <v>717.7655456954268</v>
+        <v>715.8816192999709</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08403078846182749</v>
+        <v>0.08443586144828466</v>
       </c>
       <c r="T23">
-        <v>0.6446260166432407</v>
+        <v>0.6514561291315141</v>
       </c>
       <c r="U23">
         <v>0.06717323332506819</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.056005839781232</v>
+        <v>4.826187392518449</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3332,22 +3332,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07753467988155888</v>
+        <v>0.07754099746964524</v>
       </c>
       <c r="C24">
-        <v>2835.545694099491</v>
+        <v>2799.827393919209</v>
       </c>
       <c r="D24">
-        <v>3581.867694099491</v>
+        <v>3581.65039391921</v>
       </c>
       <c r="E24">
-        <v>-1006.278</v>
+        <v>-970.7769999999999</v>
       </c>
       <c r="F24">
-        <v>781.0219999999999</v>
+        <v>816.523</v>
       </c>
       <c r="G24">
         <v>34.7</v>
@@ -3368,28 +3368,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M24">
-        <v>52.4637730380114</v>
+        <v>54.84848999428466</v>
       </c>
       <c r="N24">
-        <v>200.7362269619885</v>
+        <v>198.3515100057153</v>
       </c>
       <c r="O24">
-        <v>42.15460766201759</v>
+        <v>41.65381710120021</v>
       </c>
       <c r="P24">
-        <v>158.581619299971</v>
+        <v>156.6976929045151</v>
       </c>
       <c r="Q24">
-        <v>715.8816192999709</v>
+        <v>713.997692904515</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08443586144828466</v>
+        <v>0.08485145581101344</v>
       </c>
       <c r="T24">
-        <v>0.6514561291315141</v>
+        <v>0.6584636471389634</v>
       </c>
       <c r="U24">
         <v>0.06717323332506819</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.826187392518449</v>
+        <v>4.616353158061124</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3414,22 +3414,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07754099746964524</v>
+        <v>0.07802131505773159</v>
       </c>
       <c r="C25">
-        <v>2799.827393919209</v>
+        <v>2747.882207767366</v>
       </c>
       <c r="D25">
-        <v>3581.65039391921</v>
+        <v>3565.206207767366</v>
       </c>
       <c r="E25">
-        <v>-970.7769999999999</v>
+        <v>-935.276</v>
       </c>
       <c r="F25">
-        <v>816.523</v>
+        <v>852.024</v>
       </c>
       <c r="G25">
         <v>34.7</v>
@@ -3450,45 +3450,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M25">
-        <v>54.84848999428466</v>
+        <v>59.36326695055789</v>
       </c>
       <c r="N25">
-        <v>198.3515100057153</v>
+        <v>193.836733049442</v>
       </c>
       <c r="O25">
-        <v>41.65381710120021</v>
+        <v>40.70571394038283</v>
       </c>
       <c r="P25">
-        <v>156.6976929045151</v>
+        <v>153.1310191090592</v>
       </c>
       <c r="Q25">
-        <v>713.997692904515</v>
+        <v>710.4310191090592</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08485145581101344</v>
+        <v>0.08527798686749824</v>
       </c>
       <c r="T25">
-        <v>0.6584636471389634</v>
+        <v>0.6656555735150298</v>
       </c>
       <c r="U25">
-        <v>0.06717323332506819</v>
+        <v>0.06967323332506818</v>
       </c>
       <c r="V25">
         <v>0.21</v>
       </c>
       <c r="W25">
-        <v>0.05306685432680387</v>
+        <v>0.05504185432680386</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.616353158061124</v>
+        <v>4.265263908249585</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3496,22 +3496,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07802131505773159</v>
+        <v>0.07804738264581795</v>
       </c>
       <c r="C26">
-        <v>2747.882207767366</v>
+        <v>2711.493074771136</v>
       </c>
       <c r="D26">
-        <v>3565.206207767366</v>
+        <v>3564.318074771136</v>
       </c>
       <c r="E26">
-        <v>-935.276</v>
+        <v>-899.775</v>
       </c>
       <c r="F26">
-        <v>852.024</v>
+        <v>887.525</v>
       </c>
       <c r="G26">
         <v>34.7</v>
@@ -3532,28 +3532,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M26">
-        <v>59.36326695055789</v>
+        <v>61.83673640683114</v>
       </c>
       <c r="N26">
-        <v>193.836733049442</v>
+        <v>191.3632635931688</v>
       </c>
       <c r="O26">
-        <v>40.70571394038283</v>
+        <v>40.18628535456545</v>
       </c>
       <c r="P26">
-        <v>153.1310191090592</v>
+        <v>151.1769782386033</v>
       </c>
       <c r="Q26">
-        <v>710.4310191090592</v>
+        <v>708.4769782386034</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08527798686749824</v>
+        <v>0.08571589208548931</v>
       </c>
       <c r="T26">
-        <v>0.6656555735150298</v>
+        <v>0.6730392845944579</v>
       </c>
       <c r="U26">
         <v>0.06967323332506818</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.265263908249585</v>
+        <v>4.094653351919601</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3578,22 +3578,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07804738264581795</v>
+        <v>0.0787923502339043</v>
       </c>
       <c r="C27">
-        <v>2711.493074771136</v>
+        <v>2650.796430606559</v>
       </c>
       <c r="D27">
-        <v>3564.318074771136</v>
+        <v>3539.122430606559</v>
       </c>
       <c r="E27">
-        <v>-899.775</v>
+        <v>-864.274</v>
       </c>
       <c r="F27">
-        <v>887.525</v>
+        <v>923.026</v>
       </c>
       <c r="G27">
         <v>34.7</v>
@@ -3614,45 +3614,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M27">
-        <v>61.83673640683114</v>
+        <v>67.54079686310439</v>
       </c>
       <c r="N27">
-        <v>191.3632635931688</v>
+        <v>185.6592031368955</v>
       </c>
       <c r="O27">
-        <v>40.18628535456545</v>
+        <v>38.98843265874806</v>
       </c>
       <c r="P27">
-        <v>151.1769782386033</v>
+        <v>146.6707704781475</v>
       </c>
       <c r="Q27">
-        <v>708.4769782386034</v>
+        <v>703.9707704781474</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08571589208548931</v>
+        <v>0.0861656325796423</v>
       </c>
       <c r="T27">
-        <v>0.6730392845944579</v>
+        <v>0.6806225554327896</v>
       </c>
       <c r="U27">
-        <v>0.06967323332506818</v>
+        <v>0.07317323332506818</v>
       </c>
       <c r="V27">
         <v>0.21</v>
       </c>
       <c r="W27">
-        <v>0.05504185432680386</v>
+        <v>0.05780685432680387</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.094653351919601</v>
+        <v>3.748845316604724</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3660,22 +3660,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0787923502339043</v>
+        <v>0.07884606782199066</v>
       </c>
       <c r="C28">
-        <v>2650.796430606559</v>
+        <v>2613.492402834231</v>
       </c>
       <c r="D28">
-        <v>3539.122430606559</v>
+        <v>3537.319402834231</v>
       </c>
       <c r="E28">
-        <v>-864.274</v>
+        <v>-828.7729999999999</v>
       </c>
       <c r="F28">
-        <v>923.026</v>
+        <v>958.527</v>
       </c>
       <c r="G28">
         <v>34.7</v>
@@ -3696,28 +3696,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M28">
-        <v>67.54079686310439</v>
+        <v>70.13851981937763</v>
       </c>
       <c r="N28">
-        <v>185.6592031368955</v>
+        <v>183.0614801806223</v>
       </c>
       <c r="O28">
-        <v>38.98843265874806</v>
+        <v>38.44291083793068</v>
       </c>
       <c r="P28">
-        <v>146.6707704781475</v>
+        <v>144.6185693426916</v>
       </c>
       <c r="Q28">
-        <v>703.9707704781474</v>
+        <v>701.9185693426916</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0861656325796423</v>
+        <v>0.08662769473116935</v>
       </c>
       <c r="T28">
-        <v>0.6806225554327896</v>
+        <v>0.6884135871160071</v>
       </c>
       <c r="U28">
         <v>0.07317323332506818</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.748845316604724</v>
+        <v>3.609999193767512</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3742,22 +3742,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07884606782199066</v>
+        <v>0.07951914541007701</v>
       </c>
       <c r="C29">
-        <v>2613.492402834231</v>
+        <v>2555.554327562993</v>
       </c>
       <c r="D29">
-        <v>3537.319402834231</v>
+        <v>3514.882327562993</v>
       </c>
       <c r="E29">
-        <v>-828.7729999999999</v>
+        <v>-793.2719999999999</v>
       </c>
       <c r="F29">
-        <v>958.527</v>
+        <v>994.028</v>
       </c>
       <c r="G29">
         <v>34.7</v>
@@ -3778,45 +3778,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M29">
-        <v>70.13851981937763</v>
+        <v>75.51952117565088</v>
       </c>
       <c r="N29">
-        <v>183.0614801806223</v>
+        <v>177.6804788243491</v>
       </c>
       <c r="O29">
-        <v>38.44291083793068</v>
+        <v>37.3129005531133</v>
       </c>
       <c r="P29">
-        <v>144.6185693426916</v>
+        <v>140.3675782712357</v>
       </c>
       <c r="Q29">
-        <v>701.9185693426916</v>
+        <v>697.6675782712357</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08662769473116935</v>
+        <v>0.08710259194246102</v>
       </c>
       <c r="T29">
-        <v>0.6884135871160071</v>
+        <v>0.6964210363459805</v>
       </c>
       <c r="U29">
-        <v>0.07317323332506818</v>
+        <v>0.07597323332506818</v>
       </c>
       <c r="V29">
         <v>0.21</v>
       </c>
       <c r="W29">
-        <v>0.05780685432680387</v>
+        <v>0.06001885432680387</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.609999193767512</v>
+        <v>3.352775495107841</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3824,22 +3824,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07951914541007701</v>
+        <v>0.07959498299816337</v>
       </c>
       <c r="C30">
-        <v>2555.554327562993</v>
+        <v>2517.54310706958</v>
       </c>
       <c r="D30">
-        <v>3514.882327562993</v>
+        <v>3512.372107069581</v>
       </c>
       <c r="E30">
-        <v>-793.2719999999999</v>
+        <v>-757.771</v>
       </c>
       <c r="F30">
-        <v>994.028</v>
+        <v>1029.529</v>
       </c>
       <c r="G30">
         <v>34.7</v>
@@ -3860,28 +3860,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M30">
-        <v>75.51952117565088</v>
+        <v>78.21664693192412</v>
       </c>
       <c r="N30">
-        <v>177.6804788243491</v>
+        <v>174.9833530680758</v>
       </c>
       <c r="O30">
-        <v>37.3129005531133</v>
+        <v>36.74650414429592</v>
       </c>
       <c r="P30">
-        <v>140.3675782712357</v>
+        <v>138.2368489237799</v>
       </c>
       <c r="Q30">
-        <v>697.6675782712357</v>
+        <v>695.5368489237799</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08710259194246102</v>
+        <v>0.08759086653998627</v>
       </c>
       <c r="T30">
-        <v>0.6964210363459805</v>
+        <v>0.7046540475260941</v>
       </c>
       <c r="U30">
         <v>0.07597323332506818</v>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.352775495107841</v>
+        <v>3.237162547000674</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3906,22 +3906,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07959498299816337</v>
+        <v>0.07967082058624972</v>
       </c>
       <c r="C31">
-        <v>2517.54310706958</v>
+        <v>2479.535469461409</v>
       </c>
       <c r="D31">
-        <v>3512.372107069581</v>
+        <v>3509.865469461409</v>
       </c>
       <c r="E31">
-        <v>-757.771</v>
+        <v>-722.27</v>
       </c>
       <c r="F31">
-        <v>1029.529</v>
+        <v>1065.03</v>
       </c>
       <c r="G31">
         <v>34.7</v>
@@ -3942,28 +3942,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M31">
-        <v>78.21664693192412</v>
+        <v>80.91377268819737</v>
       </c>
       <c r="N31">
-        <v>174.9833530680758</v>
+        <v>172.2862273118026</v>
       </c>
       <c r="O31">
-        <v>36.74650414429592</v>
+        <v>36.18010773547854</v>
       </c>
       <c r="P31">
-        <v>138.2368489237799</v>
+        <v>136.106119576324</v>
       </c>
       <c r="Q31">
-        <v>695.5368489237799</v>
+        <v>693.406119576324</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08759086653998627</v>
+        <v>0.08809309184029795</v>
       </c>
       <c r="T31">
-        <v>0.7046540475260941</v>
+        <v>0.713122287597068</v>
       </c>
       <c r="U31">
         <v>0.07597323332506818</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.237162547000674</v>
+        <v>3.129257128767318</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3988,22 +3988,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07967082058624972</v>
+        <v>0.07974665817433607</v>
       </c>
       <c r="C32">
-        <v>2479.535469461409</v>
+        <v>2441.531407073071</v>
       </c>
       <c r="D32">
-        <v>3509.865469461409</v>
+        <v>3507.362407073071</v>
       </c>
       <c r="E32">
-        <v>-722.27</v>
+        <v>-686.769</v>
       </c>
       <c r="F32">
-        <v>1065.03</v>
+        <v>1100.531</v>
       </c>
       <c r="G32">
         <v>34.7</v>
@@ -4024,28 +4024,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M32">
-        <v>80.91377268819737</v>
+        <v>83.61089844447061</v>
       </c>
       <c r="N32">
-        <v>172.2862273118026</v>
+        <v>169.5891015555293</v>
       </c>
       <c r="O32">
-        <v>36.18010773547854</v>
+        <v>35.61371132666116</v>
       </c>
       <c r="P32">
-        <v>136.106119576324</v>
+        <v>133.9753902288682</v>
       </c>
       <c r="Q32">
-        <v>693.406119576324</v>
+        <v>691.2753902288681</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08809309184029795</v>
+        <v>0.08860987439569114</v>
       </c>
       <c r="T32">
-        <v>0.713122287597068</v>
+        <v>0.7218359839019833</v>
       </c>
       <c r="U32">
         <v>0.07597323332506818</v>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.129257128767318</v>
+        <v>3.028313350419986</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4070,22 +4070,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07974665817433607</v>
+        <v>0.08179433576242244</v>
       </c>
       <c r="C33">
-        <v>2441.531407073071</v>
+        <v>2339.769743319551</v>
       </c>
       <c r="D33">
-        <v>3507.362407073071</v>
+        <v>3441.101743319551</v>
       </c>
       <c r="E33">
-        <v>-686.769</v>
+        <v>-651.268</v>
       </c>
       <c r="F33">
-        <v>1100.531</v>
+        <v>1136.032</v>
       </c>
       <c r="G33">
         <v>34.7</v>
@@ -4106,45 +4106,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M33">
-        <v>83.61089844447061</v>
+        <v>95.16907380074387</v>
       </c>
       <c r="N33">
-        <v>169.5891015555293</v>
+        <v>158.030926199256</v>
       </c>
       <c r="O33">
-        <v>35.61371132666116</v>
+        <v>33.18649450184377</v>
       </c>
       <c r="P33">
-        <v>133.9753902288682</v>
+        <v>124.8444316974123</v>
       </c>
       <c r="Q33">
-        <v>691.2753902288681</v>
+        <v>682.1444316974122</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08860987439569114</v>
+        <v>0.08914185643800765</v>
       </c>
       <c r="T33">
-        <v>0.7218359839019833</v>
+        <v>0.7308059653923371</v>
       </c>
       <c r="U33">
-        <v>0.07597323332506818</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V33">
         <v>0.21</v>
       </c>
       <c r="W33">
-        <v>0.06001885432680387</v>
+        <v>0.06618085432680387</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.028313350419986</v>
+        <v>2.660528151509874</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4152,22 +4152,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08179433576242244</v>
+        <v>0.08193179335050879</v>
       </c>
       <c r="C34">
-        <v>2339.769743319551</v>
+        <v>2299.910320308845</v>
       </c>
       <c r="D34">
-        <v>3441.101743319551</v>
+        <v>3436.743320308845</v>
       </c>
       <c r="E34">
-        <v>-651.268</v>
+        <v>-615.7669999999998</v>
       </c>
       <c r="F34">
-        <v>1136.032</v>
+        <v>1171.533</v>
       </c>
       <c r="G34">
         <v>34.7</v>
@@ -4188,28 +4188,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M34">
-        <v>95.16907380074387</v>
+        <v>98.14310735701713</v>
       </c>
       <c r="N34">
-        <v>158.030926199256</v>
+        <v>155.0568926429828</v>
       </c>
       <c r="O34">
-        <v>33.18649450184377</v>
+        <v>32.56194745502638</v>
       </c>
       <c r="P34">
-        <v>124.8444316974123</v>
+        <v>122.4949451879564</v>
       </c>
       <c r="Q34">
-        <v>682.1444316974122</v>
+        <v>679.7949451879564</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08914185643800765</v>
+        <v>0.08968971854128882</v>
       </c>
       <c r="T34">
-        <v>0.7308059653923371</v>
+        <v>0.7400437075241941</v>
       </c>
       <c r="U34">
         <v>0.0837732333250682</v>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.660528151509874</v>
+        <v>2.579906086312605</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4234,22 +4234,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08193179335050879</v>
+        <v>0.08206925093859514</v>
       </c>
       <c r="C35">
-        <v>2299.910320308845</v>
+        <v>2260.061923895588</v>
       </c>
       <c r="D35">
-        <v>3436.743320308845</v>
+        <v>3432.395923895589</v>
       </c>
       <c r="E35">
-        <v>-615.7669999999998</v>
+        <v>-580.2659999999998</v>
       </c>
       <c r="F35">
-        <v>1171.533</v>
+        <v>1207.034</v>
       </c>
       <c r="G35">
         <v>34.7</v>
@@ -4270,28 +4270,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M35">
-        <v>98.14310735701713</v>
+        <v>101.1171409132904</v>
       </c>
       <c r="N35">
-        <v>155.0568926429828</v>
+        <v>152.0828590867096</v>
       </c>
       <c r="O35">
-        <v>32.56194745502638</v>
+        <v>31.93740040820901</v>
       </c>
       <c r="P35">
-        <v>122.4949451879564</v>
+        <v>120.1454586785005</v>
       </c>
       <c r="Q35">
-        <v>679.7949451879564</v>
+        <v>677.4454586785005</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08968971854128882</v>
+        <v>0.09025418252648762</v>
       </c>
       <c r="T35">
-        <v>0.7400437075241941</v>
+        <v>0.7495613812358045</v>
       </c>
       <c r="U35">
         <v>0.0837732333250682</v>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.579906086312605</v>
+        <v>2.504026495538705</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4316,22 +4316,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08206925093859514</v>
+        <v>0.0832850585266815</v>
       </c>
       <c r="C36">
-        <v>2260.061923895588</v>
+        <v>2186.581929564155</v>
       </c>
       <c r="D36">
-        <v>3432.395923895589</v>
+        <v>3394.416929564155</v>
       </c>
       <c r="E36">
-        <v>-580.2659999999998</v>
+        <v>-544.7649999999999</v>
       </c>
       <c r="F36">
-        <v>1207.034</v>
+        <v>1242.535</v>
       </c>
       <c r="G36">
         <v>34.7</v>
@@ -4352,45 +4352,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M36">
-        <v>101.1171409132904</v>
+        <v>108.9370609695636</v>
       </c>
       <c r="N36">
-        <v>152.0828590867096</v>
+        <v>144.2629390304363</v>
       </c>
       <c r="O36">
-        <v>31.93740040820901</v>
+        <v>30.29521719639163</v>
       </c>
       <c r="P36">
-        <v>120.1454586785005</v>
+        <v>113.9677218340447</v>
       </c>
       <c r="Q36">
-        <v>677.4454586785005</v>
+        <v>671.2677218340447</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09025418252648762</v>
+        <v>0.09083601463430792</v>
       </c>
       <c r="T36">
-        <v>0.7495613812358045</v>
+        <v>0.7593719064462334</v>
       </c>
       <c r="U36">
-        <v>0.0837732333250682</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V36">
         <v>0.21</v>
       </c>
       <c r="W36">
-        <v>0.06618085432680387</v>
+        <v>0.06926185432680387</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.504026495538705</v>
+        <v>2.324277869684244</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4398,22 +4398,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0832850585266815</v>
+        <v>0.08345332611476786</v>
       </c>
       <c r="C37">
-        <v>2186.581929564155</v>
+        <v>2145.890750652766</v>
       </c>
       <c r="D37">
-        <v>3394.416929564155</v>
+        <v>3389.226750652766</v>
       </c>
       <c r="E37">
-        <v>-544.7649999999999</v>
+        <v>-509.2639999999999</v>
       </c>
       <c r="F37">
-        <v>1242.535</v>
+        <v>1278.036</v>
       </c>
       <c r="G37">
         <v>34.7</v>
@@ -4434,28 +4434,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M37">
-        <v>108.9370609695636</v>
+        <v>112.0495484258368</v>
       </c>
       <c r="N37">
-        <v>144.2629390304363</v>
+        <v>141.1504515741631</v>
       </c>
       <c r="O37">
-        <v>30.29521719639163</v>
+        <v>29.64159483057425</v>
       </c>
       <c r="P37">
-        <v>113.9677218340447</v>
+        <v>111.5088567435888</v>
       </c>
       <c r="Q37">
-        <v>671.2677218340447</v>
+        <v>668.8088567435888</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09083601463430792</v>
+        <v>0.0914360289954976</v>
       </c>
       <c r="T37">
-        <v>0.7593719064462334</v>
+        <v>0.7694890105694885</v>
       </c>
       <c r="U37">
         <v>0.08767323332506818</v>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.324277869684244</v>
+        <v>2.259714595526349</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4480,22 +4480,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08345332611476786</v>
+        <v>0.0836215937028542</v>
       </c>
       <c r="C38">
-        <v>2145.890750652767</v>
+        <v>2105.215419429815</v>
       </c>
       <c r="D38">
-        <v>3389.226750652766</v>
+        <v>3384.052419429815</v>
       </c>
       <c r="E38">
-        <v>-509.2640000000001</v>
+        <v>-473.7629999999999</v>
       </c>
       <c r="F38">
-        <v>1278.036</v>
+        <v>1313.537</v>
       </c>
       <c r="G38">
         <v>34.7</v>
@@ -4516,28 +4516,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M38">
-        <v>112.0495484258368</v>
+        <v>115.1620358821101</v>
       </c>
       <c r="N38">
-        <v>141.1504515741631</v>
+        <v>138.0379641178898</v>
       </c>
       <c r="O38">
-        <v>29.64159483057425</v>
+        <v>28.98797246475686</v>
       </c>
       <c r="P38">
-        <v>111.5088567435889</v>
+        <v>109.049991653133</v>
       </c>
       <c r="Q38">
-        <v>668.8088567435888</v>
+        <v>666.349991653133</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0914360289954976</v>
+        <v>0.09205509143164567</v>
       </c>
       <c r="T38">
-        <v>0.7694890105694884</v>
+        <v>0.779927292601418</v>
       </c>
       <c r="U38">
         <v>0.08767323332506818</v>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.259714595526349</v>
+        <v>2.198641228079691</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0836215937028542</v>
+        <v>0.08378986129094057</v>
       </c>
       <c r="C39">
-        <v>2105.215419429815</v>
+        <v>2064.555863421965</v>
       </c>
       <c r="D39">
-        <v>3384.052419429815</v>
+        <v>3378.893863421965</v>
       </c>
       <c r="E39">
-        <v>-473.7629999999999</v>
+        <v>-438.2619999999999</v>
       </c>
       <c r="F39">
-        <v>1313.537</v>
+        <v>1349.038</v>
       </c>
       <c r="G39">
         <v>34.7</v>
@@ -4598,28 +4598,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M39">
-        <v>115.1620358821101</v>
+        <v>118.2745233383833</v>
       </c>
       <c r="N39">
-        <v>138.0379641178898</v>
+        <v>134.9254766616166</v>
       </c>
       <c r="O39">
-        <v>28.98797246475686</v>
+        <v>28.33435009893948</v>
       </c>
       <c r="P39">
-        <v>109.049991653133</v>
+        <v>106.5911265626771</v>
       </c>
       <c r="Q39">
-        <v>666.349991653133</v>
+        <v>663.8911265626771</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09205509143164567</v>
+        <v>0.09269412362379854</v>
       </c>
       <c r="T39">
-        <v>0.779927292601418</v>
+        <v>0.7907022934085713</v>
       </c>
       <c r="U39">
         <v>0.08767323332506818</v>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.198641228079691</v>
+        <v>2.140782248393383</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4644,22 +4644,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08378986129094057</v>
+        <v>0.08395812887902691</v>
       </c>
       <c r="C40">
-        <v>2064.555863421965</v>
+        <v>2023.912010597116</v>
       </c>
       <c r="D40">
-        <v>3378.893863421965</v>
+        <v>3373.751010597116</v>
       </c>
       <c r="E40">
-        <v>-438.2619999999999</v>
+        <v>-402.761</v>
       </c>
       <c r="F40">
-        <v>1349.038</v>
+        <v>1384.539</v>
       </c>
       <c r="G40">
         <v>34.7</v>
@@ -4680,28 +4680,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M40">
-        <v>118.2745233383833</v>
+        <v>121.3870107946566</v>
       </c>
       <c r="N40">
-        <v>134.9254766616166</v>
+        <v>131.8129892053433</v>
       </c>
       <c r="O40">
-        <v>28.33435009893948</v>
+        <v>27.6807277331221</v>
       </c>
       <c r="P40">
-        <v>106.5911265626771</v>
+        <v>104.1322614722212</v>
       </c>
       <c r="Q40">
-        <v>663.8911265626771</v>
+        <v>661.4322614722212</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09269412362379854</v>
+        <v>0.09335410769110394</v>
       </c>
       <c r="T40">
-        <v>0.7907022934085713</v>
+        <v>0.8018305729307131</v>
       </c>
       <c r="U40">
         <v>0.08767323332506818</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.140782248393383</v>
+        <v>2.085890395870476</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4726,22 +4726,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08395812887902691</v>
+        <v>0.08412639646711327</v>
       </c>
       <c r="C41">
-        <v>2023.912010597116</v>
+        <v>1983.283789361044</v>
       </c>
       <c r="D41">
-        <v>3373.751010597116</v>
+        <v>3368.623789361044</v>
       </c>
       <c r="E41">
-        <v>-402.761</v>
+        <v>-367.26</v>
       </c>
       <c r="F41">
-        <v>1384.539</v>
+        <v>1420.04</v>
       </c>
       <c r="G41">
         <v>34.7</v>
@@ -4762,28 +4762,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M41">
-        <v>121.3870107946566</v>
+        <v>124.4994982509298</v>
       </c>
       <c r="N41">
-        <v>131.8129892053433</v>
+        <v>128.7005017490701</v>
       </c>
       <c r="O41">
-        <v>27.6807277331221</v>
+        <v>27.02710536730472</v>
       </c>
       <c r="P41">
-        <v>104.1322614722212</v>
+        <v>101.6733963817654</v>
       </c>
       <c r="Q41">
-        <v>661.4322614722212</v>
+        <v>658.9733963817653</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09335410769110394</v>
+        <v>0.09403609122731954</v>
       </c>
       <c r="T41">
-        <v>0.8018305729307131</v>
+        <v>0.8133297951035932</v>
       </c>
       <c r="U41">
         <v>0.08767323332506818</v>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.085890395870476</v>
+        <v>2.033743135973714</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4808,22 +4808,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08412639646711327</v>
+        <v>0.08889404405519963</v>
       </c>
       <c r="C42">
-        <v>1983.283789361044</v>
+        <v>1808.718384754376</v>
       </c>
       <c r="D42">
-        <v>3368.623789361044</v>
+        <v>3229.559384754376</v>
       </c>
       <c r="E42">
-        <v>-367.26</v>
+        <v>-331.7589999999998</v>
       </c>
       <c r="F42">
-        <v>1420.04</v>
+        <v>1455.541</v>
       </c>
       <c r="G42">
         <v>34.7</v>
@@ -4844,45 +4844,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M42">
-        <v>124.4994982509298</v>
+        <v>148.2806679072031</v>
       </c>
       <c r="N42">
-        <v>128.7005017490701</v>
+        <v>104.9193320927969</v>
       </c>
       <c r="O42">
-        <v>27.02710536730472</v>
+        <v>22.03305973948734</v>
       </c>
       <c r="P42">
-        <v>101.6733963817654</v>
+        <v>82.88627235330951</v>
       </c>
       <c r="Q42">
-        <v>658.9733963817653</v>
+        <v>640.1862723533095</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09403609122731954</v>
+        <v>0.09474119284950855</v>
       </c>
       <c r="T42">
-        <v>0.8133297951035932</v>
+        <v>0.8252188214179265</v>
       </c>
       <c r="U42">
-        <v>0.08767323332506818</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V42">
         <v>0.21</v>
       </c>
       <c r="W42">
-        <v>0.06926185432680387</v>
+        <v>0.08047985432680388</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.033743135973714</v>
+        <v>1.707572562044685</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4890,22 +4890,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08889404405519963</v>
+        <v>0.089174491643286</v>
       </c>
       <c r="C43">
-        <v>1808.718384754376</v>
+        <v>1765.393886906166</v>
       </c>
       <c r="D43">
-        <v>3229.559384754376</v>
+        <v>3221.735886906166</v>
       </c>
       <c r="E43">
-        <v>-331.7589999999998</v>
+        <v>-296.2579999999998</v>
       </c>
       <c r="F43">
-        <v>1455.541</v>
+        <v>1491.042</v>
       </c>
       <c r="G43">
         <v>34.7</v>
@@ -4926,28 +4926,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M43">
-        <v>148.2806679072031</v>
+        <v>151.8972695634763</v>
       </c>
       <c r="N43">
-        <v>104.9193320927969</v>
+        <v>101.3027304365236</v>
       </c>
       <c r="O43">
-        <v>22.03305973948734</v>
+        <v>21.27357339166996</v>
       </c>
       <c r="P43">
-        <v>82.88627235330951</v>
+        <v>80.02915704485365</v>
       </c>
       <c r="Q43">
-        <v>640.1862723533095</v>
+        <v>637.3291570448536</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09474119284950855</v>
+        <v>0.09547060832073856</v>
       </c>
       <c r="T43">
-        <v>0.8252188214179265</v>
+        <v>0.8375178141568923</v>
       </c>
       <c r="U43">
         <v>0.1018732333250682</v>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.707572562044685</v>
+        <v>1.666916072472193</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08917449164328597</v>
+        <v>0.08945493923137235</v>
       </c>
       <c r="C44">
-        <v>1765.393886906166</v>
+        <v>1722.107201773227</v>
       </c>
       <c r="D44">
-        <v>3221.735886906166</v>
+        <v>3213.950201773227</v>
       </c>
       <c r="E44">
-        <v>-296.258</v>
+        <v>-260.7570000000001</v>
       </c>
       <c r="F44">
-        <v>1491.042</v>
+        <v>1526.543</v>
       </c>
       <c r="G44">
         <v>34.7</v>
@@ -5008,28 +5008,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M44">
-        <v>151.8972695634763</v>
+        <v>155.5138712197495</v>
       </c>
       <c r="N44">
-        <v>101.3027304365236</v>
+        <v>97.68612878025039</v>
       </c>
       <c r="O44">
-        <v>21.27357339166996</v>
+        <v>20.51408704385258</v>
       </c>
       <c r="P44">
-        <v>80.02915704485366</v>
+        <v>77.1720417363978</v>
       </c>
       <c r="Q44">
-        <v>637.3291570448537</v>
+        <v>634.4720417363977</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09547060832073853</v>
+        <v>0.09622561731727486</v>
       </c>
       <c r="T44">
-        <v>0.8375178141568921</v>
+        <v>0.8502483505007338</v>
       </c>
       <c r="U44">
         <v>0.1018732333250682</v>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.666916072472193</v>
+        <v>1.6281505824147</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5054,22 +5054,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08945493923137235</v>
+        <v>0.0897353868194587</v>
       </c>
       <c r="C45">
-        <v>1722.107201773227</v>
+        <v>1678.858055880474</v>
       </c>
       <c r="D45">
-        <v>3213.950201773227</v>
+        <v>3206.202055880474</v>
       </c>
       <c r="E45">
-        <v>-260.7570000000001</v>
+        <v>-225.2560000000001</v>
       </c>
       <c r="F45">
-        <v>1526.543</v>
+        <v>1562.044</v>
       </c>
       <c r="G45">
         <v>34.7</v>
@@ -5090,28 +5090,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M45">
-        <v>155.5138712197495</v>
+        <v>159.1304728760228</v>
       </c>
       <c r="N45">
-        <v>97.68612878025039</v>
+        <v>94.06952712397714</v>
       </c>
       <c r="O45">
-        <v>20.51408704385258</v>
+        <v>19.7546006960352</v>
       </c>
       <c r="P45">
-        <v>77.1720417363978</v>
+        <v>74.31492642794194</v>
       </c>
       <c r="Q45">
-        <v>634.4720417363977</v>
+        <v>631.6149264279419</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09622561731727486</v>
+        <v>0.09700759092083033</v>
       </c>
       <c r="T45">
-        <v>0.8502483505007338</v>
+        <v>0.8634335488568556</v>
       </c>
       <c r="U45">
         <v>0.1018732333250682</v>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.6281505824147</v>
+        <v>1.591147160087094</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5136,22 +5136,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0897353868194587</v>
+        <v>0.09001583440754506</v>
       </c>
       <c r="C46">
-        <v>1678.858055880474</v>
+        <v>1635.646178383638</v>
       </c>
       <c r="D46">
-        <v>3206.202055880474</v>
+        <v>3198.491178383639</v>
       </c>
       <c r="E46">
-        <v>-225.2560000000001</v>
+        <v>-189.7549999999999</v>
       </c>
       <c r="F46">
-        <v>1562.044</v>
+        <v>1597.545</v>
       </c>
       <c r="G46">
         <v>34.7</v>
@@ -5172,28 +5172,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M46">
-        <v>159.1304728760228</v>
+        <v>162.7470745322961</v>
       </c>
       <c r="N46">
-        <v>94.06952712397714</v>
+        <v>90.45292546770386</v>
       </c>
       <c r="O46">
-        <v>19.7546006960352</v>
+        <v>18.99511434821781</v>
       </c>
       <c r="P46">
-        <v>74.31492642794194</v>
+        <v>71.45781111948605</v>
       </c>
       <c r="Q46">
-        <v>631.6149264279419</v>
+        <v>628.757811119486</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09700759092083033</v>
+        <v>0.09781799992815146</v>
       </c>
       <c r="T46">
-        <v>0.8634335488568556</v>
+        <v>0.8770982089713818</v>
       </c>
       <c r="U46">
         <v>0.1018732333250682</v>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.591147160087094</v>
+        <v>1.55578833430738</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5218,22 +5218,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09001583440754506</v>
+        <v>0.09029628199563142</v>
       </c>
       <c r="C47">
-        <v>1635.646178383638</v>
+        <v>1592.471301037713</v>
       </c>
       <c r="D47">
-        <v>3198.491178383639</v>
+        <v>3190.817301037713</v>
       </c>
       <c r="E47">
-        <v>-189.7549999999999</v>
+        <v>-154.2539999999999</v>
       </c>
       <c r="F47">
-        <v>1597.545</v>
+        <v>1633.046</v>
       </c>
       <c r="G47">
         <v>34.7</v>
@@ -5254,28 +5254,28 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M47">
-        <v>162.7470745322961</v>
+        <v>166.3636761885693</v>
       </c>
       <c r="N47">
-        <v>90.45292546770386</v>
+        <v>86.83632381143062</v>
       </c>
       <c r="O47">
-        <v>18.99511434821781</v>
+        <v>18.23562800040043</v>
       </c>
       <c r="P47">
-        <v>71.45781111948605</v>
+        <v>68.60069581103019</v>
       </c>
       <c r="Q47">
-        <v>628.757811119486</v>
+        <v>625.9006958110301</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09781799992815146</v>
+        <v>0.09865842408389189</v>
       </c>
       <c r="T47">
-        <v>0.8770982089713818</v>
+        <v>0.891268967608668</v>
       </c>
       <c r="U47">
         <v>0.1018732333250682</v>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.55578833430738</v>
+        <v>1.521966848778959</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5300,22 +5300,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09029628199563142</v>
+        <v>0.1124861013157825</v>
       </c>
       <c r="C48">
-        <v>1592.471301037713</v>
+        <v>1047.888379719555</v>
       </c>
       <c r="D48">
-        <v>3190.817301037713</v>
+        <v>2681.735379719555</v>
       </c>
       <c r="E48">
-        <v>-154.2539999999999</v>
+        <v>-118.7529999999999</v>
       </c>
       <c r="F48">
-        <v>1633.046</v>
+        <v>1668.547</v>
       </c>
       <c r="G48">
         <v>34.7</v>
@@ -5336,45 +5336,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M48">
-        <v>166.3636761885693</v>
+        <v>264.7537474448425</v>
       </c>
       <c r="N48">
-        <v>86.83632381143062</v>
+        <v>-11.5537474448426</v>
       </c>
       <c r="O48">
-        <v>18.23562800040043</v>
+        <v>-2.426286963416946</v>
       </c>
       <c r="P48">
-        <v>68.60069581103019</v>
+        <v>-9.127460481425654</v>
       </c>
       <c r="Q48">
-        <v>625.9006958110301</v>
+        <v>548.1725395185744</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09865842408389189</v>
+        <v>0.09978733569360888</v>
       </c>
       <c r="T48">
-        <v>0.891268967608668</v>
+        <v>0.9103040391673096</v>
       </c>
       <c r="U48">
-        <v>0.1018732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V48">
-        <v>0.21</v>
+        <v>0.2008356841524125</v>
       </c>
       <c r="W48">
-        <v>0.08047985432680388</v>
+        <v>0.1268059859535527</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.521966848778959</v>
+        <v>0.9563604007257739</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5382,22 +5382,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1124861013157825</v>
+        <v>0.1136148336490332</v>
       </c>
       <c r="C49">
-        <v>1047.888379719555</v>
+        <v>990.7985796711421</v>
       </c>
       <c r="D49">
-        <v>2681.735379719555</v>
+        <v>2660.146579671142</v>
       </c>
       <c r="E49">
-        <v>-118.7529999999999</v>
+        <v>-83.25199999999995</v>
       </c>
       <c r="F49">
-        <v>1668.547</v>
+        <v>1704.048</v>
       </c>
       <c r="G49">
         <v>34.7</v>
@@ -5418,37 +5418,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M49">
-        <v>264.7537474448425</v>
+        <v>270.3868059011158</v>
       </c>
       <c r="N49">
-        <v>-11.5537474448426</v>
+        <v>-17.18680590111586</v>
       </c>
       <c r="O49">
-        <v>-2.426286963416946</v>
+        <v>-3.609229239234331</v>
       </c>
       <c r="P49">
-        <v>-9.127460481425654</v>
+        <v>-13.57757666188153</v>
       </c>
       <c r="Q49">
-        <v>548.1725395185744</v>
+        <v>543.7224233381185</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09978733569360888</v>
+        <v>0.1008255536877167</v>
       </c>
       <c r="T49">
-        <v>0.9103040391673096</v>
+        <v>0.9278098860743732</v>
       </c>
       <c r="U49">
         <v>0.1586732333250682</v>
       </c>
       <c r="V49">
-        <v>0.2008356841524125</v>
+        <v>0.1966516073992372</v>
       </c>
       <c r="W49">
-        <v>0.1268059859535527</v>
+        <v>0.1274698869404593</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.9563604007257739</v>
+        <v>0.9364362257106535</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5464,22 +5464,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1136148336490332</v>
+        <v>0.1147435659822839</v>
       </c>
       <c r="C50">
-        <v>990.7985796711421</v>
+        <v>934.053596785996</v>
       </c>
       <c r="D50">
-        <v>2660.146579671142</v>
+        <v>2638.902596785996</v>
       </c>
       <c r="E50">
-        <v>-83.25199999999995</v>
+        <v>-47.75099999999998</v>
       </c>
       <c r="F50">
-        <v>1704.048</v>
+        <v>1739.549</v>
       </c>
       <c r="G50">
         <v>34.7</v>
@@ -5500,37 +5500,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M50">
-        <v>270.3868059011158</v>
+        <v>276.0198643573891</v>
       </c>
       <c r="N50">
-        <v>-17.18680590111586</v>
+        <v>-22.81986435738912</v>
       </c>
       <c r="O50">
-        <v>-3.609229239234331</v>
+        <v>-4.792171515051716</v>
       </c>
       <c r="P50">
-        <v>-13.57757666188153</v>
+        <v>-18.02769284233741</v>
       </c>
       <c r="Q50">
-        <v>543.7224233381185</v>
+        <v>539.2723071576626</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1008255536877167</v>
+        <v>0.1019044861129661</v>
       </c>
       <c r="T50">
-        <v>0.9278098860743732</v>
+        <v>0.9460022367817138</v>
       </c>
       <c r="U50">
         <v>0.1586732333250682</v>
       </c>
       <c r="V50">
-        <v>0.1966516073992372</v>
+        <v>0.1926383092890487</v>
       </c>
       <c r="W50">
-        <v>0.1274698869404593</v>
+        <v>0.1281066899279003</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.9364362257106535</v>
+        <v>0.9173252823288034</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5546,22 +5546,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1147435659822839</v>
+        <v>0.1158722983155345</v>
       </c>
       <c r="C51">
-        <v>934.053596785996</v>
+        <v>877.645235365196</v>
       </c>
       <c r="D51">
-        <v>2638.902596785996</v>
+        <v>2617.995235365196</v>
       </c>
       <c r="E51">
-        <v>-47.75099999999998</v>
+        <v>-12.25</v>
       </c>
       <c r="F51">
-        <v>1739.549</v>
+        <v>1775.05</v>
       </c>
       <c r="G51">
         <v>34.7</v>
@@ -5582,37 +5582,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M51">
-        <v>276.0198643573891</v>
+        <v>281.6529228136623</v>
       </c>
       <c r="N51">
-        <v>-22.81986435738912</v>
+        <v>-28.45292281366233</v>
       </c>
       <c r="O51">
-        <v>-4.792171515051716</v>
+        <v>-5.975113790869088</v>
       </c>
       <c r="P51">
-        <v>-18.02769284233741</v>
+        <v>-22.47780902279324</v>
       </c>
       <c r="Q51">
-        <v>539.2723071576626</v>
+        <v>534.8221909772067</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1019044861129661</v>
+        <v>0.1030265758352254</v>
       </c>
       <c r="T51">
-        <v>0.9460022367817138</v>
+        <v>0.964922281517348</v>
       </c>
       <c r="U51">
         <v>0.1586732333250682</v>
       </c>
       <c r="V51">
-        <v>0.1926383092890487</v>
+        <v>0.1887855431032678</v>
       </c>
       <c r="W51">
-        <v>0.1281066899279003</v>
+        <v>0.1287180207958437</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9173252823288034</v>
+        <v>0.8989787766822275</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5628,22 +5628,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1158722983155345</v>
+        <v>0.1170010306487852</v>
       </c>
       <c r="C52">
-        <v>877.645235365196</v>
+        <v>821.5655573980616</v>
       </c>
       <c r="D52">
-        <v>2617.995235365196</v>
+        <v>2597.416557398062</v>
       </c>
       <c r="E52">
-        <v>-12.25</v>
+        <v>23.25099999999998</v>
       </c>
       <c r="F52">
-        <v>1775.05</v>
+        <v>1810.551</v>
       </c>
       <c r="G52">
         <v>34.7</v>
@@ -5664,37 +5664,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M52">
-        <v>281.6529228136623</v>
+        <v>287.2859812699355</v>
       </c>
       <c r="N52">
-        <v>-28.45292281366233</v>
+        <v>-34.08598126993559</v>
       </c>
       <c r="O52">
-        <v>-5.975113790869088</v>
+        <v>-7.158056066686473</v>
       </c>
       <c r="P52">
-        <v>-22.47780902279324</v>
+        <v>-26.92792520324911</v>
       </c>
       <c r="Q52">
-        <v>534.8221909772067</v>
+        <v>530.3720747967509</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1030265758352254</v>
+        <v>0.1041944651379851</v>
       </c>
       <c r="T52">
-        <v>0.964922281517348</v>
+        <v>0.9846145729768859</v>
       </c>
       <c r="U52">
         <v>0.1586732333250682</v>
       </c>
       <c r="V52">
-        <v>0.1887855431032678</v>
+        <v>0.1850838657875174</v>
       </c>
       <c r="W52">
-        <v>0.1287180207958437</v>
+        <v>0.1293053779042598</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8989787766822275</v>
+        <v>0.8813517418453209</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5710,22 +5710,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1170010306487852</v>
+        <v>0.1181297629820359</v>
       </c>
       <c r="C53">
-        <v>821.5655573980616</v>
+        <v>765.8068725133915</v>
       </c>
       <c r="D53">
-        <v>2597.416557398062</v>
+        <v>2577.158872513392</v>
       </c>
       <c r="E53">
-        <v>23.25099999999998</v>
+        <v>58.75199999999995</v>
       </c>
       <c r="F53">
-        <v>1810.551</v>
+        <v>1846.052</v>
       </c>
       <c r="G53">
         <v>34.7</v>
@@ -5746,37 +5746,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M53">
-        <v>287.2859812699355</v>
+        <v>292.9190397262088</v>
       </c>
       <c r="N53">
-        <v>-34.08598126993559</v>
+        <v>-39.71903972620885</v>
       </c>
       <c r="O53">
-        <v>-7.158056066686473</v>
+        <v>-8.340998342503857</v>
       </c>
       <c r="P53">
-        <v>-26.92792520324911</v>
+        <v>-31.37804138370499</v>
       </c>
       <c r="Q53">
-        <v>530.3720747967509</v>
+        <v>525.921958616295</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1041944651379851</v>
+        <v>0.1054110164950265</v>
       </c>
       <c r="T53">
-        <v>0.9846145729768859</v>
+        <v>1.005127376580571</v>
       </c>
       <c r="U53">
         <v>0.1586732333250682</v>
       </c>
       <c r="V53">
-        <v>0.1850838657875174</v>
+        <v>0.181524560676219</v>
       </c>
       <c r="W53">
-        <v>0.1293053779042598</v>
+        <v>0.12987014435466</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8813517418453209</v>
+        <v>0.8644026698867571</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5792,22 +5792,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1181297629820359</v>
+        <v>0.1192584953152866</v>
       </c>
       <c r="C54">
-        <v>765.8068725133915</v>
+        <v>710.3617283972842</v>
       </c>
       <c r="D54">
-        <v>2577.158872513392</v>
+        <v>2557.214728397284</v>
       </c>
       <c r="E54">
-        <v>58.75199999999995</v>
+        <v>94.25300000000016</v>
       </c>
       <c r="F54">
-        <v>1846.052</v>
+        <v>1881.553</v>
       </c>
       <c r="G54">
         <v>34.7</v>
@@ -5828,37 +5828,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M54">
-        <v>292.9190397262088</v>
+        <v>298.552098182482</v>
       </c>
       <c r="N54">
-        <v>-39.71903972620885</v>
+        <v>-45.35209818248211</v>
       </c>
       <c r="O54">
-        <v>-8.340998342503857</v>
+        <v>-9.523940618321243</v>
       </c>
       <c r="P54">
-        <v>-31.37804138370499</v>
+        <v>-35.82815756416087</v>
       </c>
       <c r="Q54">
-        <v>525.921958616295</v>
+        <v>521.4718424358391</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1054110164950265</v>
+        <v>0.1066793359949207</v>
       </c>
       <c r="T54">
-        <v>1.005127376580571</v>
+        <v>1.026513065443988</v>
       </c>
       <c r="U54">
         <v>0.1586732333250682</v>
       </c>
       <c r="V54">
-        <v>0.181524560676219</v>
+        <v>0.1780995689653469</v>
       </c>
       <c r="W54">
-        <v>0.12987014435466</v>
+        <v>0.1304135988635357</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8644026698867571</v>
+        <v>0.848093185549271</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5874,22 +5874,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1192584953152866</v>
+        <v>0.1203872276485373</v>
       </c>
       <c r="C55">
-        <v>710.3617283972842</v>
+        <v>655.2229016524766</v>
       </c>
       <c r="D55">
-        <v>2557.214728397284</v>
+        <v>2537.576901652477</v>
       </c>
       <c r="E55">
-        <v>94.25300000000016</v>
+        <v>129.7540000000001</v>
       </c>
       <c r="F55">
-        <v>1881.553</v>
+        <v>1917.054</v>
       </c>
       <c r="G55">
         <v>34.7</v>
@@ -5910,37 +5910,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M55">
-        <v>298.552098182482</v>
+        <v>304.1851566387553</v>
       </c>
       <c r="N55">
-        <v>-45.35209818248211</v>
+        <v>-50.98515663875537</v>
       </c>
       <c r="O55">
-        <v>-9.523940618321243</v>
+        <v>-10.70688289413863</v>
       </c>
       <c r="P55">
-        <v>-35.82815756416087</v>
+        <v>-40.27827374461674</v>
       </c>
       <c r="Q55">
-        <v>521.4718424358391</v>
+        <v>517.0217262553832</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1066793359949207</v>
+        <v>0.1080027998208972</v>
       </c>
       <c r="T55">
-        <v>1.026513065443988</v>
+        <v>1.048828566866683</v>
       </c>
       <c r="U55">
         <v>0.1586732333250682</v>
       </c>
       <c r="V55">
-        <v>0.1780995689653469</v>
+        <v>0.174801428799322</v>
       </c>
       <c r="W55">
-        <v>0.1304135988635357</v>
+        <v>0.1309369254276381</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.848093185549271</v>
+        <v>0.8323877561872475</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5956,22 +5956,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1203872276485373</v>
+        <v>0.1215159599817879</v>
       </c>
       <c r="C56">
-        <v>655.2229016524766</v>
+        <v>600.3833890756375</v>
       </c>
       <c r="D56">
-        <v>2537.576901652477</v>
+        <v>2518.238389075638</v>
       </c>
       <c r="E56">
-        <v>129.7540000000001</v>
+        <v>165.2550000000001</v>
       </c>
       <c r="F56">
-        <v>1917.054</v>
+        <v>1952.555</v>
       </c>
       <c r="G56">
         <v>34.7</v>
@@ -5992,37 +5992,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M56">
-        <v>304.1851566387553</v>
+        <v>309.8182150950285</v>
       </c>
       <c r="N56">
-        <v>-50.98515663875537</v>
+        <v>-56.61821509502857</v>
       </c>
       <c r="O56">
-        <v>-10.70688289413863</v>
+        <v>-11.889825169956</v>
       </c>
       <c r="P56">
-        <v>-40.27827374461674</v>
+        <v>-44.72838992507258</v>
       </c>
       <c r="Q56">
-        <v>517.0217262553832</v>
+        <v>512.5716100749273</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1080027998208972</v>
+        <v>0.1093850842613616</v>
       </c>
       <c r="T56">
-        <v>1.048828566866683</v>
+        <v>1.072135868352609</v>
       </c>
       <c r="U56">
         <v>0.1586732333250682</v>
       </c>
       <c r="V56">
-        <v>0.174801428799322</v>
+        <v>0.1716232210029707</v>
       </c>
       <c r="W56">
-        <v>0.1309369254276381</v>
+        <v>0.1314412219348641</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8323877561872475</v>
+        <v>0.8172534333474795</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6038,22 +6038,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1215159599817879</v>
+        <v>0.1226446923150386</v>
       </c>
       <c r="C57">
-        <v>600.3833890756375</v>
+        <v>545.8363993304906</v>
       </c>
       <c r="D57">
-        <v>2518.238389075638</v>
+        <v>2499.192399330491</v>
       </c>
       <c r="E57">
-        <v>165.2550000000001</v>
+        <v>200.7560000000001</v>
       </c>
       <c r="F57">
-        <v>1952.555</v>
+        <v>1988.056</v>
       </c>
       <c r="G57">
         <v>34.7</v>
@@ -6074,37 +6074,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M57">
-        <v>309.8182150950285</v>
+        <v>315.4512735513018</v>
       </c>
       <c r="N57">
-        <v>-56.61821509502857</v>
+        <v>-62.25127355130184</v>
       </c>
       <c r="O57">
-        <v>-11.889825169956</v>
+        <v>-13.07276744577339</v>
       </c>
       <c r="P57">
-        <v>-44.72838992507258</v>
+        <v>-49.17850610552845</v>
       </c>
       <c r="Q57">
-        <v>512.5716100749273</v>
+        <v>508.1214938944715</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1093850842613616</v>
+        <v>0.1108301998127562</v>
       </c>
       <c r="T57">
-        <v>1.072135868352609</v>
+        <v>1.09650259263335</v>
       </c>
       <c r="U57">
         <v>0.1586732333250682</v>
       </c>
       <c r="V57">
-        <v>0.1716232210029707</v>
+        <v>0.1685585206279176</v>
       </c>
       <c r="W57">
-        <v>0.1314412219348641</v>
+        <v>0.1319275078525463</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8172534333474795</v>
+        <v>0.802659622037703</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1226446923150386</v>
+        <v>0.1553106890622852</v>
       </c>
       <c r="C58">
-        <v>545.8363993304906</v>
+        <v>61.53896899954907</v>
       </c>
       <c r="D58">
-        <v>2499.192399330491</v>
+        <v>2050.395968999549</v>
       </c>
       <c r="E58">
-        <v>200.7560000000001</v>
+        <v>236.2570000000003</v>
       </c>
       <c r="F58">
-        <v>1988.056</v>
+        <v>2023.557</v>
       </c>
       <c r="G58">
         <v>34.7</v>
@@ -6156,45 +6156,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M58">
-        <v>315.4512735513018</v>
+        <v>430.3564100075751</v>
       </c>
       <c r="N58">
-        <v>-62.25127355130184</v>
+        <v>-177.1564100075751</v>
       </c>
       <c r="O58">
-        <v>-13.07276744577339</v>
+        <v>-37.20284610159077</v>
       </c>
       <c r="P58">
-        <v>-49.17850610552845</v>
+        <v>-139.9535639059843</v>
       </c>
       <c r="Q58">
-        <v>508.1214938944715</v>
+        <v>417.3464360940156</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1108301998127562</v>
+        <v>0.1141036100735082</v>
       </c>
       <c r="T58">
-        <v>1.09650259263335</v>
+        <v>1.151696992281545</v>
       </c>
       <c r="U58">
-        <v>0.1586732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V58">
-        <v>0.1685585206279176</v>
+        <v>0.1235534054182301</v>
       </c>
       <c r="W58">
-        <v>0.1319275078525463</v>
+        <v>0.1863967311064502</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.802659622037703</v>
+        <v>0.5883495496106197</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6202,22 +6202,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1553106890622852</v>
+        <v>0.1569794213955358</v>
       </c>
       <c r="C59">
-        <v>61.53896899954907</v>
+        <v>7.399410488333615</v>
       </c>
       <c r="D59">
-        <v>2050.395968999549</v>
+        <v>2031.757410488334</v>
       </c>
       <c r="E59">
-        <v>236.2570000000003</v>
+        <v>271.758</v>
       </c>
       <c r="F59">
-        <v>2023.557</v>
+        <v>2059.058</v>
       </c>
       <c r="G59">
         <v>34.7</v>
@@ -6238,37 +6238,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M59">
-        <v>430.3564100075751</v>
+        <v>437.9065224638483</v>
       </c>
       <c r="N59">
-        <v>-177.1564100075751</v>
+        <v>-184.7065224638483</v>
       </c>
       <c r="O59">
-        <v>-37.20284610159077</v>
+        <v>-38.78836971740814</v>
       </c>
       <c r="P59">
-        <v>-139.9535639059843</v>
+        <v>-145.9181527464402</v>
       </c>
       <c r="Q59">
-        <v>417.3464360940156</v>
+        <v>411.3818472535598</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1141036100735082</v>
+        <v>0.1157298865038298</v>
       </c>
       <c r="T59">
-        <v>1.151696992281545</v>
+        <v>1.17911834924063</v>
       </c>
       <c r="U59">
         <v>0.2126732333250682</v>
       </c>
       <c r="V59">
-        <v>0.1235534054182301</v>
+        <v>0.1214231742903296</v>
       </c>
       <c r="W59">
-        <v>0.1863967311064502</v>
+        <v>0.1868497742481505</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5883495496106197</v>
+        <v>0.5782055918587123</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6284,22 +6284,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1569794213955358</v>
+        <v>0.1586481537287865</v>
       </c>
       <c r="C60">
-        <v>7.39941048833407</v>
+        <v>-46.40434322237525</v>
       </c>
       <c r="D60">
-        <v>2031.757410488334</v>
+        <v>2013.454656777625</v>
       </c>
       <c r="E60">
-        <v>271.758</v>
+        <v>307.2589999999998</v>
       </c>
       <c r="F60">
-        <v>2059.058</v>
+        <v>2094.559</v>
       </c>
       <c r="G60">
         <v>34.7</v>
@@ -6320,37 +6320,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M60">
-        <v>437.9065224638483</v>
+        <v>445.4566349201214</v>
       </c>
       <c r="N60">
-        <v>-184.7065224638483</v>
+        <v>-192.2566349201215</v>
       </c>
       <c r="O60">
-        <v>-38.78836971740814</v>
+        <v>-40.37389333322551</v>
       </c>
       <c r="P60">
-        <v>-145.9181527464402</v>
+        <v>-151.882741586896</v>
       </c>
       <c r="Q60">
-        <v>411.3818472535598</v>
+        <v>405.417258413104</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1157298865038298</v>
+        <v>0.1174354934917281</v>
       </c>
       <c r="T60">
-        <v>1.17911834924063</v>
+        <v>1.20787733336845</v>
       </c>
       <c r="U60">
         <v>0.2126732333250682</v>
       </c>
       <c r="V60">
-        <v>0.1214231742903296</v>
+        <v>0.1193651543871037</v>
       </c>
       <c r="W60">
-        <v>0.1868497742481505</v>
+        <v>0.1872874599952169</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5782055918587123</v>
+        <v>0.5684054970814463</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6366,22 +6366,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1586481537287865</v>
+        <v>0.1603168860620372</v>
       </c>
       <c r="C61">
-        <v>-46.40434322237525</v>
+        <v>-99.88128623821308</v>
       </c>
       <c r="D61">
-        <v>2013.454656777625</v>
+        <v>1995.478713761787</v>
       </c>
       <c r="E61">
-        <v>307.2589999999998</v>
+        <v>342.76</v>
       </c>
       <c r="F61">
-        <v>2094.559</v>
+        <v>2130.06</v>
       </c>
       <c r="G61">
         <v>34.7</v>
@@ -6402,37 +6402,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M61">
-        <v>445.4566349201214</v>
+        <v>453.0067473763947</v>
       </c>
       <c r="N61">
-        <v>-192.2566349201215</v>
+        <v>-199.8067473763948</v>
       </c>
       <c r="O61">
-        <v>-40.37389333322551</v>
+        <v>-41.95941694904291</v>
       </c>
       <c r="P61">
-        <v>-151.882741586896</v>
+        <v>-157.8473304273519</v>
       </c>
       <c r="Q61">
-        <v>405.417258413104</v>
+        <v>399.4526695726481</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1174354934917281</v>
+        <v>0.1192263808290213</v>
       </c>
       <c r="T61">
-        <v>1.20787733336845</v>
+        <v>1.238074266702661</v>
       </c>
       <c r="U61">
         <v>0.2126732333250682</v>
       </c>
       <c r="V61">
-        <v>0.1193651543871037</v>
+        <v>0.1173757351473186</v>
       </c>
       <c r="W61">
-        <v>0.1872874599952169</v>
+        <v>0.1877105562173811</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5684054970814463</v>
+        <v>0.5589320721300887</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6448,22 +6448,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1603168860620372</v>
+        <v>0.1619856183952879</v>
       </c>
       <c r="C62">
-        <v>-99.88128623821308</v>
+        <v>-153.0400943127522</v>
       </c>
       <c r="D62">
-        <v>1995.478713761787</v>
+        <v>1977.820905687247</v>
       </c>
       <c r="E62">
-        <v>342.76</v>
+        <v>378.2609999999997</v>
       </c>
       <c r="F62">
-        <v>2130.06</v>
+        <v>2165.561</v>
       </c>
       <c r="G62">
         <v>34.7</v>
@@ -6484,37 +6484,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M62">
-        <v>453.0067473763947</v>
+        <v>460.5568598326679</v>
       </c>
       <c r="N62">
-        <v>-199.8067473763948</v>
+        <v>-207.356859832668</v>
       </c>
       <c r="O62">
-        <v>-41.95941694904291</v>
+        <v>-43.54494056486027</v>
       </c>
       <c r="P62">
-        <v>-157.8473304273519</v>
+        <v>-163.8119192678077</v>
       </c>
       <c r="Q62">
-        <v>399.4526695726481</v>
+        <v>393.4880807321923</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1192263808290213</v>
+        <v>0.121109108542586</v>
       </c>
       <c r="T62">
-        <v>1.238074266702661</v>
+        <v>1.269819760720678</v>
       </c>
       <c r="U62">
         <v>0.2126732333250682</v>
       </c>
       <c r="V62">
-        <v>0.1173757351473186</v>
+        <v>0.1154515427678544</v>
       </c>
       <c r="W62">
-        <v>0.1877105562173811</v>
+        <v>0.1881197804322612</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5589320721300887</v>
+        <v>0.5497692512754973</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6530,22 +6530,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1619856183952879</v>
+        <v>0.1636543507285385</v>
       </c>
       <c r="C63">
-        <v>-153.0400943127522</v>
+        <v>-205.8891388092977</v>
       </c>
       <c r="D63">
-        <v>1977.820905687247</v>
+        <v>1960.472861190702</v>
       </c>
       <c r="E63">
-        <v>378.2609999999997</v>
+        <v>413.7619999999999</v>
       </c>
       <c r="F63">
-        <v>2165.561</v>
+        <v>2201.062</v>
       </c>
       <c r="G63">
         <v>34.7</v>
@@ -6566,37 +6566,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M63">
-        <v>460.5568598326679</v>
+        <v>468.1069722889412</v>
       </c>
       <c r="N63">
-        <v>-207.356859832668</v>
+        <v>-214.9069722889413</v>
       </c>
       <c r="O63">
-        <v>-43.54494056486027</v>
+        <v>-45.13046418067767</v>
       </c>
       <c r="P63">
-        <v>-163.8119192678077</v>
+        <v>-169.7765081082636</v>
       </c>
       <c r="Q63">
-        <v>393.4880807321923</v>
+        <v>387.5234918917363</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.121109108542586</v>
+        <v>0.1230909271884435</v>
       </c>
       <c r="T63">
-        <v>1.269819760720678</v>
+        <v>1.303236070213327</v>
       </c>
       <c r="U63">
         <v>0.2126732333250682</v>
       </c>
       <c r="V63">
-        <v>0.1154515427678544</v>
+        <v>0.1135894211103083</v>
       </c>
       <c r="W63">
-        <v>0.1881197804322612</v>
+        <v>0.1885158038660162</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5497692512754973</v>
+        <v>0.5409020052871827</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6612,22 +6612,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1636543507285385</v>
+        <v>0.1653230830617892</v>
       </c>
       <c r="C64">
-        <v>-205.8891388092977</v>
+        <v>-258.4364999342909</v>
       </c>
       <c r="D64">
-        <v>1960.472861190702</v>
+        <v>1943.426500065709</v>
       </c>
       <c r="E64">
-        <v>413.7619999999999</v>
+        <v>449.2630000000001</v>
       </c>
       <c r="F64">
-        <v>2201.062</v>
+        <v>2236.563</v>
       </c>
       <c r="G64">
         <v>34.7</v>
@@ -6648,37 +6648,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M64">
-        <v>468.1069722889412</v>
+        <v>475.6570847452145</v>
       </c>
       <c r="N64">
-        <v>-214.9069722889413</v>
+        <v>-222.4570847452146</v>
       </c>
       <c r="O64">
-        <v>-45.13046418067767</v>
+        <v>-46.71598779649506</v>
       </c>
       <c r="P64">
-        <v>-169.7765081082636</v>
+        <v>-175.7410969487195</v>
       </c>
       <c r="Q64">
-        <v>387.5234918917363</v>
+        <v>381.5589030512805</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1230909271884435</v>
+        <v>0.1251798711665095</v>
       </c>
       <c r="T64">
-        <v>1.303236070213327</v>
+        <v>1.33845866670558</v>
       </c>
       <c r="U64">
         <v>0.2126732333250682</v>
       </c>
       <c r="V64">
-        <v>0.1135894211103083</v>
+        <v>0.1117864144260177</v>
       </c>
       <c r="W64">
-        <v>0.1885158038660162</v>
+        <v>0.1888992551272709</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5409020052871827</v>
+        <v>0.532316259171513</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6694,22 +6694,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1653230830617892</v>
+        <v>0.1669918153950399</v>
       </c>
       <c r="C65">
-        <v>-258.4364999342909</v>
+        <v>-310.689979286278</v>
       </c>
       <c r="D65">
-        <v>1943.426500065709</v>
+        <v>1926.674020713722</v>
       </c>
       <c r="E65">
-        <v>449.2630000000001</v>
+        <v>484.7639999999999</v>
       </c>
       <c r="F65">
-        <v>2236.563</v>
+        <v>2272.064</v>
       </c>
       <c r="G65">
         <v>34.7</v>
@@ -6730,37 +6730,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M65">
-        <v>475.6570847452145</v>
+        <v>483.2071972014877</v>
       </c>
       <c r="N65">
-        <v>-222.4570847452146</v>
+        <v>-230.0071972014878</v>
       </c>
       <c r="O65">
-        <v>-46.71598779649506</v>
+        <v>-48.30151141231243</v>
       </c>
       <c r="P65">
-        <v>-175.7410969487195</v>
+        <v>-181.7056857891753</v>
       </c>
       <c r="Q65">
-        <v>381.5589030512805</v>
+        <v>375.5943142108246</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1251798711665095</v>
+        <v>0.1273848675878015</v>
       </c>
       <c r="T65">
-        <v>1.33845866670558</v>
+        <v>1.375638074114068</v>
       </c>
       <c r="U65">
         <v>0.2126732333250682</v>
       </c>
       <c r="V65">
-        <v>0.1117864144260177</v>
+        <v>0.1100397517006112</v>
       </c>
       <c r="W65">
-        <v>0.1888992551272709</v>
+        <v>0.1892707235366115</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.532316259171513</v>
+        <v>0.5239988176219581</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6776,22 +6776,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1669918153950399</v>
+        <v>0.1686605477282906</v>
       </c>
       <c r="C66">
-        <v>-310.689979286278</v>
+        <v>-362.6571117613873</v>
       </c>
       <c r="D66">
-        <v>1926.674020713722</v>
+        <v>1910.207888238613</v>
       </c>
       <c r="E66">
-        <v>484.7639999999999</v>
+        <v>520.2650000000001</v>
       </c>
       <c r="F66">
-        <v>2272.064</v>
+        <v>2307.565</v>
       </c>
       <c r="G66">
         <v>34.7</v>
@@ -6812,37 +6812,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M66">
-        <v>483.2071972014877</v>
+        <v>490.757309657761</v>
       </c>
       <c r="N66">
-        <v>-230.0071972014878</v>
+        <v>-237.557309657761</v>
       </c>
       <c r="O66">
-        <v>-48.30151141231243</v>
+        <v>-49.88703502812982</v>
       </c>
       <c r="P66">
-        <v>-181.7056857891753</v>
+        <v>-187.6702746296312</v>
       </c>
       <c r="Q66">
-        <v>375.5943142108246</v>
+        <v>369.6297253703688</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1273848675878015</v>
+        <v>0.1297158638045958</v>
       </c>
       <c r="T66">
-        <v>1.375638074114068</v>
+        <v>1.414942019088756</v>
       </c>
       <c r="U66">
         <v>0.2126732333250682</v>
       </c>
       <c r="V66">
-        <v>0.1100397517006112</v>
+        <v>0.1083468324436787</v>
       </c>
       <c r="W66">
-        <v>0.1892707235366115</v>
+        <v>0.1896307621487416</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5239988176219581</v>
+        <v>0.5159372973508511</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6858,22 +6858,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1686605477282906</v>
+        <v>0.1703292800615413</v>
       </c>
       <c r="C67">
-        <v>-362.6571117613873</v>
+        <v>-414.3451768534844</v>
       </c>
       <c r="D67">
-        <v>1910.207888238613</v>
+        <v>1894.020823146516</v>
       </c>
       <c r="E67">
-        <v>520.2650000000001</v>
+        <v>555.7660000000003</v>
       </c>
       <c r="F67">
-        <v>2307.565</v>
+        <v>2343.066</v>
       </c>
       <c r="G67">
         <v>34.7</v>
@@ -6894,37 +6894,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M67">
-        <v>490.757309657761</v>
+        <v>498.3074221140342</v>
       </c>
       <c r="N67">
-        <v>-237.557309657761</v>
+        <v>-245.1074221140343</v>
       </c>
       <c r="O67">
-        <v>-49.88703502812982</v>
+        <v>-51.4725586439472</v>
       </c>
       <c r="P67">
-        <v>-187.6702746296312</v>
+        <v>-193.6348634700871</v>
       </c>
       <c r="Q67">
-        <v>369.6297253703688</v>
+        <v>363.6651365299128</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1297158638045958</v>
+        <v>0.1321839774459074</v>
       </c>
       <c r="T67">
-        <v>1.414942019088756</v>
+        <v>1.45655796082666</v>
       </c>
       <c r="U67">
         <v>0.2126732333250682</v>
       </c>
       <c r="V67">
-        <v>0.1083468324436787</v>
+        <v>0.1067052137702896</v>
       </c>
       <c r="W67">
-        <v>0.1896307621487416</v>
+        <v>0.1899798904998981</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5159372973508511</v>
+        <v>0.5081200655728079</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6940,22 +6940,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1703292800615413</v>
+        <v>0.171998012394792</v>
       </c>
       <c r="C68">
-        <v>-414.3451768534844</v>
+        <v>-465.7612093846133</v>
       </c>
       <c r="D68">
-        <v>1894.020823146516</v>
+        <v>1878.105790615387</v>
       </c>
       <c r="E68">
-        <v>555.7660000000003</v>
+        <v>591.2670000000001</v>
       </c>
       <c r="F68">
-        <v>2343.066</v>
+        <v>2378.567</v>
       </c>
       <c r="G68">
         <v>34.7</v>
@@ -6976,37 +6976,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M68">
-        <v>498.3074221140342</v>
+        <v>505.8575345703075</v>
       </c>
       <c r="N68">
-        <v>-245.1074221140343</v>
+        <v>-252.6575345703075</v>
       </c>
       <c r="O68">
-        <v>-51.4725586439472</v>
+        <v>-53.05808225976457</v>
       </c>
       <c r="P68">
-        <v>-193.6348634700871</v>
+        <v>-199.5994523105429</v>
       </c>
       <c r="Q68">
-        <v>363.6651365299128</v>
+        <v>357.700547689457</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1321839774459074</v>
+        <v>0.1348016737321471</v>
       </c>
       <c r="T68">
-        <v>1.45655796082666</v>
+        <v>1.50069608085171</v>
       </c>
       <c r="U68">
         <v>0.2126732333250682</v>
       </c>
       <c r="V68">
-        <v>0.1067052137702896</v>
+        <v>0.1051125986393898</v>
       </c>
       <c r="W68">
-        <v>0.1899798904998981</v>
+        <v>0.190318597109229</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5081200655728079</v>
+        <v>0.5005361839970943</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7022,22 +7022,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.171998012394792</v>
+        <v>0.1977811909860263</v>
       </c>
       <c r="C69">
-        <v>-465.7612093846133</v>
+        <v>-717.0762987017288</v>
       </c>
       <c r="D69">
-        <v>1878.105790615387</v>
+        <v>1662.291701298271</v>
       </c>
       <c r="E69">
-        <v>591.2670000000001</v>
+        <v>626.7680000000003</v>
       </c>
       <c r="F69">
-        <v>2378.567</v>
+        <v>2414.068</v>
       </c>
       <c r="G69">
         <v>34.7</v>
@@ -7058,45 +7058,45 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M69">
-        <v>505.8575345703075</v>
+        <v>597.9000270265808</v>
       </c>
       <c r="N69">
-        <v>-252.6575345703075</v>
+        <v>-344.7000270265809</v>
       </c>
       <c r="O69">
-        <v>-53.05808225976457</v>
+        <v>-72.38700567558197</v>
       </c>
       <c r="P69">
-        <v>-199.5994523105429</v>
+        <v>-272.3130213509989</v>
       </c>
       <c r="Q69">
-        <v>357.700547689457</v>
+        <v>284.9869786490011</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1348016737321471</v>
+        <v>0.1385656205924755</v>
       </c>
       <c r="T69">
-        <v>1.50069608085171</v>
+        <v>1.564161632284241</v>
       </c>
       <c r="U69">
-        <v>0.2126732333250682</v>
+        <v>0.2476732333250682</v>
       </c>
       <c r="V69">
-        <v>0.1051125986393898</v>
+        <v>0.08893125538801175</v>
       </c>
       <c r="W69">
-        <v>0.190318597109229</v>
+        <v>0.2256473417594619</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5005361839970943</v>
+        <v>0.4234821685143417</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7104,22 +7104,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1977811909860263</v>
+        <v>0.1997999233192769</v>
       </c>
       <c r="C70">
-        <v>-717.0762987017288</v>
+        <v>-767.3997266468687</v>
       </c>
       <c r="D70">
-        <v>1662.291701298271</v>
+        <v>1647.469273353131</v>
       </c>
       <c r="E70">
-        <v>626.7680000000003</v>
+        <v>662.269</v>
       </c>
       <c r="F70">
-        <v>2414.068</v>
+        <v>2449.569</v>
       </c>
       <c r="G70">
         <v>34.7</v>
@@ -7140,37 +7140,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M70">
-        <v>597.9000270265808</v>
+        <v>606.6926744828539</v>
       </c>
       <c r="N70">
-        <v>-344.7000270265809</v>
+        <v>-353.492674482854</v>
       </c>
       <c r="O70">
-        <v>-72.38700567558197</v>
+        <v>-74.23346164139933</v>
       </c>
       <c r="P70">
-        <v>-272.3130213509989</v>
+        <v>-279.2592128414547</v>
       </c>
       <c r="Q70">
-        <v>284.9869786490011</v>
+        <v>278.0407871585453</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1385656205924755</v>
+        <v>0.1415580599664263</v>
       </c>
       <c r="T70">
-        <v>1.564161632284241</v>
+        <v>1.61461845913212</v>
       </c>
       <c r="U70">
         <v>0.2476732333250682</v>
       </c>
       <c r="V70">
-        <v>0.08893125538801175</v>
+        <v>0.08764239661427246</v>
       </c>
       <c r="W70">
-        <v>0.2256473417594619</v>
+        <v>0.2259665575792533</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4234821685143417</v>
+        <v>0.4173447457822499</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7186,22 +7186,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1997999233192769</v>
+        <v>0.2018186556525276</v>
       </c>
       <c r="C71">
-        <v>-767.3997266468687</v>
+        <v>-817.461151706985</v>
       </c>
       <c r="D71">
-        <v>1647.469273353131</v>
+        <v>1632.908848293015</v>
       </c>
       <c r="E71">
-        <v>662.269</v>
+        <v>697.7700000000002</v>
       </c>
       <c r="F71">
-        <v>2449.569</v>
+        <v>2485.07</v>
       </c>
       <c r="G71">
         <v>34.7</v>
@@ -7222,37 +7222,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M71">
-        <v>606.6926744828539</v>
+        <v>615.4853219391273</v>
       </c>
       <c r="N71">
-        <v>-353.492674482854</v>
+        <v>-362.2853219391274</v>
       </c>
       <c r="O71">
-        <v>-74.23346164139933</v>
+        <v>-76.07991760721674</v>
       </c>
       <c r="P71">
-        <v>-279.2592128414547</v>
+        <v>-286.2054043319106</v>
       </c>
       <c r="Q71">
-        <v>278.0407871585453</v>
+        <v>271.0945956680894</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1415580599664263</v>
+        <v>0.1447499952986405</v>
       </c>
       <c r="T71">
-        <v>1.61461845913212</v>
+        <v>1.668439074436524</v>
       </c>
       <c r="U71">
         <v>0.2476732333250682</v>
       </c>
       <c r="V71">
-        <v>0.08764239661427246</v>
+        <v>0.0863903623769257</v>
       </c>
       <c r="W71">
-        <v>0.2259665575792533</v>
+        <v>0.2262766529470507</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4173447457822499</v>
+        <v>0.4113826779853604</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7268,22 +7268,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2018186556525276</v>
+        <v>0.2038373879857783</v>
       </c>
       <c r="C72">
-        <v>-817.461151706985</v>
+        <v>-867.2674598120502</v>
       </c>
       <c r="D72">
-        <v>1632.908848293015</v>
+        <v>1618.60354018795</v>
       </c>
       <c r="E72">
-        <v>697.7700000000002</v>
+        <v>733.2710000000004</v>
       </c>
       <c r="F72">
-        <v>2485.07</v>
+        <v>2520.571</v>
       </c>
       <c r="G72">
         <v>34.7</v>
@@ -7304,37 +7304,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M72">
-        <v>615.4853219391273</v>
+        <v>624.2779693954005</v>
       </c>
       <c r="N72">
-        <v>-362.2853219391274</v>
+        <v>-371.0779693954006</v>
       </c>
       <c r="O72">
-        <v>-76.07991760721674</v>
+        <v>-77.92637357303413</v>
       </c>
       <c r="P72">
-        <v>-286.2054043319106</v>
+        <v>-293.1515958223665</v>
       </c>
       <c r="Q72">
-        <v>271.0945956680894</v>
+        <v>264.1484041776335</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1447499952986405</v>
+        <v>0.1481620641020419</v>
       </c>
       <c r="T72">
-        <v>1.668439074436524</v>
+        <v>1.725971456313646</v>
       </c>
       <c r="U72">
         <v>0.2476732333250682</v>
       </c>
       <c r="V72">
-        <v>0.0863903623769257</v>
+        <v>0.08517359670964506</v>
       </c>
       <c r="W72">
-        <v>0.2262766529470507</v>
+        <v>0.226578013234065</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4113826779853604</v>
+        <v>0.4055885557602146</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7350,22 +7350,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2038373879857783</v>
+        <v>0.205856120319029</v>
       </c>
       <c r="C73">
-        <v>-867.2674598120498</v>
+        <v>-916.8252976873202</v>
       </c>
       <c r="D73">
-        <v>1618.60354018795</v>
+        <v>1604.546702312679</v>
       </c>
       <c r="E73">
-        <v>733.271</v>
+        <v>768.7719999999997</v>
       </c>
       <c r="F73">
-        <v>2520.571</v>
+        <v>2556.072</v>
       </c>
       <c r="G73">
         <v>34.7</v>
@@ -7386,37 +7386,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M73">
-        <v>624.2779693954004</v>
+        <v>633.0706168516737</v>
       </c>
       <c r="N73">
-        <v>-371.0779693954005</v>
+        <v>-379.8706168516737</v>
       </c>
       <c r="O73">
-        <v>-77.9263735730341</v>
+        <v>-79.77282953885148</v>
       </c>
       <c r="P73">
-        <v>-293.1515958223664</v>
+        <v>-300.0977873128222</v>
       </c>
       <c r="Q73">
-        <v>264.1484041776336</v>
+        <v>257.2022126871777</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1481620641020419</v>
+        <v>0.1518178521056862</v>
       </c>
       <c r="T73">
-        <v>1.725971456313645</v>
+        <v>1.787613294039132</v>
       </c>
       <c r="U73">
         <v>0.2476732333250682</v>
       </c>
       <c r="V73">
-        <v>0.08517359670964507</v>
+        <v>0.08399063008867777</v>
       </c>
       <c r="W73">
-        <v>0.226578013234065</v>
+        <v>0.2268710024019956</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4055885557602147</v>
+        <v>0.3999553813746561</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7432,22 +7432,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.205856120319029</v>
+        <v>0.2078748526522797</v>
       </c>
       <c r="C74">
-        <v>-916.8252976873202</v>
+        <v>-966.1410831508258</v>
       </c>
       <c r="D74">
-        <v>1604.546702312679</v>
+        <v>1590.731916849174</v>
       </c>
       <c r="E74">
-        <v>768.7719999999997</v>
+        <v>804.2729999999999</v>
       </c>
       <c r="F74">
-        <v>2556.072</v>
+        <v>2591.573</v>
       </c>
       <c r="G74">
         <v>34.7</v>
@@ -7468,37 +7468,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M74">
-        <v>633.0706168516737</v>
+        <v>641.8632643079469</v>
       </c>
       <c r="N74">
-        <v>-379.8706168516737</v>
+        <v>-388.663264307947</v>
       </c>
       <c r="O74">
-        <v>-79.77282953885148</v>
+        <v>-81.61928550466887</v>
       </c>
       <c r="P74">
-        <v>-300.0977873128222</v>
+        <v>-307.0439788032781</v>
       </c>
       <c r="Q74">
-        <v>257.2022126871777</v>
+        <v>250.2560211967219</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1518178521056862</v>
+        <v>0.1557444392207116</v>
       </c>
       <c r="T74">
-        <v>1.787613294039132</v>
+        <v>1.85382119381836</v>
       </c>
       <c r="U74">
         <v>0.2476732333250682</v>
       </c>
       <c r="V74">
-        <v>0.08399063008867777</v>
+        <v>0.08284007351212055</v>
       </c>
       <c r="W74">
-        <v>0.2268710024019956</v>
+        <v>0.227155964469435</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3999553813746561</v>
+        <v>0.3944765405339073</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7514,22 +7514,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2078748526522797</v>
+        <v>0.2098935849855303</v>
       </c>
       <c r="C75">
-        <v>-966.1410831508258</v>
+        <v>-1015.221014883451</v>
       </c>
       <c r="D75">
-        <v>1590.731916849174</v>
+        <v>1577.152985116549</v>
       </c>
       <c r="E75">
-        <v>804.2729999999999</v>
+        <v>839.7740000000001</v>
       </c>
       <c r="F75">
-        <v>2591.573</v>
+        <v>2627.074</v>
       </c>
       <c r="G75">
         <v>34.7</v>
@@ -7550,37 +7550,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M75">
-        <v>641.8632643079469</v>
+        <v>650.6559117642201</v>
       </c>
       <c r="N75">
-        <v>-388.663264307947</v>
+        <v>-397.4559117642202</v>
       </c>
       <c r="O75">
-        <v>-81.61928550466887</v>
+        <v>-83.46574147048624</v>
       </c>
       <c r="P75">
-        <v>-307.0439788032781</v>
+        <v>-313.990170293734</v>
       </c>
       <c r="Q75">
-        <v>250.2560211967219</v>
+        <v>243.309829706266</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1557444392207116</v>
+        <v>0.1599730714984313</v>
       </c>
       <c r="T75">
-        <v>1.85382119381836</v>
+        <v>1.92512200896522</v>
       </c>
       <c r="U75">
         <v>0.2476732333250682</v>
       </c>
       <c r="V75">
-        <v>0.08284007351212055</v>
+        <v>0.08172061305925406</v>
       </c>
       <c r="W75">
-        <v>0.227155964469435</v>
+        <v>0.2274332248593759</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3944765405339073</v>
+        <v>0.3891457764726384</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7596,22 +7596,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2098935849855303</v>
+        <v>0.211912317318781</v>
       </c>
       <c r="C76">
-        <v>-1015.221014883451</v>
+        <v>-1064.071081702849</v>
       </c>
       <c r="D76">
-        <v>1577.152985116549</v>
+        <v>1563.803918297151</v>
       </c>
       <c r="E76">
-        <v>839.7740000000001</v>
+        <v>875.2749999999999</v>
       </c>
       <c r="F76">
-        <v>2627.074</v>
+        <v>2662.575</v>
       </c>
       <c r="G76">
         <v>34.7</v>
@@ -7632,37 +7632,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M76">
-        <v>650.6559117642201</v>
+        <v>659.4485592204934</v>
       </c>
       <c r="N76">
-        <v>-397.4559117642202</v>
+        <v>-406.2485592204935</v>
       </c>
       <c r="O76">
-        <v>-83.46574147048624</v>
+        <v>-85.31219743630362</v>
       </c>
       <c r="P76">
-        <v>-313.990170293734</v>
+        <v>-320.9363617841898</v>
       </c>
       <c r="Q76">
-        <v>243.309829706266</v>
+        <v>236.3636382158101</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1599730714984313</v>
+        <v>0.1645399943583686</v>
       </c>
       <c r="T76">
-        <v>1.92512200896522</v>
+        <v>2.002126889323829</v>
       </c>
       <c r="U76">
         <v>0.2476732333250682</v>
       </c>
       <c r="V76">
-        <v>0.08172061305925406</v>
+        <v>0.08063100488513067</v>
       </c>
       <c r="W76">
-        <v>0.2274332248593759</v>
+        <v>0.2277030916389185</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3891457764726384</v>
+        <v>0.3839571661196699</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7678,22 +7678,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.211912317318781</v>
+        <v>0.2139310496520317</v>
       </c>
       <c r="C77">
-        <v>-1064.071081702849</v>
+        <v>-1112.697071370342</v>
       </c>
       <c r="D77">
-        <v>1563.803918297151</v>
+        <v>1550.678928629658</v>
       </c>
       <c r="E77">
-        <v>875.2749999999999</v>
+        <v>910.7760000000001</v>
       </c>
       <c r="F77">
-        <v>2662.575</v>
+        <v>2698.076</v>
       </c>
       <c r="G77">
         <v>34.7</v>
@@ -7714,37 +7714,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M77">
-        <v>659.4485592204934</v>
+        <v>668.2412066767666</v>
       </c>
       <c r="N77">
-        <v>-406.2485592204935</v>
+        <v>-415.0412066767667</v>
       </c>
       <c r="O77">
-        <v>-85.31219743630362</v>
+        <v>-87.158653402121</v>
       </c>
       <c r="P77">
-        <v>-320.9363617841898</v>
+        <v>-327.8825532746457</v>
       </c>
       <c r="Q77">
-        <v>236.3636382158101</v>
+        <v>229.4174467253542</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1645399943583686</v>
+        <v>0.1694874941233006</v>
       </c>
       <c r="T77">
-        <v>2.002126889323829</v>
+        <v>2.085548843045655</v>
       </c>
       <c r="U77">
         <v>0.2476732333250682</v>
       </c>
       <c r="V77">
-        <v>0.08063100488513067</v>
+        <v>0.07957007061032631</v>
       </c>
       <c r="W77">
-        <v>0.2277030916389185</v>
+        <v>0.2279658566611047</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3839571661196699</v>
+        <v>0.3789050981444111</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7760,22 +7760,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2139310496520317</v>
+        <v>0.2159497819852824</v>
       </c>
       <c r="C78">
-        <v>-1112.697071370342</v>
+        <v>-1161.104578958011</v>
       </c>
       <c r="D78">
-        <v>1550.678928629658</v>
+        <v>1537.772421041988</v>
       </c>
       <c r="E78">
-        <v>910.7760000000001</v>
+        <v>946.2769999999998</v>
       </c>
       <c r="F78">
-        <v>2698.076</v>
+        <v>2733.577</v>
       </c>
       <c r="G78">
         <v>34.7</v>
@@ -7796,37 +7796,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M78">
-        <v>668.2412066767666</v>
+        <v>677.0338541330399</v>
       </c>
       <c r="N78">
-        <v>-415.0412066767667</v>
+        <v>-423.8338541330399</v>
       </c>
       <c r="O78">
-        <v>-87.158653402121</v>
+        <v>-89.00510936793839</v>
       </c>
       <c r="P78">
-        <v>-327.8825532746457</v>
+        <v>-334.8287447651015</v>
       </c>
       <c r="Q78">
-        <v>229.4174467253542</v>
+        <v>222.4712552348984</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1694874941233006</v>
+        <v>0.1748652112590963</v>
       </c>
       <c r="T78">
-        <v>2.085548843045655</v>
+        <v>2.176224879699814</v>
       </c>
       <c r="U78">
         <v>0.2476732333250682</v>
       </c>
       <c r="V78">
-        <v>0.07957007061032631</v>
+        <v>0.07853669306993247</v>
       </c>
       <c r="W78">
-        <v>0.2279658566611047</v>
+        <v>0.2282217966177795</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3789050981444111</v>
+        <v>0.3739842527139642</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7842,22 +7842,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2159497819852824</v>
+        <v>0.2179685143185331</v>
       </c>
       <c r="C79">
-        <v>-1161.104578958011</v>
+        <v>-1209.299014801405</v>
       </c>
       <c r="D79">
-        <v>1537.772421041988</v>
+        <v>1525.078985198595</v>
       </c>
       <c r="E79">
-        <v>946.2769999999998</v>
+        <v>981.778</v>
       </c>
       <c r="F79">
-        <v>2733.577</v>
+        <v>2769.078</v>
       </c>
       <c r="G79">
         <v>34.7</v>
@@ -7878,37 +7878,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M79">
-        <v>677.0338541330399</v>
+        <v>685.8265015893131</v>
       </c>
       <c r="N79">
-        <v>-423.8338541330399</v>
+        <v>-432.6265015893132</v>
       </c>
       <c r="O79">
-        <v>-89.00510936793839</v>
+        <v>-90.85156533375577</v>
       </c>
       <c r="P79">
-        <v>-334.8287447651015</v>
+        <v>-341.7749362555574</v>
       </c>
       <c r="Q79">
-        <v>222.4712552348984</v>
+        <v>215.5250637444425</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1748652112590963</v>
+        <v>0.1807318117708734</v>
       </c>
       <c r="T79">
-        <v>2.176224879699814</v>
+        <v>2.275144192413442</v>
       </c>
       <c r="U79">
         <v>0.2476732333250682</v>
       </c>
       <c r="V79">
-        <v>0.07853669306993247</v>
+        <v>0.07752981238954872</v>
       </c>
       <c r="W79">
-        <v>0.2282217966177795</v>
+        <v>0.2284711740114627</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3739842527139642</v>
+        <v>0.3691895828073749</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7924,22 +7924,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2179685143185331</v>
+        <v>0.2199872466517838</v>
       </c>
       <c r="C80">
-        <v>-1209.299014801405</v>
+        <v>-1257.285612061582</v>
       </c>
       <c r="D80">
-        <v>1525.078985198595</v>
+        <v>1512.593387938418</v>
       </c>
       <c r="E80">
-        <v>981.778</v>
+        <v>1017.279</v>
       </c>
       <c r="F80">
-        <v>2769.078</v>
+        <v>2804.579</v>
       </c>
       <c r="G80">
         <v>34.7</v>
@@ -7960,37 +7960,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M80">
-        <v>685.8265015893131</v>
+        <v>694.6191490455865</v>
       </c>
       <c r="N80">
-        <v>-432.6265015893132</v>
+        <v>-441.4191490455866</v>
       </c>
       <c r="O80">
-        <v>-90.85156533375577</v>
+        <v>-92.69802129957317</v>
       </c>
       <c r="P80">
-        <v>-341.7749362555574</v>
+        <v>-348.7211277460134</v>
       </c>
       <c r="Q80">
-        <v>215.5250637444425</v>
+        <v>208.5788722539866</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1807318117708734</v>
+        <v>0.187157136140915</v>
       </c>
       <c r="T80">
-        <v>2.275144192413442</v>
+        <v>2.383484392052178</v>
       </c>
       <c r="U80">
         <v>0.2476732333250682</v>
       </c>
       <c r="V80">
-        <v>0.07752981238954872</v>
+        <v>0.07654842235930126</v>
       </c>
       <c r="W80">
-        <v>0.2284711740114627</v>
+        <v>0.2287142380534071</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3691895828073749</v>
+        <v>0.3645162969490536</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8006,22 +8006,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2199872466517838</v>
+        <v>0.2220059789850345</v>
       </c>
       <c r="C81">
-        <v>-1257.285612061582</v>
+        <v>-1305.069433918732</v>
       </c>
       <c r="D81">
-        <v>1512.593387938418</v>
+        <v>1500.310566081268</v>
       </c>
       <c r="E81">
-        <v>1017.279</v>
+        <v>1052.78</v>
       </c>
       <c r="F81">
-        <v>2804.579</v>
+        <v>2840.08</v>
       </c>
       <c r="G81">
         <v>34.7</v>
@@ -8042,37 +8042,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M81">
-        <v>694.6191490455865</v>
+        <v>703.4117965018596</v>
       </c>
       <c r="N81">
-        <v>-441.4191490455866</v>
+        <v>-450.2117965018597</v>
       </c>
       <c r="O81">
-        <v>-92.69802129957317</v>
+        <v>-94.54447726539053</v>
       </c>
       <c r="P81">
-        <v>-348.7211277460134</v>
+        <v>-355.6673192364692</v>
       </c>
       <c r="Q81">
-        <v>208.5788722539866</v>
+        <v>201.6326807635308</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.187157136140915</v>
+        <v>0.1942249929479607</v>
       </c>
       <c r="T81">
-        <v>2.383484392052178</v>
+        <v>2.502658611654786</v>
       </c>
       <c r="U81">
         <v>0.2476732333250682</v>
       </c>
       <c r="V81">
-        <v>0.07654842235930126</v>
+        <v>0.07559156707981</v>
       </c>
       <c r="W81">
-        <v>0.2287142380534071</v>
+        <v>0.2289512254943029</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3645162969490536</v>
+        <v>0.3599598432371905</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8088,22 +8088,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2220059789850345</v>
+        <v>0.2240247113182851</v>
       </c>
       <c r="C82">
-        <v>-1305.069433918732</v>
+        <v>-1352.655380418126</v>
       </c>
       <c r="D82">
-        <v>1500.310566081268</v>
+        <v>1488.225619581875</v>
       </c>
       <c r="E82">
-        <v>1052.78</v>
+        <v>1088.281</v>
       </c>
       <c r="F82">
-        <v>2840.08</v>
+        <v>2875.581</v>
       </c>
       <c r="G82">
         <v>34.7</v>
@@ -8124,37 +8124,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M82">
-        <v>703.4117965018596</v>
+        <v>712.204443958133</v>
       </c>
       <c r="N82">
-        <v>-450.2117965018597</v>
+        <v>-459.004443958133</v>
       </c>
       <c r="O82">
-        <v>-94.54447726539053</v>
+        <v>-96.39093323120794</v>
       </c>
       <c r="P82">
-        <v>-355.6673192364692</v>
+        <v>-362.6135107269251</v>
       </c>
       <c r="Q82">
-        <v>201.6326807635308</v>
+        <v>194.6864892730749</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1942249929479607</v>
+        <v>0.2020368346820639</v>
       </c>
       <c r="T82">
-        <v>2.502658611654786</v>
+        <v>2.634377485952407</v>
       </c>
       <c r="U82">
         <v>0.2476732333250682</v>
       </c>
       <c r="V82">
-        <v>0.07559156707981</v>
+        <v>0.07465833785660246</v>
       </c>
       <c r="W82">
-        <v>0.2289512254943029</v>
+        <v>0.2291823613934481</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3599598432371905</v>
+        <v>0.3555158945552498</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8170,22 +8170,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2240247113182851</v>
+        <v>0.2260434436515358</v>
       </c>
       <c r="C83">
-        <v>-1352.655380418126</v>
+        <v>-1400.048194987837</v>
       </c>
       <c r="D83">
-        <v>1488.225619581875</v>
+        <v>1476.333805012163</v>
       </c>
       <c r="E83">
-        <v>1088.281</v>
+        <v>1123.782</v>
       </c>
       <c r="F83">
-        <v>2875.581</v>
+        <v>2911.082</v>
       </c>
       <c r="G83">
         <v>34.7</v>
@@ -8206,37 +8206,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M83">
-        <v>712.204443958133</v>
+        <v>720.9970914144062</v>
       </c>
       <c r="N83">
-        <v>-459.004443958133</v>
+        <v>-467.7970914144063</v>
       </c>
       <c r="O83">
-        <v>-96.39093323120794</v>
+        <v>-98.23738919702532</v>
       </c>
       <c r="P83">
-        <v>-362.6135107269251</v>
+        <v>-369.559702217381</v>
       </c>
       <c r="Q83">
-        <v>194.6864892730749</v>
+        <v>187.740297782619</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2020368346820639</v>
+        <v>0.2107166588310675</v>
       </c>
       <c r="T83">
-        <v>2.634377485952407</v>
+        <v>2.78073179072754</v>
       </c>
       <c r="U83">
         <v>0.2476732333250682</v>
       </c>
       <c r="V83">
-        <v>0.07465833785660246</v>
+        <v>0.07374787032176584</v>
       </c>
       <c r="W83">
-        <v>0.2291823613934481</v>
+        <v>0.2294078598316386</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3555158945552498</v>
+        <v>0.3511803348655517</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8252,22 +8252,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2260434436515358</v>
+        <v>0.2280621759847865</v>
       </c>
       <c r="C84">
-        <v>-1400.048194987837</v>
+        <v>-1447.252470646474</v>
       </c>
       <c r="D84">
-        <v>1476.333805012163</v>
+        <v>1464.630529353527</v>
       </c>
       <c r="E84">
-        <v>1123.782</v>
+        <v>1159.283</v>
       </c>
       <c r="F84">
-        <v>2911.082</v>
+        <v>2946.583</v>
       </c>
       <c r="G84">
         <v>34.7</v>
@@ -8288,37 +8288,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M84">
-        <v>720.9970914144062</v>
+        <v>729.7897388706795</v>
       </c>
       <c r="N84">
-        <v>-467.7970914144063</v>
+        <v>-476.5897388706795</v>
       </c>
       <c r="O84">
-        <v>-98.23738919702532</v>
+        <v>-100.0838451628427</v>
       </c>
       <c r="P84">
-        <v>-369.559702217381</v>
+        <v>-376.5058937078368</v>
       </c>
       <c r="Q84">
-        <v>187.740297782619</v>
+        <v>180.7941062921631</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2107166588310675</v>
+        <v>0.2204176387623068</v>
       </c>
       <c r="T84">
-        <v>2.78073179072754</v>
+        <v>2.944304249005631</v>
       </c>
       <c r="U84">
         <v>0.2476732333250682</v>
       </c>
       <c r="V84">
-        <v>0.07374787032176584</v>
+        <v>0.07285934176367227</v>
       </c>
       <c r="W84">
-        <v>0.2294078598316386</v>
+        <v>0.2296279245725233</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3511803348655517</v>
+        <v>0.3469492464936775</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8334,22 +8334,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2280621759847865</v>
+        <v>0.2300809083180372</v>
       </c>
       <c r="C85">
-        <v>-1447.252470646474</v>
+        <v>-1494.272655917953</v>
       </c>
       <c r="D85">
-        <v>1464.630529353527</v>
+        <v>1453.111344082047</v>
       </c>
       <c r="E85">
-        <v>1159.283</v>
+        <v>1194.784</v>
       </c>
       <c r="F85">
-        <v>2946.583</v>
+        <v>2982.084</v>
       </c>
       <c r="G85">
         <v>34.7</v>
@@ -8370,37 +8370,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M85">
-        <v>729.7897388706795</v>
+        <v>738.5823863269527</v>
       </c>
       <c r="N85">
-        <v>-476.5897388706795</v>
+        <v>-485.3823863269528</v>
       </c>
       <c r="O85">
-        <v>-100.0838451628427</v>
+        <v>-101.9303011286601</v>
       </c>
       <c r="P85">
-        <v>-376.5058937078368</v>
+        <v>-383.4520851982927</v>
       </c>
       <c r="Q85">
-        <v>180.7941062921631</v>
+        <v>173.8479148017072</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2204176387623068</v>
+        <v>0.231331241184951</v>
       </c>
       <c r="T85">
-        <v>2.944304249005631</v>
+        <v>3.128323264568484</v>
       </c>
       <c r="U85">
         <v>0.2476732333250682</v>
       </c>
       <c r="V85">
-        <v>0.07285934176367227</v>
+        <v>0.07199196864743809</v>
       </c>
       <c r="W85">
-        <v>0.2296279245725233</v>
+        <v>0.2298427496767203</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3469492464936775</v>
+        <v>0.3428188983211338</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8416,22 +8416,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2300809083180372</v>
+        <v>0.2320996406512879</v>
       </c>
       <c r="C86">
-        <v>-1494.272655917953</v>
+        <v>-1541.113060469355</v>
       </c>
       <c r="D86">
-        <v>1453.111344082047</v>
+        <v>1441.771939530645</v>
       </c>
       <c r="E86">
-        <v>1194.784</v>
+        <v>1230.285</v>
       </c>
       <c r="F86">
-        <v>2982.084</v>
+        <v>3017.585</v>
       </c>
       <c r="G86">
         <v>34.7</v>
@@ -8452,37 +8452,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M86">
-        <v>738.5823863269526</v>
+        <v>747.3750337832259</v>
       </c>
       <c r="N86">
-        <v>-485.3823863269527</v>
+        <v>-494.175033783226</v>
       </c>
       <c r="O86">
-        <v>-101.93030112866</v>
+        <v>-103.7767570944775</v>
       </c>
       <c r="P86">
-        <v>-383.4520851982926</v>
+        <v>-390.3982766887485</v>
       </c>
       <c r="Q86">
-        <v>173.8479148017074</v>
+        <v>166.9017233112514</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2313312411849509</v>
+        <v>0.2436999905972809</v>
       </c>
       <c r="T86">
-        <v>3.128323264568482</v>
+        <v>3.336878148873047</v>
       </c>
       <c r="U86">
         <v>0.2476732333250682</v>
       </c>
       <c r="V86">
-        <v>0.07199196864743811</v>
+        <v>0.0711450043104094</v>
       </c>
       <c r="W86">
-        <v>0.2298427496767203</v>
+        <v>0.2300525200725832</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3428188983211338</v>
+        <v>0.3387857348114733</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8498,22 +8498,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2320996406512879</v>
+        <v>0.2341183729845385</v>
       </c>
       <c r="C87">
-        <v>-1541.113060469355</v>
+        <v>-1587.777860486838</v>
       </c>
       <c r="D87">
-        <v>1441.771939530645</v>
+        <v>1430.608139513162</v>
       </c>
       <c r="E87">
-        <v>1230.285</v>
+        <v>1265.786</v>
       </c>
       <c r="F87">
-        <v>3017.585</v>
+        <v>3053.086</v>
       </c>
       <c r="G87">
         <v>34.7</v>
@@ -8534,37 +8534,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M87">
-        <v>747.3750337832259</v>
+        <v>756.1676812394991</v>
       </c>
       <c r="N87">
-        <v>-494.175033783226</v>
+        <v>-502.9676812394991</v>
       </c>
       <c r="O87">
-        <v>-103.7767570944775</v>
+        <v>-105.6232130602948</v>
       </c>
       <c r="P87">
-        <v>-390.3982766887485</v>
+        <v>-397.3444681792043</v>
       </c>
       <c r="Q87">
-        <v>166.9017233112514</v>
+        <v>159.9555318207956</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2436999905972809</v>
+        <v>0.2578357042113724</v>
       </c>
       <c r="T87">
-        <v>3.336878148873047</v>
+        <v>3.575226588078265</v>
       </c>
       <c r="U87">
         <v>0.2476732333250682</v>
       </c>
       <c r="V87">
-        <v>0.0711450043104094</v>
+        <v>0.07031773681842791</v>
       </c>
       <c r="W87">
-        <v>0.2300525200725832</v>
+        <v>0.230257412087147</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3387857348114733</v>
+        <v>0.3348463658020376</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8580,22 +8580,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2341183729845385</v>
+        <v>0.2361371053177892</v>
       </c>
       <c r="C88">
-        <v>-1587.777860486838</v>
+        <v>-1634.271103803721</v>
       </c>
       <c r="D88">
-        <v>1430.608139513162</v>
+        <v>1419.615896196279</v>
       </c>
       <c r="E88">
-        <v>1265.786</v>
+        <v>1301.287</v>
       </c>
       <c r="F88">
-        <v>3053.086</v>
+        <v>3088.587</v>
       </c>
       <c r="G88">
         <v>34.7</v>
@@ -8616,37 +8616,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M88">
-        <v>756.1676812394991</v>
+        <v>764.9603286957723</v>
       </c>
       <c r="N88">
-        <v>-502.9676812394991</v>
+        <v>-511.7603286957724</v>
       </c>
       <c r="O88">
-        <v>-105.6232130602948</v>
+        <v>-107.4696690261122</v>
       </c>
       <c r="P88">
-        <v>-397.3444681792043</v>
+        <v>-404.2906596696602</v>
       </c>
       <c r="Q88">
-        <v>159.9555318207956</v>
+        <v>153.0093403303398</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2578357042113724</v>
+        <v>0.2741461429968626</v>
       </c>
       <c r="T88">
-        <v>3.575226588078265</v>
+        <v>3.850244017930439</v>
       </c>
       <c r="U88">
         <v>0.2476732333250682</v>
       </c>
       <c r="V88">
-        <v>0.07031773681842791</v>
+        <v>0.06950948696994023</v>
       </c>
       <c r="W88">
-        <v>0.230257412087147</v>
+        <v>0.2304575939404564</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3348463658020376</v>
+        <v>0.3309975569997154</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8662,22 +8662,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2361371053177892</v>
+        <v>0.2381558376510399</v>
       </c>
       <c r="C89">
-        <v>-1634.271103803721</v>
+        <v>-1680.596714793953</v>
       </c>
       <c r="D89">
-        <v>1419.615896196279</v>
+        <v>1408.791285206047</v>
       </c>
       <c r="E89">
-        <v>1301.287</v>
+        <v>1336.788</v>
       </c>
       <c r="F89">
-        <v>3088.587</v>
+        <v>3124.088</v>
       </c>
       <c r="G89">
         <v>34.7</v>
@@ -8698,37 +8698,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M89">
-        <v>764.9603286957723</v>
+        <v>773.7529761520456</v>
       </c>
       <c r="N89">
-        <v>-511.7603286957724</v>
+        <v>-520.5529761520456</v>
       </c>
       <c r="O89">
-        <v>-107.4696690261122</v>
+        <v>-109.3161249919296</v>
       </c>
       <c r="P89">
-        <v>-404.2906596696602</v>
+        <v>-411.236851160116</v>
       </c>
       <c r="Q89">
-        <v>153.0093403303398</v>
+        <v>146.0631488398839</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2741461429968626</v>
+        <v>0.2931749882466012</v>
       </c>
       <c r="T89">
-        <v>3.850244017930439</v>
+        <v>4.17109768609131</v>
       </c>
       <c r="U89">
         <v>0.2476732333250682</v>
       </c>
       <c r="V89">
-        <v>0.06950948696994023</v>
+        <v>0.06871960643619091</v>
       </c>
       <c r="W89">
-        <v>0.2304575939404564</v>
+        <v>0.2306532262061906</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3309975569997154</v>
+        <v>0.3272362211247186</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8744,22 +8744,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2381558376510399</v>
+        <v>0.2401745699842905</v>
       </c>
       <c r="C90">
-        <v>-1680.596714793953</v>
+        <v>-1726.7584990434</v>
       </c>
       <c r="D90">
-        <v>1408.791285206047</v>
+        <v>1398.1305009566</v>
       </c>
       <c r="E90">
-        <v>1336.788</v>
+        <v>1372.289</v>
       </c>
       <c r="F90">
-        <v>3124.088</v>
+        <v>3159.589</v>
       </c>
       <c r="G90">
         <v>34.7</v>
@@ -8780,37 +8780,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M90">
-        <v>773.7529761520456</v>
+        <v>782.5456236083188</v>
       </c>
       <c r="N90">
-        <v>-520.5529761520456</v>
+        <v>-529.3456236083189</v>
       </c>
       <c r="O90">
-        <v>-109.3161249919296</v>
+        <v>-111.162580957747</v>
       </c>
       <c r="P90">
-        <v>-411.236851160116</v>
+        <v>-418.1830426505719</v>
       </c>
       <c r="Q90">
-        <v>146.0631488398839</v>
+        <v>139.116957349428</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2931749882466012</v>
+        <v>0.3156636235417468</v>
       </c>
       <c r="T90">
-        <v>4.17109768609131</v>
+        <v>4.550288384826883</v>
       </c>
       <c r="U90">
         <v>0.2476732333250682</v>
       </c>
       <c r="V90">
-        <v>0.06871960643619091</v>
+        <v>0.0679474760267955</v>
       </c>
       <c r="W90">
-        <v>0.2306532262061906</v>
+        <v>0.2308444622412342</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3272362211247186</v>
+        <v>0.3235594096514072</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8826,22 +8826,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2401745699842905</v>
+        <v>0.2421933023175413</v>
       </c>
       <c r="C91">
-        <v>-1726.7584990434</v>
+        <v>-1772.760147810629</v>
       </c>
       <c r="D91">
-        <v>1398.1305009566</v>
+        <v>1387.629852189371</v>
       </c>
       <c r="E91">
-        <v>1372.289</v>
+        <v>1407.79</v>
       </c>
       <c r="F91">
-        <v>3159.589</v>
+        <v>3195.09</v>
       </c>
       <c r="G91">
         <v>34.7</v>
@@ -8862,37 +8862,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M91">
-        <v>782.5456236083188</v>
+        <v>791.3382710645922</v>
       </c>
       <c r="N91">
-        <v>-529.3456236083189</v>
+        <v>-538.1382710645922</v>
       </c>
       <c r="O91">
-        <v>-111.162580957747</v>
+        <v>-113.0090369235644</v>
       </c>
       <c r="P91">
-        <v>-418.1830426505719</v>
+        <v>-425.1292341410278</v>
       </c>
       <c r="Q91">
-        <v>139.116957349428</v>
+        <v>132.1707658589721</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3156636235417468</v>
+        <v>0.3426499858959214</v>
       </c>
       <c r="T91">
-        <v>4.550288384826883</v>
+        <v>5.005317223309572</v>
       </c>
       <c r="U91">
         <v>0.2476732333250682</v>
       </c>
       <c r="V91">
-        <v>0.0679474760267955</v>
+        <v>0.06719250407094221</v>
       </c>
       <c r="W91">
-        <v>0.2308444622412342</v>
+        <v>0.2310314485866101</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3235594096514072</v>
+        <v>0.3199643050997248</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8908,22 +8908,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2421933023175413</v>
+        <v>0.2442120346507919</v>
       </c>
       <c r="C92">
-        <v>-1772.760147810629</v>
+        <v>-1818.605242288179</v>
       </c>
       <c r="D92">
-        <v>1387.629852189371</v>
+        <v>1377.285757711821</v>
       </c>
       <c r="E92">
-        <v>1407.79</v>
+        <v>1443.291</v>
       </c>
       <c r="F92">
-        <v>3195.09</v>
+        <v>3230.591</v>
       </c>
       <c r="G92">
         <v>34.7</v>
@@ -8944,37 +8944,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M92">
-        <v>791.3382710645922</v>
+        <v>800.1309185208653</v>
       </c>
       <c r="N92">
-        <v>-538.1382710645922</v>
+        <v>-546.9309185208654</v>
       </c>
       <c r="O92">
-        <v>-113.0090369235644</v>
+        <v>-114.8554928893817</v>
       </c>
       <c r="P92">
-        <v>-425.1292341410278</v>
+        <v>-432.0754256314837</v>
       </c>
       <c r="Q92">
-        <v>132.1707658589721</v>
+        <v>125.2245743685163</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3426499858959214</v>
+        <v>0.375633317662135</v>
       </c>
       <c r="T92">
-        <v>5.005317223309572</v>
+        <v>5.561463581455081</v>
       </c>
       <c r="U92">
         <v>0.2476732333250682</v>
       </c>
       <c r="V92">
-        <v>0.06719250407094221</v>
+        <v>0.06645412490532747</v>
       </c>
       <c r="W92">
-        <v>0.2310314485866101</v>
+        <v>0.2312143253419778</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3199643050997248</v>
+        <v>0.3164482138348927</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8990,22 +8990,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2442120346507919</v>
+        <v>0.2462307669840426</v>
       </c>
       <c r="C93">
-        <v>-1818.605242288179</v>
+        <v>-1864.297257674641</v>
       </c>
       <c r="D93">
-        <v>1377.285757711821</v>
+        <v>1367.094742325359</v>
       </c>
       <c r="E93">
-        <v>1443.291</v>
+        <v>1478.792</v>
       </c>
       <c r="F93">
-        <v>3230.591</v>
+        <v>3266.092</v>
       </c>
       <c r="G93">
         <v>34.7</v>
@@ -9026,37 +9026,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M93">
-        <v>800.1309185208653</v>
+        <v>808.9235659771387</v>
       </c>
       <c r="N93">
-        <v>-546.9309185208654</v>
+        <v>-555.7235659771387</v>
       </c>
       <c r="O93">
-        <v>-114.8554928893817</v>
+        <v>-116.7019488551991</v>
       </c>
       <c r="P93">
-        <v>-432.0754256314837</v>
+        <v>-439.0216171219396</v>
       </c>
       <c r="Q93">
-        <v>125.2245743685163</v>
+        <v>118.2783828780604</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.375633317662135</v>
+        <v>0.416862482369902</v>
       </c>
       <c r="T93">
-        <v>5.561463581455081</v>
+        <v>6.256646529136969</v>
       </c>
       <c r="U93">
         <v>0.2476732333250682</v>
       </c>
       <c r="V93">
-        <v>0.06645412490532747</v>
+        <v>0.06573179746070434</v>
       </c>
       <c r="W93">
-        <v>0.2312143253419778</v>
+        <v>0.231393226515707</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3164482138348927</v>
+        <v>0.3130085593366874</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9072,22 +9072,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2462307669840426</v>
+        <v>0.2482494993172933</v>
       </c>
       <c r="C94">
-        <v>-1864.297257674641</v>
+        <v>-1909.839567067286</v>
       </c>
       <c r="D94">
-        <v>1367.094742325359</v>
+        <v>1357.053432932714</v>
       </c>
       <c r="E94">
-        <v>1478.792</v>
+        <v>1514.293</v>
       </c>
       <c r="F94">
-        <v>3266.092</v>
+        <v>3301.593</v>
       </c>
       <c r="G94">
         <v>34.7</v>
@@ -9108,37 +9108,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M94">
-        <v>808.9235659771387</v>
+        <v>817.7162134334119</v>
       </c>
       <c r="N94">
-        <v>-555.7235659771387</v>
+        <v>-564.516213433412</v>
       </c>
       <c r="O94">
-        <v>-116.7019488551991</v>
+        <v>-118.5484048210165</v>
       </c>
       <c r="P94">
-        <v>-439.0216171219396</v>
+        <v>-445.9678086123955</v>
       </c>
       <c r="Q94">
-        <v>118.2783828780604</v>
+        <v>111.3321913876045</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.416862482369902</v>
+        <v>0.4698714084227452</v>
       </c>
       <c r="T94">
-        <v>6.256646529136969</v>
+        <v>7.150453176156536</v>
       </c>
       <c r="U94">
         <v>0.2476732333250682</v>
       </c>
       <c r="V94">
-        <v>0.06573179746070434</v>
+        <v>0.0650250039396215</v>
       </c>
       <c r="W94">
-        <v>0.231393226515707</v>
+        <v>0.2315682803523668</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3130085593366874</v>
+        <v>0.3096428759029596</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9154,22 +9154,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2482494993172933</v>
+        <v>0.250268231650544</v>
       </c>
       <c r="C95">
-        <v>-1909.839567067286</v>
+        <v>-1955.235445184396</v>
       </c>
       <c r="D95">
-        <v>1357.053432932714</v>
+        <v>1347.158554815604</v>
       </c>
       <c r="E95">
-        <v>1514.293</v>
+        <v>1549.794</v>
       </c>
       <c r="F95">
-        <v>3301.593</v>
+        <v>3337.094</v>
       </c>
       <c r="G95">
         <v>34.7</v>
@@ -9190,37 +9190,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M95">
-        <v>817.7162134334119</v>
+        <v>826.5088608896851</v>
       </c>
       <c r="N95">
-        <v>-564.516213433412</v>
+        <v>-573.3088608896852</v>
       </c>
       <c r="O95">
-        <v>-118.5484048210165</v>
+        <v>-120.3948607868339</v>
       </c>
       <c r="P95">
-        <v>-445.9678086123955</v>
+        <v>-452.9140001028513</v>
       </c>
       <c r="Q95">
-        <v>111.3321913876045</v>
+        <v>104.3859998971486</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4698714084227452</v>
+        <v>0.5405499764932028</v>
       </c>
       <c r="T95">
-        <v>7.150453176156536</v>
+        <v>8.342195372182628</v>
       </c>
       <c r="U95">
         <v>0.2476732333250682</v>
       </c>
       <c r="V95">
-        <v>0.0650250039396215</v>
+        <v>0.06433324857856169</v>
       </c>
       <c r="W95">
-        <v>0.2315682803523668</v>
+        <v>0.2317396096393105</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3096428759029596</v>
+        <v>0.3063488027550557</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9236,22 +9236,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.250268231650544</v>
+        <v>0.2522869639837947</v>
       </c>
       <c r="C96">
-        <v>-1955.235445184396</v>
+        <v>-2000.488071925927</v>
       </c>
       <c r="D96">
-        <v>1347.158554815604</v>
+        <v>1337.406928074074</v>
       </c>
       <c r="E96">
-        <v>1549.794</v>
+        <v>1585.295</v>
       </c>
       <c r="F96">
-        <v>3337.094</v>
+        <v>3372.595</v>
       </c>
       <c r="G96">
         <v>34.7</v>
@@ -9272,37 +9272,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M96">
-        <v>826.5088608896851</v>
+        <v>835.3015083459584</v>
       </c>
       <c r="N96">
-        <v>-573.3088608896852</v>
+        <v>-582.1015083459585</v>
       </c>
       <c r="O96">
-        <v>-120.3948607868339</v>
+        <v>-122.2413167526513</v>
       </c>
       <c r="P96">
-        <v>-452.9140001028513</v>
+        <v>-459.8601915933071</v>
       </c>
       <c r="Q96">
-        <v>104.3859998971486</v>
+        <v>97.4398084066928</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5405499764932028</v>
+        <v>0.6394999717918437</v>
       </c>
       <c r="T96">
-        <v>8.342195372182628</v>
+        <v>10.01063444661916</v>
       </c>
       <c r="U96">
         <v>0.2476732333250682</v>
       </c>
       <c r="V96">
-        <v>0.06433324857856169</v>
+        <v>0.06365605648826105</v>
       </c>
       <c r="W96">
-        <v>0.2317396096393105</v>
+        <v>0.2319073319938974</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3063488027550557</v>
+        <v>0.3031240785155288</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9318,22 +9318,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2522869639837947</v>
+        <v>0.2543056963170453</v>
       </c>
       <c r="C97">
-        <v>-2000.488071925927</v>
+        <v>-2045.600535780629</v>
       </c>
       <c r="D97">
-        <v>1337.406928074074</v>
+        <v>1327.795464219371</v>
       </c>
       <c r="E97">
-        <v>1585.295</v>
+        <v>1620.796</v>
       </c>
       <c r="F97">
-        <v>3372.595</v>
+        <v>3408.096</v>
       </c>
       <c r="G97">
         <v>34.7</v>
@@ -9354,37 +9354,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M97">
-        <v>835.3015083459584</v>
+        <v>844.0941558022316</v>
       </c>
       <c r="N97">
-        <v>-582.1015083459585</v>
+        <v>-590.8941558022317</v>
       </c>
       <c r="O97">
-        <v>-122.2413167526513</v>
+        <v>-124.0877727184687</v>
       </c>
       <c r="P97">
-        <v>-459.8601915933071</v>
+        <v>-466.806383083763</v>
       </c>
       <c r="Q97">
-        <v>97.4398084066928</v>
+        <v>90.49361691623693</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6394999717918437</v>
+        <v>0.7879249647398048</v>
       </c>
       <c r="T97">
-        <v>10.01063444661916</v>
+        <v>12.51329305827395</v>
       </c>
       <c r="U97">
         <v>0.2476732333250682</v>
       </c>
       <c r="V97">
-        <v>0.06365605648826105</v>
+        <v>0.06299297256650833</v>
       </c>
       <c r="W97">
-        <v>0.2319073319938974</v>
+        <v>0.2320715601327637</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3031240785155288</v>
+        <v>0.2999665360309921</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9400,22 +9400,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2543056963170453</v>
+        <v>0.256324428650296</v>
       </c>
       <c r="C98">
-        <v>-2045.600535780629</v>
+        <v>-2090.575837087316</v>
       </c>
       <c r="D98">
-        <v>1327.795464219371</v>
+        <v>1318.321162912683</v>
       </c>
       <c r="E98">
-        <v>1620.796</v>
+        <v>1656.297</v>
       </c>
       <c r="F98">
-        <v>3408.096</v>
+        <v>3443.597</v>
       </c>
       <c r="G98">
         <v>34.7</v>
@@ -9436,37 +9436,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M98">
-        <v>844.0941558022316</v>
+        <v>852.8868032585048</v>
       </c>
       <c r="N98">
-        <v>-590.8941558022317</v>
+        <v>-599.6868032585048</v>
       </c>
       <c r="O98">
-        <v>-124.0877727184687</v>
+        <v>-125.934228684286</v>
       </c>
       <c r="P98">
-        <v>-466.806383083763</v>
+        <v>-473.7525745742188</v>
       </c>
       <c r="Q98">
-        <v>90.49361691623693</v>
+        <v>83.54742542578117</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7879249647398028</v>
+        <v>1.035299952986404</v>
       </c>
       <c r="T98">
-        <v>12.51329305827392</v>
+        <v>16.68439074436523</v>
       </c>
       <c r="U98">
         <v>0.2476732333250682</v>
       </c>
       <c r="V98">
-        <v>0.06299297256650833</v>
+        <v>0.06234356047819382</v>
       </c>
       <c r="W98">
-        <v>0.2320715601327637</v>
+        <v>0.232232402124437</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2999665360309921</v>
+        <v>0.2968740975152087</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9482,22 +9482,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.256324428650296</v>
+        <v>0.2583431609835467</v>
       </c>
       <c r="C99">
-        <v>-2090.575837087316</v>
+        <v>-2135.416891157487</v>
       </c>
       <c r="D99">
-        <v>1318.321162912683</v>
+        <v>1308.981108842513</v>
       </c>
       <c r="E99">
-        <v>1656.297</v>
+        <v>1691.798</v>
       </c>
       <c r="F99">
-        <v>3443.597</v>
+        <v>3479.098</v>
       </c>
       <c r="G99">
         <v>34.7</v>
@@ -9518,37 +9518,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M99">
-        <v>852.8868032585048</v>
+        <v>861.6794507147781</v>
       </c>
       <c r="N99">
-        <v>-599.6868032585048</v>
+        <v>-608.4794507147782</v>
       </c>
       <c r="O99">
-        <v>-125.934228684286</v>
+        <v>-127.7806846501034</v>
       </c>
       <c r="P99">
-        <v>-473.7525745742188</v>
+        <v>-480.6987660646748</v>
       </c>
       <c r="Q99">
-        <v>83.54742542578117</v>
+        <v>76.60123393532518</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.035299952986404</v>
+        <v>1.530049929479606</v>
       </c>
       <c r="T99">
-        <v>16.68439074436523</v>
+        <v>25.02658611654784</v>
       </c>
       <c r="U99">
         <v>0.2476732333250682</v>
       </c>
       <c r="V99">
-        <v>0.06234356047819382</v>
+        <v>0.06170740169780407</v>
       </c>
       <c r="W99">
-        <v>0.232232402124437</v>
+        <v>0.2323899616264843</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2968740975152087</v>
+        <v>0.2938447699895432</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9564,22 +9564,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2583431609835467</v>
+        <v>0.2603618933167974</v>
       </c>
       <c r="C100">
-        <v>-2135.416891157487</v>
+        <v>-2180.126531266147</v>
       </c>
       <c r="D100">
-        <v>1308.981108842513</v>
+        <v>1299.772468733853</v>
       </c>
       <c r="E100">
-        <v>1691.798</v>
+        <v>1727.299</v>
       </c>
       <c r="F100">
-        <v>3479.098</v>
+        <v>3514.599</v>
       </c>
       <c r="G100">
         <v>34.7</v>
@@ -9600,37 +9600,37 @@
         <v>253.1999999999999</v>
       </c>
       <c r="M100">
-        <v>861.6794507147781</v>
+        <v>870.4720981710512</v>
       </c>
       <c r="N100">
-        <v>-608.4794507147782</v>
+        <v>-617.2720981710513</v>
       </c>
       <c r="O100">
-        <v>-127.7806846501034</v>
+        <v>-129.6271406159208</v>
       </c>
       <c r="P100">
-        <v>-480.6987660646748</v>
+        <v>-487.6449575551305</v>
       </c>
       <c r="Q100">
-        <v>76.60123393532518</v>
+        <v>69.65504244486942</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.530049929479606</v>
+        <v>3.014299858959211</v>
       </c>
       <c r="T100">
-        <v>25.02658611654784</v>
+        <v>50.05317223309567</v>
       </c>
       <c r="U100">
         <v>0.2476732333250682</v>
       </c>
       <c r="V100">
-        <v>0.06170740169780407</v>
+        <v>0.06108409460994748</v>
       </c>
       <c r="W100">
-        <v>0.2323899616264843</v>
+        <v>0.2325443381082881</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9638,91 +9638,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2938447699895432</v>
+        <v>0.2908766409997499</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2603618933167974</v>
-      </c>
-      <c r="C101">
-        <v>-2180.126531266147</v>
-      </c>
-      <c r="D101">
-        <v>1299.772468733853</v>
-      </c>
-      <c r="E101">
-        <v>1727.299</v>
-      </c>
-      <c r="F101">
-        <v>3514.599</v>
-      </c>
-      <c r="G101">
-        <v>34.7</v>
-      </c>
-      <c r="H101">
-        <v>1762.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>810.4999999999999</v>
-      </c>
-      <c r="K101">
-        <v>557.3</v>
-      </c>
-      <c r="L101">
-        <v>253.1999999999999</v>
-      </c>
-      <c r="M101">
-        <v>870.4720981710512</v>
-      </c>
-      <c r="N101">
-        <v>-617.2720981710513</v>
-      </c>
-      <c r="O101">
-        <v>-129.6271406159208</v>
-      </c>
-      <c r="P101">
-        <v>-487.6449575551305</v>
-      </c>
-      <c r="Q101">
-        <v>69.65504244486942</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.014299858959211</v>
-      </c>
-      <c r="T101">
-        <v>50.05317223309567</v>
-      </c>
-      <c r="U101">
-        <v>0.2476732333250682</v>
-      </c>
-      <c r="V101">
-        <v>0.06108409460994748</v>
-      </c>
-      <c r="W101">
-        <v>0.2325443381082881</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2908766409997499</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
